--- a/Excel Daily Challenges.xlsx
+++ b/Excel Daily Challenges.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28817"/>
   <workbookPr filterPrivacy="1" codeName="ThisWorkbook" defaultThemeVersion="166925"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F6C596E7-30B1-4C63-A815-3D55EF1B4C14}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DE05E16B-CEC3-4A64-86C3-E712EF4BDE0A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" firstSheet="14" activeTab="14" xr2:uid="{0ACB132C-7219-4B66-ACBB-64BA10C47BDC}"/>
   </bookViews>
@@ -45,6 +45,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">Aggregate!$A$6:$D$36</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Daily Challenge 1 - Cleaning'!$B$6:$I$6</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="24" hidden="1">'Daily Challenge 10 - Referencin'!$A$10:$D$10</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Daily Challenge 2 - IF'!$A$6:$D$21</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Daily Challenge 3 - SUMIFS'!$A$7:$D$7</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="15" hidden="1">'Daily Challenge 9 - IS Number'!$A$11:$D$11</definedName>
@@ -1623,7 +1624,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="19">
+  <numFmts count="20">
     <numFmt numFmtId="6" formatCode="&quot;$&quot;#,##0_);[Red]\(&quot;$&quot;#,##0\)"/>
     <numFmt numFmtId="8" formatCode="&quot;$&quot;#,##0.00_);[Red]\(&quot;$&quot;#,##0.00\)"/>
     <numFmt numFmtId="44" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
@@ -1643,6 +1644,7 @@
     <numFmt numFmtId="176" formatCode="\(0.0%\)"/>
     <numFmt numFmtId="177" formatCode="0.0%;0.0%"/>
     <numFmt numFmtId="178" formatCode="\(0.0%\);0.0%"/>
+    <numFmt numFmtId="179" formatCode="&quot;$&quot;#,##0.00"/>
   </numFmts>
   <fonts count="28">
     <font>
@@ -2568,7 +2570,7 @@
     <xf numFmtId="9" fontId="18" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="165" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="167">
+  <cellXfs count="170">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" quotePrefix="1" applyFont="1"/>
@@ -2707,8 +2709,6 @@
     <xf numFmtId="0" fontId="12" fillId="18" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="20" borderId="11" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="0" fillId="19" borderId="11" xfId="8" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="8" fontId="0" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="20" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="centerContinuous" wrapText="1"/>
@@ -2850,6 +2850,21 @@
     <xf numFmtId="0" fontId="7" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="0" fillId="19" borderId="11" xfId="8" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="8" fontId="0" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="173" fontId="24" fillId="22" borderId="46" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1" readingOrder="1"/>
     </xf>
@@ -2873,11 +2888,71 @@
     <cellStyle name="Percent" xfId="9" builtinId="5"/>
     <cellStyle name="Percent 2" xfId="12" xr:uid="{ECCEC94D-8720-4B08-A6AD-07F7FD42CF90}"/>
   </cellStyles>
-  <dxfs count="2">
+  <dxfs count="8">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <condense val="0"/>
         <extend val="0"/>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <color rgb="FF9C0006"/>
       </font>
       <fill>
@@ -6748,7 +6823,7 @@
         <f>INDEX($J$8:$J$19,MATCH(A7,$H$8:$H$19,0))</f>
         <v>Cost Of Goods Sold</v>
       </c>
-      <c r="C7" s="162" t="str">
+      <c r="C7" s="160" t="str">
         <f>INDEX($I$8:$I$19, MATCH(A7, $H$8:$H$19))</f>
         <v>COGS</v>
       </c>
@@ -6773,7 +6848,7 @@
         <f t="shared" ref="B8:B35" si="0">INDEX($J$8:$J$19,MATCH(A8,$H$8:$H$19,0))</f>
         <v>Cost Of Goods Sold</v>
       </c>
-      <c r="C8" s="162" t="str">
+      <c r="C8" s="160" t="str">
         <f t="shared" ref="C8:C35" si="1">INDEX($I$8:$I$19, MATCH(A8, $H$8:$H$19))</f>
         <v>COGS</v>
       </c>
@@ -6798,7 +6873,7 @@
         <f t="shared" si="0"/>
         <v>Cost Of Goods Sold</v>
       </c>
-      <c r="C9" s="162" t="str">
+      <c r="C9" s="160" t="str">
         <f t="shared" si="1"/>
         <v>COGS</v>
       </c>
@@ -6823,7 +6898,7 @@
         <f t="shared" si="0"/>
         <v>Merchandise, Material, Supplies And Utilities</v>
       </c>
-      <c r="C10" s="162" t="str">
+      <c r="C10" s="160" t="str">
         <f t="shared" si="1"/>
         <v>MMSAU</v>
       </c>
@@ -6848,7 +6923,7 @@
         <f t="shared" si="0"/>
         <v>Employee Related Expenses</v>
       </c>
-      <c r="C11" s="162" t="str">
+      <c r="C11" s="160" t="str">
         <f t="shared" si="1"/>
         <v>ERE</v>
       </c>
@@ -6873,7 +6948,7 @@
         <f t="shared" si="0"/>
         <v>Merchandise, Material, Supplies And Utilities</v>
       </c>
-      <c r="C12" s="162" t="str">
+      <c r="C12" s="160" t="str">
         <f t="shared" si="1"/>
         <v>MMSAU</v>
       </c>
@@ -6898,7 +6973,7 @@
         <f t="shared" si="0"/>
         <v>Employee Related Expenses</v>
       </c>
-      <c r="C13" s="162" t="str">
+      <c r="C13" s="160" t="str">
         <f t="shared" si="1"/>
         <v>ERE</v>
       </c>
@@ -6923,7 +6998,7 @@
         <f t="shared" si="0"/>
         <v>Merchandise, Material, Supplies And Utilities</v>
       </c>
-      <c r="C14" s="162" t="str">
+      <c r="C14" s="160" t="str">
         <f t="shared" si="1"/>
         <v>MMSAU</v>
       </c>
@@ -6948,7 +7023,7 @@
         <f t="shared" si="0"/>
         <v>Employee Related Expenses</v>
       </c>
-      <c r="C15" s="162" t="str">
+      <c r="C15" s="160" t="str">
         <f t="shared" si="1"/>
         <v>ERE</v>
       </c>
@@ -6973,7 +7048,7 @@
         <f t="shared" si="0"/>
         <v>Services</v>
       </c>
-      <c r="C16" s="162" t="str">
+      <c r="C16" s="160" t="str">
         <f t="shared" si="1"/>
         <v>S</v>
       </c>
@@ -6998,7 +7073,7 @@
         <f t="shared" si="0"/>
         <v>Rent, Depreciation, and Amortization</v>
       </c>
-      <c r="C17" s="162" t="str">
+      <c r="C17" s="160" t="str">
         <f t="shared" si="1"/>
         <v>RDA</v>
       </c>
@@ -7023,7 +7098,7 @@
         <f t="shared" si="0"/>
         <v>Rental Income, Nonoperating</v>
       </c>
-      <c r="C18" s="162" t="str">
+      <c r="C18" s="160" t="str">
         <f t="shared" si="1"/>
         <v>RIN</v>
       </c>
@@ -7048,7 +7123,7 @@
         <f t="shared" si="0"/>
         <v>Merchandise, Material, Supplies And Utilities</v>
       </c>
-      <c r="C19" s="162" t="str">
+      <c r="C19" s="160" t="str">
         <f t="shared" si="1"/>
         <v>MMSAU</v>
       </c>
@@ -7073,7 +7148,7 @@
         <f t="shared" si="0"/>
         <v>Employee Related Expenses</v>
       </c>
-      <c r="C20" s="162" t="str">
+      <c r="C20" s="160" t="str">
         <f t="shared" si="1"/>
         <v>ERE</v>
       </c>
@@ -7089,7 +7164,7 @@
         <f t="shared" si="0"/>
         <v>Merchandise, Material, Supplies And Utilities</v>
       </c>
-      <c r="C21" s="162" t="str">
+      <c r="C21" s="160" t="str">
         <f t="shared" si="1"/>
         <v>MMSAU</v>
       </c>
@@ -7105,7 +7180,7 @@
         <f t="shared" si="0"/>
         <v>Employee Related Expenses</v>
       </c>
-      <c r="C22" s="162" t="str">
+      <c r="C22" s="160" t="str">
         <f t="shared" si="1"/>
         <v>ERE</v>
       </c>
@@ -7121,7 +7196,7 @@
         <f t="shared" si="0"/>
         <v>Merchandise, Material, Supplies And Utilities</v>
       </c>
-      <c r="C23" s="162" t="str">
+      <c r="C23" s="160" t="str">
         <f t="shared" si="1"/>
         <v>MMSAU</v>
       </c>
@@ -7137,7 +7212,7 @@
         <f t="shared" si="0"/>
         <v>Employee Related Expenses</v>
       </c>
-      <c r="C24" s="162" t="str">
+      <c r="C24" s="160" t="str">
         <f t="shared" si="1"/>
         <v>ERE</v>
       </c>
@@ -7153,7 +7228,7 @@
         <f t="shared" si="0"/>
         <v>Services</v>
       </c>
-      <c r="C25" s="162" t="str">
+      <c r="C25" s="160" t="str">
         <f t="shared" si="1"/>
         <v>S</v>
       </c>
@@ -7169,7 +7244,7 @@
         <f t="shared" si="0"/>
         <v>Rental Income, Nonoperating</v>
       </c>
-      <c r="C26" s="162" t="str">
+      <c r="C26" s="160" t="str">
         <f t="shared" si="1"/>
         <v>RIN</v>
       </c>
@@ -7185,7 +7260,7 @@
         <f t="shared" si="0"/>
         <v>Operating Lease</v>
       </c>
-      <c r="C27" s="162" t="str">
+      <c r="C27" s="160" t="str">
         <f t="shared" si="1"/>
         <v>OL</v>
       </c>
@@ -7201,7 +7276,7 @@
         <f t="shared" si="0"/>
         <v>Other Nonoperating Income</v>
       </c>
-      <c r="C28" s="162" t="str">
+      <c r="C28" s="160" t="str">
         <f t="shared" si="1"/>
         <v>ONI</v>
       </c>
@@ -7217,7 +7292,7 @@
         <f t="shared" si="0"/>
         <v>Other Nonoperating Expense</v>
       </c>
-      <c r="C29" s="162" t="str">
+      <c r="C29" s="160" t="str">
         <f t="shared" si="1"/>
         <v>ONE</v>
       </c>
@@ -7233,7 +7308,7 @@
         <f t="shared" si="0"/>
         <v>Interest Expense</v>
       </c>
-      <c r="C30" s="162" t="str">
+      <c r="C30" s="160" t="str">
         <f t="shared" si="1"/>
         <v>IE</v>
       </c>
@@ -7249,7 +7324,7 @@
         <f t="shared" si="0"/>
         <v>Employee Related Expenses</v>
       </c>
-      <c r="C31" s="162" t="str">
+      <c r="C31" s="160" t="str">
         <f t="shared" si="1"/>
         <v>ERE</v>
       </c>
@@ -7265,7 +7340,7 @@
         <f t="shared" si="0"/>
         <v>Services</v>
       </c>
-      <c r="C32" s="162" t="str">
+      <c r="C32" s="160" t="str">
         <f t="shared" si="1"/>
         <v>S</v>
       </c>
@@ -7281,7 +7356,7 @@
         <f t="shared" si="0"/>
         <v>Rental Income, Nonoperating</v>
       </c>
-      <c r="C33" s="162" t="str">
+      <c r="C33" s="160" t="str">
         <f t="shared" si="1"/>
         <v>RIN</v>
       </c>
@@ -7297,7 +7372,7 @@
         <f t="shared" si="0"/>
         <v>Operating Lease</v>
       </c>
-      <c r="C34" s="162" t="str">
+      <c r="C34" s="160" t="str">
         <f t="shared" si="1"/>
         <v>OL</v>
       </c>
@@ -7313,7 +7388,7 @@
         <f t="shared" si="0"/>
         <v>Other Nonoperating Income</v>
       </c>
-      <c r="C35" s="162" t="str">
+      <c r="C35" s="160" t="str">
         <f t="shared" si="1"/>
         <v>ONI</v>
       </c>
@@ -7341,13 +7416,13 @@
   </cols>
   <sheetData>
     <row r="6" spans="1:8">
-      <c r="A6" s="163" t="s">
+      <c r="A6" s="161" t="s">
         <v>62</v>
       </c>
-      <c r="B6" s="164" t="s">
+      <c r="B6" s="162" t="s">
         <v>63</v>
       </c>
-      <c r="C6" s="163" t="s">
+      <c r="C6" s="161" t="s">
         <v>24</v>
       </c>
       <c r="G6" s="14" t="s">
@@ -7363,7 +7438,7 @@
         <f t="array" ref="B7">INDEX($H$8:$H$19,MATCH(TRIM(A7),TRIM($G$8:$G$19)))</f>
         <v>Cost Of Goods Sold</v>
       </c>
-      <c r="C7" s="162">
+      <c r="C7" s="160">
         <v>17813</v>
       </c>
       <c r="G7" s="12" t="s">
@@ -7381,7 +7456,7 @@
         <f t="array" ref="B8">INDEX($H$8:$H$19,MATCH(TRIM(A8),TRIM($G$8:$G$19)))</f>
         <v>Cost Of Goods Sold</v>
       </c>
-      <c r="C8" s="162">
+      <c r="C8" s="160">
         <v>13759</v>
       </c>
       <c r="G8" t="s">
@@ -7399,7 +7474,7 @@
         <f t="array" ref="B9">INDEX($H$8:$H$19,MATCH(TRIM(A9),TRIM($G$8:$G$19)))</f>
         <v>Cost Of Goods Sold</v>
       </c>
-      <c r="C9" s="162">
+      <c r="C9" s="160">
         <v>10899</v>
       </c>
       <c r="G9" t="s">
@@ -7417,7 +7492,7 @@
         <f t="array" ref="B10">INDEX($H$8:$H$19,MATCH(TRIM(A10),TRIM($G$8:$G$19)))</f>
         <v>Cost Of Goods Sold</v>
       </c>
-      <c r="C10" s="162">
+      <c r="C10" s="160">
         <v>17883</v>
       </c>
       <c r="G10" t="s">
@@ -7435,7 +7510,7 @@
         <f t="array" ref="B11">INDEX($H$8:$H$19,MATCH(TRIM(A11),TRIM($G$8:$G$19)))</f>
         <v>Cost Of Goods Sold</v>
       </c>
-      <c r="C11" s="162">
+      <c r="C11" s="160">
         <v>16024</v>
       </c>
       <c r="G11" t="s">
@@ -7453,7 +7528,7 @@
         <f t="array" ref="B12">INDEX($H$8:$H$19,MATCH(TRIM(A12),TRIM($G$8:$G$19)))</f>
         <v>Merchandise, Material, Supplies And Utilities</v>
       </c>
-      <c r="C12" s="162">
+      <c r="C12" s="160">
         <v>11635</v>
       </c>
       <c r="G12" t="s">
@@ -7471,7 +7546,7 @@
         <f t="array" ref="B13">INDEX($H$8:$H$19,MATCH(TRIM(A13),TRIM($G$8:$G$19)))</f>
         <v>Employee Related Expenses</v>
       </c>
-      <c r="C13" s="162">
+      <c r="C13" s="160">
         <v>20579</v>
       </c>
       <c r="G13" t="s">
@@ -7489,7 +7564,7 @@
         <f t="array" ref="B14">INDEX($H$8:$H$19,MATCH(TRIM(A14),TRIM($G$8:$G$19)))</f>
         <v>Merchandise, Material, Supplies And Utilities</v>
       </c>
-      <c r="C14" s="162">
+      <c r="C14" s="160">
         <v>14090</v>
       </c>
       <c r="G14" t="s">
@@ -7507,7 +7582,7 @@
         <f t="array" ref="B15">INDEX($H$8:$H$19,MATCH(TRIM(A15),TRIM($G$8:$G$19)))</f>
         <v>Employee Related Expenses</v>
       </c>
-      <c r="C15" s="162">
+      <c r="C15" s="160">
         <v>21485</v>
       </c>
       <c r="G15" t="s">
@@ -7525,7 +7600,7 @@
         <f t="array" ref="B16">INDEX($H$8:$H$19,MATCH(TRIM(A16),TRIM($G$8:$G$19)))</f>
         <v>Services</v>
       </c>
-      <c r="C16" s="162">
+      <c r="C16" s="160">
         <v>16730</v>
       </c>
       <c r="G16" t="s">
@@ -7543,7 +7618,7 @@
         <f t="array" ref="B17">INDEX($H$8:$H$19,MATCH(TRIM(A17),TRIM($G$8:$G$19)))</f>
         <v>Rent, Depreciation, and Amortization</v>
       </c>
-      <c r="C17" s="162">
+      <c r="C17" s="160">
         <v>14001</v>
       </c>
       <c r="G17" t="s">
@@ -7561,7 +7636,7 @@
         <f t="array" ref="B18">INDEX($H$8:$H$19,MATCH(TRIM(A18),TRIM($G$8:$G$19)))</f>
         <v>Rental Income, Nonoperating</v>
       </c>
-      <c r="C18" s="162">
+      <c r="C18" s="160">
         <v>18440</v>
       </c>
       <c r="G18" t="s">
@@ -7579,7 +7654,7 @@
         <f t="array" ref="B19">INDEX($H$8:$H$19,MATCH(TRIM(A19),TRIM($G$8:$G$19)))</f>
         <v>Merchandise, Material, Supplies And Utilities</v>
       </c>
-      <c r="C19" s="162">
+      <c r="C19" s="160">
         <v>11796</v>
       </c>
       <c r="G19" t="s">
@@ -7682,7 +7757,10 @@
       <c r="C12" s="100" t="s">
         <v>246</v>
       </c>
-      <c r="D12" s="101"/>
+      <c r="D12" s="101" t="b" cm="1">
+        <f t="array" ref="D12:D23">ISNUMBER(MATCH(C12:C23, A12:A30,0))</f>
+        <v>1</v>
+      </c>
     </row>
     <row r="13" spans="1:4">
       <c r="A13" s="100" t="s">
@@ -7691,7 +7769,9 @@
       <c r="C13" s="100" t="s">
         <v>248</v>
       </c>
-      <c r="D13" s="101"/>
+      <c r="D13" s="101" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="14" spans="1:4">
       <c r="A14" s="100" t="s">
@@ -7700,7 +7780,9 @@
       <c r="C14" s="100" t="s">
         <v>250</v>
       </c>
-      <c r="D14" s="101"/>
+      <c r="D14" s="101" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="15" spans="1:4">
       <c r="A15" s="100" t="s">
@@ -7709,7 +7791,9 @@
       <c r="C15" s="100" t="s">
         <v>252</v>
       </c>
-      <c r="D15" s="101"/>
+      <c r="D15" s="101" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="16" spans="1:4">
       <c r="A16" s="100" t="s">
@@ -7718,7 +7802,9 @@
       <c r="C16" s="100" t="s">
         <v>254</v>
       </c>
-      <c r="D16" s="101"/>
+      <c r="D16" s="101" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="17" spans="1:4">
       <c r="A17" s="100" t="s">
@@ -7727,7 +7813,9 @@
       <c r="C17" s="100" t="s">
         <v>255</v>
       </c>
-      <c r="D17" s="101"/>
+      <c r="D17" s="101" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="18" spans="1:4">
       <c r="A18" s="100" t="s">
@@ -7736,7 +7824,9 @@
       <c r="C18" s="100" t="s">
         <v>257</v>
       </c>
-      <c r="D18" s="101"/>
+      <c r="D18" s="101" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="19" spans="1:4">
       <c r="A19" s="100" t="s">
@@ -7745,7 +7835,9 @@
       <c r="C19" s="100" t="s">
         <v>259</v>
       </c>
-      <c r="D19" s="101"/>
+      <c r="D19" s="101" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="20" spans="1:4">
       <c r="A20" s="100" t="s">
@@ -7754,7 +7846,9 @@
       <c r="C20" s="100" t="s">
         <v>249</v>
       </c>
-      <c r="D20" s="101"/>
+      <c r="D20" s="101" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="21" spans="1:4">
       <c r="A21" s="100" t="s">
@@ -7763,7 +7857,9 @@
       <c r="C21" s="100" t="s">
         <v>262</v>
       </c>
-      <c r="D21" s="101"/>
+      <c r="D21" s="101" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="22" spans="1:4">
       <c r="A22" s="100" t="s">
@@ -7772,7 +7868,9 @@
       <c r="C22" s="100" t="s">
         <v>247</v>
       </c>
-      <c r="D22" s="101"/>
+      <c r="D22" s="101" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="23" spans="1:4">
       <c r="A23" s="100" t="s">
@@ -7781,7 +7879,9 @@
       <c r="C23" s="100" t="s">
         <v>265</v>
       </c>
-      <c r="D23" s="101"/>
+      <c r="D23" s="101" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="24" spans="1:4">
       <c r="A24" s="100" t="s">
@@ -7823,6 +7923,11 @@
     </row>
   </sheetData>
   <autoFilter ref="A11:D11" xr:uid="{E7F32FCF-B1A4-492B-BE4C-DC5E7C5DB630}"/>
+  <conditionalFormatting sqref="D12:D23">
+    <cfRule type="containsText" dxfId="0" priority="1" operator="containsText" text="TRUE">
+      <formula>NOT(ISERROR(SEARCH("TRUE",D12)))</formula>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -8065,9 +8170,9 @@
   <cols>
     <col min="1" max="1" width="7.26953125" style="58" customWidth="1"/>
     <col min="2" max="2" width="7.81640625" style="58" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="26.1796875" style="116" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="12.26953125" style="116" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.7265625" style="116" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="26.1796875" style="114" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.26953125" style="114" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.7265625" style="114" bestFit="1" customWidth="1"/>
     <col min="6" max="7" width="6.6328125" style="58" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="5.7265625" style="58" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="9.26953125" style="58" customWidth="1"/>
@@ -8075,862 +8180,862 @@
   </cols>
   <sheetData>
     <row r="6" spans="2:9">
-      <c r="B6" s="150" t="s">
+      <c r="B6" s="148" t="s">
         <v>21</v>
       </c>
-      <c r="C6" s="150" t="s">
+      <c r="C6" s="148" t="s">
         <v>105</v>
       </c>
-      <c r="D6" s="151" t="s">
+      <c r="D6" s="149" t="s">
         <v>106</v>
       </c>
-      <c r="E6" s="151" t="s">
+      <c r="E6" s="149" t="s">
         <v>107</v>
       </c>
-      <c r="F6" s="151" t="s">
+      <c r="F6" s="149" t="s">
         <v>108</v>
       </c>
-      <c r="G6" s="151" t="s">
+      <c r="G6" s="149" t="s">
         <v>35</v>
       </c>
-      <c r="H6" s="151" t="s">
+      <c r="H6" s="149" t="s">
         <v>109</v>
       </c>
-      <c r="I6" s="151" t="s">
+      <c r="I6" s="149" t="s">
         <v>110</v>
       </c>
     </row>
     <row r="7" spans="2:9">
-      <c r="B7" s="152">
+      <c r="B7" s="150">
         <v>45076</v>
       </c>
-      <c r="C7" s="153" t="s">
+      <c r="C7" s="151" t="s">
         <v>111</v>
       </c>
-      <c r="D7" s="153" t="s">
+      <c r="D7" s="151" t="s">
         <v>112</v>
       </c>
-      <c r="E7" s="153" t="s">
+      <c r="E7" s="151" t="s">
         <v>113</v>
       </c>
-      <c r="F7" s="153" t="s">
+      <c r="F7" s="151" t="s">
         <v>114</v>
       </c>
-      <c r="G7" s="154">
+      <c r="G7" s="152">
         <v>4500</v>
       </c>
-      <c r="H7" s="154">
+      <c r="H7" s="152">
         <v>598</v>
       </c>
-      <c r="I7" s="155">
+      <c r="I7" s="153">
         <f>H7/G7</f>
         <v>0.13288888888888889</v>
       </c>
     </row>
     <row r="8" spans="2:9">
-      <c r="B8" s="152">
+      <c r="B8" s="150">
         <v>45076</v>
       </c>
-      <c r="C8" s="153" t="s">
+      <c r="C8" s="151" t="s">
         <v>115</v>
       </c>
-      <c r="D8" s="153" t="s">
+      <c r="D8" s="151" t="s">
         <v>116</v>
       </c>
-      <c r="E8" s="153" t="s">
+      <c r="E8" s="151" t="s">
         <v>117</v>
       </c>
-      <c r="F8" s="153" t="s">
+      <c r="F8" s="151" t="s">
         <v>118</v>
       </c>
-      <c r="G8" s="154">
+      <c r="G8" s="152">
         <v>3800</v>
       </c>
-      <c r="H8" s="154">
+      <c r="H8" s="152">
         <v>1045</v>
       </c>
-      <c r="I8" s="155">
+      <c r="I8" s="153">
         <f t="shared" ref="I8:I37" si="0">H8/G8</f>
         <v>0.27500000000000002</v>
       </c>
     </row>
     <row r="9" spans="2:9">
-      <c r="B9" s="152">
+      <c r="B9" s="150">
         <v>45076</v>
       </c>
-      <c r="C9" s="153" t="s">
+      <c r="C9" s="151" t="s">
         <v>119</v>
       </c>
-      <c r="D9" s="153" t="s">
+      <c r="D9" s="151" t="s">
         <v>120</v>
       </c>
-      <c r="E9" s="153" t="s">
+      <c r="E9" s="151" t="s">
         <v>117</v>
       </c>
-      <c r="F9" s="153"/>
-      <c r="G9" s="154">
+      <c r="F9" s="151"/>
+      <c r="G9" s="152">
         <v>3712.5</v>
       </c>
-      <c r="H9" s="154">
+      <c r="H9" s="152">
         <v>1009</v>
       </c>
-      <c r="I9" s="155">
+      <c r="I9" s="153">
         <f t="shared" si="0"/>
         <v>0.2717845117845118</v>
       </c>
     </row>
     <row r="10" spans="2:9">
-      <c r="B10" s="152">
+      <c r="B10" s="150">
         <v>45076</v>
       </c>
-      <c r="C10" s="153" t="s">
+      <c r="C10" s="151" t="s">
         <v>121</v>
       </c>
-      <c r="D10" s="153" t="s">
+      <c r="D10" s="151" t="s">
         <v>122</v>
       </c>
-      <c r="E10" s="153" t="s">
+      <c r="E10" s="151" t="s">
         <v>123</v>
       </c>
-      <c r="F10" s="153"/>
-      <c r="G10" s="154">
+      <c r="F10" s="151"/>
+      <c r="G10" s="152">
         <f>G9*1.5</f>
         <v>5568.75</v>
       </c>
-      <c r="H10" s="154">
+      <c r="H10" s="152">
         <v>779</v>
       </c>
-      <c r="I10" s="155">
+      <c r="I10" s="153">
         <f t="shared" si="0"/>
         <v>0.13988776655443322</v>
       </c>
     </row>
     <row r="11" spans="2:9">
-      <c r="B11" s="152">
+      <c r="B11" s="150">
         <v>45076</v>
       </c>
-      <c r="C11" s="153" t="s">
+      <c r="C11" s="151" t="s">
         <v>124</v>
       </c>
-      <c r="D11" s="153" t="s">
+      <c r="D11" s="151" t="s">
         <v>125</v>
       </c>
-      <c r="E11" s="153" t="s">
+      <c r="E11" s="151" t="s">
         <v>123</v>
       </c>
-      <c r="F11" s="153" t="s">
+      <c r="F11" s="151" t="s">
         <v>126</v>
       </c>
-      <c r="G11" s="154">
+      <c r="G11" s="152">
         <v>5000</v>
       </c>
-      <c r="H11" s="154">
+      <c r="H11" s="152">
         <v>684</v>
       </c>
-      <c r="I11" s="155">
+      <c r="I11" s="153">
         <f t="shared" si="0"/>
         <v>0.1368</v>
       </c>
     </row>
     <row r="12" spans="2:9">
-      <c r="B12" s="152">
+      <c r="B12" s="150">
         <v>45077</v>
       </c>
-      <c r="C12" s="153" t="s">
+      <c r="C12" s="151" t="s">
         <v>127</v>
       </c>
-      <c r="D12" s="153" t="s">
+      <c r="D12" s="151" t="s">
         <v>128</v>
       </c>
-      <c r="E12" s="153" t="s">
+      <c r="E12" s="151" t="s">
         <v>113</v>
       </c>
-      <c r="F12" s="153" t="s">
+      <c r="F12" s="151" t="s">
         <v>114</v>
       </c>
-      <c r="G12" s="154">
+      <c r="G12" s="152">
         <v>6100</v>
       </c>
-      <c r="H12" s="154">
+      <c r="H12" s="152">
         <v>544</v>
       </c>
-      <c r="I12" s="155">
+      <c r="I12" s="153">
         <f t="shared" si="0"/>
         <v>8.9180327868852466E-2</v>
       </c>
     </row>
     <row r="13" spans="2:9">
-      <c r="B13" s="152">
+      <c r="B13" s="150">
         <v>45077</v>
       </c>
-      <c r="C13" s="153" t="s">
+      <c r="C13" s="151" t="s">
         <v>129</v>
       </c>
-      <c r="D13" s="153" t="s">
+      <c r="D13" s="151" t="s">
         <v>130</v>
       </c>
-      <c r="E13" s="153" t="s">
+      <c r="E13" s="151" t="s">
         <v>113</v>
       </c>
-      <c r="F13" s="153" t="s">
+      <c r="F13" s="151" t="s">
         <v>114</v>
       </c>
-      <c r="G13" s="154">
+      <c r="G13" s="152">
         <v>4625</v>
       </c>
-      <c r="H13" s="154">
+      <c r="H13" s="152">
         <v>670</v>
       </c>
-      <c r="I13" s="155">
+      <c r="I13" s="153">
         <f t="shared" si="0"/>
         <v>0.14486486486486486</v>
       </c>
     </row>
     <row r="14" spans="2:9">
-      <c r="B14" s="152">
+      <c r="B14" s="150">
         <v>45077</v>
       </c>
-      <c r="C14" s="153" t="s">
+      <c r="C14" s="151" t="s">
         <v>131</v>
       </c>
-      <c r="D14" s="153" t="s">
+      <c r="D14" s="151" t="s">
         <v>132</v>
       </c>
-      <c r="E14" s="153" t="s">
+      <c r="E14" s="151" t="s">
         <v>113</v>
       </c>
-      <c r="F14" s="153" t="s">
+      <c r="F14" s="151" t="s">
         <v>114</v>
       </c>
-      <c r="G14" s="154">
+      <c r="G14" s="152">
         <v>3800</v>
       </c>
-      <c r="H14" s="154">
+      <c r="H14" s="152">
         <v>2045</v>
       </c>
-      <c r="I14" s="155">
+      <c r="I14" s="153">
         <f t="shared" si="0"/>
         <v>0.53815789473684206</v>
       </c>
     </row>
     <row r="15" spans="2:9">
-      <c r="B15" s="152">
+      <c r="B15" s="150">
         <v>45077</v>
       </c>
-      <c r="C15" s="153" t="s">
+      <c r="C15" s="151" t="s">
         <v>133</v>
       </c>
-      <c r="D15" s="153" t="s">
+      <c r="D15" s="151" t="s">
         <v>134</v>
       </c>
-      <c r="E15" s="153" t="s">
+      <c r="E15" s="151" t="s">
         <v>113</v>
       </c>
-      <c r="F15" s="153" t="s">
+      <c r="F15" s="151" t="s">
         <v>135</v>
       </c>
-      <c r="G15" s="154">
+      <c r="G15" s="152">
         <v>3600</v>
       </c>
-      <c r="H15" s="154">
+      <c r="H15" s="152">
         <v>1564</v>
       </c>
-      <c r="I15" s="155">
+      <c r="I15" s="153">
         <f t="shared" si="0"/>
         <v>0.43444444444444447</v>
       </c>
     </row>
     <row r="16" spans="2:9">
-      <c r="B16" s="152">
+      <c r="B16" s="150">
         <v>45077</v>
       </c>
-      <c r="C16" s="153" t="s">
+      <c r="C16" s="151" t="s">
         <v>136</v>
       </c>
-      <c r="D16" s="153" t="s">
+      <c r="D16" s="151" t="s">
         <v>137</v>
       </c>
-      <c r="E16" s="153" t="s">
+      <c r="E16" s="151" t="s">
         <v>113</v>
       </c>
-      <c r="F16" s="153" t="s">
+      <c r="F16" s="151" t="s">
         <v>126</v>
       </c>
-      <c r="G16" s="154">
+      <c r="G16" s="152">
         <v>5100</v>
       </c>
-      <c r="H16" s="154">
+      <c r="H16" s="152">
         <v>1220</v>
       </c>
-      <c r="I16" s="155">
+      <c r="I16" s="153">
         <f t="shared" si="0"/>
         <v>0.23921568627450981</v>
       </c>
     </row>
     <row r="17" spans="2:9">
-      <c r="B17" s="152">
+      <c r="B17" s="150">
         <v>45077</v>
       </c>
-      <c r="C17" s="153" t="s">
+      <c r="C17" s="151" t="s">
         <v>138</v>
       </c>
-      <c r="D17" s="153" t="s">
+      <c r="D17" s="151" t="s">
         <v>139</v>
       </c>
-      <c r="E17" s="153" t="s">
+      <c r="E17" s="151" t="s">
         <v>113</v>
       </c>
-      <c r="F17" s="153" t="s">
+      <c r="F17" s="151" t="s">
         <v>126</v>
       </c>
-      <c r="G17" s="154">
+      <c r="G17" s="152">
         <v>4750</v>
       </c>
-      <c r="H17" s="154">
+      <c r="H17" s="152">
         <v>1435</v>
       </c>
-      <c r="I17" s="155">
+      <c r="I17" s="153">
         <f t="shared" si="0"/>
         <v>0.30210526315789471</v>
       </c>
     </row>
     <row r="18" spans="2:9">
-      <c r="B18" s="152">
+      <c r="B18" s="150">
         <v>45077</v>
       </c>
-      <c r="C18" s="153" t="s">
+      <c r="C18" s="151" t="s">
         <v>140</v>
       </c>
-      <c r="D18" s="153" t="s">
+      <c r="D18" s="151" t="s">
         <v>141</v>
       </c>
-      <c r="E18" s="153" t="s">
+      <c r="E18" s="151" t="s">
         <v>123</v>
       </c>
-      <c r="F18" s="153" t="s">
+      <c r="F18" s="151" t="s">
         <v>114</v>
       </c>
-      <c r="G18" s="154">
+      <c r="G18" s="152">
         <v>6000</v>
       </c>
-      <c r="H18" s="154">
+      <c r="H18" s="152">
         <v>998</v>
       </c>
-      <c r="I18" s="155">
+      <c r="I18" s="153">
         <f t="shared" si="0"/>
         <v>0.16633333333333333</v>
       </c>
     </row>
     <row r="19" spans="2:9">
-      <c r="B19" s="152">
+      <c r="B19" s="150">
         <v>45077</v>
       </c>
-      <c r="C19" s="153" t="s">
+      <c r="C19" s="151" t="s">
         <v>142</v>
       </c>
-      <c r="D19" s="153" t="s">
+      <c r="D19" s="151" t="s">
         <v>143</v>
       </c>
-      <c r="E19" s="153" t="s">
+      <c r="E19" s="151" t="s">
         <v>144</v>
       </c>
-      <c r="F19" s="153" t="s">
+      <c r="F19" s="151" t="s">
         <v>126</v>
       </c>
-      <c r="G19" s="154">
+      <c r="G19" s="152">
         <v>4500</v>
       </c>
-      <c r="H19" s="154">
+      <c r="H19" s="152">
         <v>780</v>
       </c>
-      <c r="I19" s="155">
+      <c r="I19" s="153">
         <f t="shared" si="0"/>
         <v>0.17333333333333334</v>
       </c>
     </row>
     <row r="20" spans="2:9">
-      <c r="B20" s="152">
+      <c r="B20" s="150">
         <v>45078</v>
       </c>
-      <c r="C20" s="153" t="s">
+      <c r="C20" s="151" t="s">
         <v>145</v>
       </c>
-      <c r="D20" s="153" t="s">
+      <c r="D20" s="151" t="s">
         <v>146</v>
       </c>
-      <c r="E20" s="153" t="s">
+      <c r="E20" s="151" t="s">
         <v>144</v>
       </c>
-      <c r="F20" s="153" t="s">
+      <c r="F20" s="151" t="s">
         <v>135</v>
       </c>
-      <c r="G20" s="154">
+      <c r="G20" s="152">
         <f>G19*1.5</f>
         <v>6750</v>
       </c>
-      <c r="H20" s="154">
+      <c r="H20" s="152">
         <v>1044</v>
       </c>
-      <c r="I20" s="155">
+      <c r="I20" s="153">
         <f t="shared" si="0"/>
         <v>0.15466666666666667</v>
       </c>
     </row>
     <row r="21" spans="2:9">
-      <c r="B21" s="152">
+      <c r="B21" s="150">
         <v>45078</v>
       </c>
-      <c r="C21" s="153" t="s">
+      <c r="C21" s="151" t="s">
         <v>147</v>
       </c>
-      <c r="D21" s="153" t="s">
+      <c r="D21" s="151" t="s">
         <v>148</v>
       </c>
-      <c r="E21" s="153" t="s">
+      <c r="E21" s="151" t="s">
         <v>144</v>
       </c>
-      <c r="F21" s="153" t="s">
+      <c r="F21" s="151" t="s">
         <v>114</v>
       </c>
-      <c r="G21" s="154">
+      <c r="G21" s="152">
         <v>3712.5</v>
       </c>
-      <c r="H21" s="154">
+      <c r="H21" s="152">
         <v>1222</v>
       </c>
-      <c r="I21" s="155">
+      <c r="I21" s="153">
         <f t="shared" si="0"/>
         <v>0.32915824915824915</v>
       </c>
     </row>
     <row r="22" spans="2:9">
-      <c r="B22" s="152">
+      <c r="B22" s="150">
         <v>45078</v>
       </c>
-      <c r="C22" s="153" t="s">
+      <c r="C22" s="151" t="s">
         <v>149</v>
       </c>
-      <c r="D22" s="153" t="s">
+      <c r="D22" s="151" t="s">
         <v>150</v>
       </c>
-      <c r="E22" s="153" t="s">
+      <c r="E22" s="151" t="s">
         <v>144</v>
       </c>
-      <c r="F22" s="153" t="s">
+      <c r="F22" s="151" t="s">
         <v>114</v>
       </c>
-      <c r="G22" s="154">
+      <c r="G22" s="152">
         <v>4950</v>
       </c>
-      <c r="H22" s="154">
+      <c r="H22" s="152">
         <v>1065</v>
       </c>
-      <c r="I22" s="155">
+      <c r="I22" s="153">
         <f t="shared" si="0"/>
         <v>0.21515151515151515</v>
       </c>
     </row>
     <row r="23" spans="2:9">
-      <c r="B23" s="152">
+      <c r="B23" s="150">
         <v>45078</v>
       </c>
-      <c r="C23" s="153" t="s">
+      <c r="C23" s="151" t="s">
         <v>151</v>
       </c>
-      <c r="D23" s="153" t="s">
+      <c r="D23" s="151" t="s">
         <v>152</v>
       </c>
-      <c r="E23" s="153" t="s">
+      <c r="E23" s="151" t="s">
         <v>123</v>
       </c>
-      <c r="F23" s="153" t="s">
+      <c r="F23" s="151" t="s">
         <v>114</v>
       </c>
-      <c r="G23" s="154">
+      <c r="G23" s="152">
         <v>4750</v>
       </c>
-      <c r="H23" s="154">
+      <c r="H23" s="152">
         <v>810</v>
       </c>
-      <c r="I23" s="155">
+      <c r="I23" s="153">
         <f t="shared" si="0"/>
         <v>0.17052631578947369</v>
       </c>
     </row>
     <row r="24" spans="2:9">
-      <c r="B24" s="152">
+      <c r="B24" s="150">
         <v>45078</v>
       </c>
-      <c r="C24" s="153" t="s">
+      <c r="C24" s="151" t="s">
         <v>153</v>
       </c>
-      <c r="D24" s="153" t="s">
+      <c r="D24" s="151" t="s">
         <v>154</v>
       </c>
-      <c r="E24" s="153" t="s">
+      <c r="E24" s="151" t="s">
         <v>123</v>
       </c>
-      <c r="F24" s="153" t="s">
+      <c r="F24" s="151" t="s">
         <v>114</v>
       </c>
-      <c r="G24" s="154">
+      <c r="G24" s="152">
         <v>7320</v>
       </c>
-      <c r="H24" s="154">
+      <c r="H24" s="152">
         <v>933</v>
       </c>
-      <c r="I24" s="155">
+      <c r="I24" s="153">
         <f t="shared" si="0"/>
         <v>0.12745901639344262</v>
       </c>
     </row>
     <row r="25" spans="2:9">
-      <c r="B25" s="152">
+      <c r="B25" s="150">
         <v>45077</v>
       </c>
-      <c r="C25" s="153" t="s">
+      <c r="C25" s="151" t="s">
         <v>140</v>
       </c>
-      <c r="D25" s="153" t="s">
+      <c r="D25" s="151" t="s">
         <v>141</v>
       </c>
-      <c r="E25" s="153" t="s">
+      <c r="E25" s="151" t="s">
         <v>123</v>
       </c>
-      <c r="F25" s="153" t="s">
+      <c r="F25" s="151" t="s">
         <v>114</v>
       </c>
-      <c r="G25" s="154">
+      <c r="G25" s="152">
         <v>6000</v>
       </c>
-      <c r="H25" s="154">
+      <c r="H25" s="152">
         <v>998</v>
       </c>
-      <c r="I25" s="155">
+      <c r="I25" s="153">
         <f t="shared" si="0"/>
         <v>0.16633333333333333</v>
       </c>
     </row>
     <row r="26" spans="2:9">
-      <c r="B26" s="152">
+      <c r="B26" s="150">
         <v>45077</v>
       </c>
-      <c r="C26" s="153" t="s">
+      <c r="C26" s="151" t="s">
         <v>142</v>
       </c>
-      <c r="D26" s="153" t="s">
+      <c r="D26" s="151" t="s">
         <v>143</v>
       </c>
-      <c r="E26" s="153" t="s">
+      <c r="E26" s="151" t="s">
         <v>144</v>
       </c>
-      <c r="F26" s="153" t="s">
+      <c r="F26" s="151" t="s">
         <v>126</v>
       </c>
-      <c r="G26" s="154">
+      <c r="G26" s="152">
         <v>4500</v>
       </c>
-      <c r="H26" s="154">
+      <c r="H26" s="152">
         <v>780</v>
       </c>
-      <c r="I26" s="155">
+      <c r="I26" s="153">
         <f t="shared" si="0"/>
         <v>0.17333333333333334</v>
       </c>
     </row>
     <row r="27" spans="2:9">
-      <c r="B27" s="152">
+      <c r="B27" s="150">
         <v>45078</v>
       </c>
-      <c r="C27" s="153" t="s">
+      <c r="C27" s="151" t="s">
         <v>155</v>
       </c>
-      <c r="D27" s="153" t="s">
+      <c r="D27" s="151" t="s">
         <v>156</v>
       </c>
-      <c r="E27" s="153" t="s">
+      <c r="E27" s="151" t="s">
         <v>144</v>
       </c>
-      <c r="F27" s="153" t="s">
+      <c r="F27" s="151" t="s">
         <v>114</v>
       </c>
-      <c r="G27" s="154">
+      <c r="G27" s="152">
         <v>5087.5</v>
       </c>
-      <c r="H27" s="154">
+      <c r="H27" s="152">
         <v>655</v>
       </c>
-      <c r="I27" s="155">
+      <c r="I27" s="153">
         <f t="shared" si="0"/>
         <v>0.12874692874692875</v>
       </c>
     </row>
     <row r="28" spans="2:9">
-      <c r="B28" s="152">
+      <c r="B28" s="150">
         <v>45078</v>
       </c>
-      <c r="C28" s="153" t="s">
+      <c r="C28" s="151" t="s">
         <v>157</v>
       </c>
-      <c r="D28" s="153" t="s">
+      <c r="D28" s="151" t="s">
         <v>158</v>
       </c>
-      <c r="E28" s="153" t="s">
+      <c r="E28" s="151" t="s">
         <v>144</v>
       </c>
-      <c r="F28" s="153" t="s">
+      <c r="F28" s="151" t="s">
         <v>114</v>
       </c>
-      <c r="G28" s="154">
+      <c r="G28" s="152">
         <v>4500</v>
       </c>
-      <c r="H28" s="154">
+      <c r="H28" s="152">
         <v>722</v>
       </c>
-      <c r="I28" s="155">
+      <c r="I28" s="153">
         <f t="shared" si="0"/>
         <v>0.16044444444444445</v>
       </c>
     </row>
     <row r="29" spans="2:9">
-      <c r="B29" s="152">
+      <c r="B29" s="150">
         <v>45078</v>
       </c>
-      <c r="C29" s="153" t="s">
+      <c r="C29" s="151" t="s">
         <v>159</v>
       </c>
-      <c r="D29" s="153" t="s">
+      <c r="D29" s="151" t="s">
         <v>160</v>
       </c>
-      <c r="E29" s="153" t="s">
+      <c r="E29" s="151" t="s">
         <v>144</v>
       </c>
-      <c r="F29" s="153" t="s">
+      <c r="F29" s="151" t="s">
         <v>135</v>
       </c>
-      <c r="G29" s="154">
+      <c r="G29" s="152">
         <v>4250</v>
       </c>
-      <c r="H29" s="154">
+      <c r="H29" s="152">
         <v>901</v>
       </c>
-      <c r="I29" s="155">
+      <c r="I29" s="153">
         <f t="shared" si="0"/>
         <v>0.21199999999999999</v>
       </c>
     </row>
     <row r="30" spans="2:9">
-      <c r="B30" s="152">
+      <c r="B30" s="150">
         <v>45079</v>
       </c>
-      <c r="C30" s="153" t="s">
+      <c r="C30" s="151" t="s">
         <v>161</v>
       </c>
-      <c r="D30" s="153" t="s">
+      <c r="D30" s="151" t="s">
         <v>162</v>
       </c>
-      <c r="E30" s="153" t="s">
+      <c r="E30" s="151" t="s">
         <v>144</v>
       </c>
-      <c r="F30" s="153" t="s">
+      <c r="F30" s="151" t="s">
         <v>118</v>
       </c>
-      <c r="G30" s="154">
+      <c r="G30" s="152">
         <v>5250</v>
       </c>
-      <c r="H30" s="154">
+      <c r="H30" s="152">
         <v>1349</v>
       </c>
-      <c r="I30" s="155">
+      <c r="I30" s="153">
         <f t="shared" si="0"/>
         <v>0.25695238095238093</v>
       </c>
     </row>
     <row r="31" spans="2:9">
-      <c r="B31" s="152">
+      <c r="B31" s="150">
         <v>45079</v>
       </c>
-      <c r="C31" s="153" t="s">
+      <c r="C31" s="151" t="s">
         <v>163</v>
       </c>
-      <c r="D31" s="153" t="s">
+      <c r="D31" s="151" t="s">
         <v>164</v>
       </c>
-      <c r="E31" s="153" t="s">
+      <c r="E31" s="151" t="s">
         <v>117</v>
       </c>
-      <c r="F31" s="153" t="s">
+      <c r="F31" s="151" t="s">
         <v>118</v>
       </c>
-      <c r="G31" s="154">
+      <c r="G31" s="152">
         <v>6500</v>
       </c>
-      <c r="H31" s="154">
+      <c r="H31" s="152">
         <v>1288</v>
       </c>
-      <c r="I31" s="155">
+      <c r="I31" s="153">
         <f t="shared" si="0"/>
         <v>0.19815384615384615</v>
       </c>
     </row>
     <row r="32" spans="2:9">
-      <c r="B32" s="152">
+      <c r="B32" s="150">
         <v>45079</v>
       </c>
-      <c r="C32" s="153" t="s">
+      <c r="C32" s="151" t="s">
         <v>165</v>
       </c>
-      <c r="D32" s="153" t="s">
+      <c r="D32" s="151" t="s">
         <v>166</v>
       </c>
-      <c r="E32" s="153" t="s">
+      <c r="E32" s="151" t="s">
         <v>117</v>
       </c>
-      <c r="F32" s="153" t="s">
+      <c r="F32" s="151" t="s">
         <v>118</v>
       </c>
-      <c r="G32" s="154">
+      <c r="G32" s="152">
         <v>7500</v>
       </c>
-      <c r="H32" s="154">
+      <c r="H32" s="152">
         <v>1664</v>
       </c>
-      <c r="I32" s="155">
+      <c r="I32" s="153">
         <f t="shared" si="0"/>
         <v>0.22186666666666666</v>
       </c>
     </row>
     <row r="33" spans="2:9">
-      <c r="B33" s="152">
+      <c r="B33" s="150">
         <v>45079</v>
       </c>
-      <c r="C33" s="153" t="s">
+      <c r="C33" s="151" t="s">
         <v>167</v>
       </c>
-      <c r="D33" s="153" t="s">
+      <c r="D33" s="151" t="s">
         <v>168</v>
       </c>
-      <c r="E33" s="153" t="s">
+      <c r="E33" s="151" t="s">
         <v>117</v>
       </c>
-      <c r="F33" s="153" t="s">
+      <c r="F33" s="151" t="s">
         <v>114</v>
       </c>
-      <c r="G33" s="154">
+      <c r="G33" s="152">
         <v>5500</v>
       </c>
-      <c r="H33" s="154">
+      <c r="H33" s="152">
         <v>1320</v>
       </c>
-      <c r="I33" s="155">
+      <c r="I33" s="153">
         <f t="shared" si="0"/>
         <v>0.24</v>
       </c>
     </row>
     <row r="34" spans="2:9">
-      <c r="B34" s="152">
+      <c r="B34" s="150">
         <v>45079</v>
       </c>
-      <c r="C34" s="153" t="s">
+      <c r="C34" s="151" t="s">
         <v>169</v>
       </c>
-      <c r="D34" s="153" t="s">
+      <c r="D34" s="151" t="s">
         <v>170</v>
       </c>
-      <c r="E34" s="153" t="s">
+      <c r="E34" s="151" t="s">
         <v>117</v>
       </c>
-      <c r="F34" s="153" t="s">
+      <c r="F34" s="151" t="s">
         <v>114</v>
       </c>
-      <c r="G34" s="154">
+      <c r="G34" s="152">
         <v>4625</v>
       </c>
-      <c r="H34" s="154">
+      <c r="H34" s="152">
         <v>1001</v>
       </c>
-      <c r="I34" s="155">
+      <c r="I34" s="153">
         <f t="shared" si="0"/>
         <v>0.21643243243243243</v>
       </c>
     </row>
     <row r="35" spans="2:9">
-      <c r="B35" s="152">
+      <c r="B35" s="150">
         <v>45079</v>
       </c>
-      <c r="C35" s="153" t="s">
+      <c r="C35" s="151" t="s">
         <v>171</v>
       </c>
-      <c r="D35" s="153" t="s">
+      <c r="D35" s="151" t="s">
         <v>172</v>
       </c>
-      <c r="E35" s="153" t="s">
+      <c r="E35" s="151" t="s">
         <v>117</v>
       </c>
-      <c r="F35" s="153" t="s">
+      <c r="F35" s="151" t="s">
         <v>114</v>
       </c>
-      <c r="G35" s="154">
+      <c r="G35" s="152">
         <v>4500</v>
       </c>
-      <c r="H35" s="154">
+      <c r="H35" s="152">
         <v>960</v>
       </c>
-      <c r="I35" s="155">
+      <c r="I35" s="153">
         <f t="shared" si="0"/>
         <v>0.21333333333333335</v>
       </c>
     </row>
     <row r="36" spans="2:9">
-      <c r="B36" s="152">
+      <c r="B36" s="150">
         <v>45079</v>
       </c>
-      <c r="C36" s="153" t="s">
+      <c r="C36" s="151" t="s">
         <v>173</v>
       </c>
-      <c r="D36" s="153" t="s">
+      <c r="D36" s="151" t="s">
         <v>174</v>
       </c>
-      <c r="E36" s="153" t="s">
+      <c r="E36" s="151" t="s">
         <v>117</v>
       </c>
-      <c r="F36" s="153" t="s">
+      <c r="F36" s="151" t="s">
         <v>135</v>
       </c>
-      <c r="G36" s="154">
+      <c r="G36" s="152">
         <v>5400</v>
       </c>
-      <c r="H36" s="154">
+      <c r="H36" s="152">
         <v>540</v>
       </c>
-      <c r="I36" s="155">
+      <c r="I36" s="153">
         <f t="shared" si="0"/>
         <v>0.1</v>
       </c>
     </row>
     <row r="37" spans="2:9">
-      <c r="B37" s="152">
+      <c r="B37" s="150">
         <v>45076</v>
       </c>
-      <c r="C37" s="153" t="s">
+      <c r="C37" s="151" t="s">
         <v>124</v>
       </c>
-      <c r="D37" s="153" t="s">
+      <c r="D37" s="151" t="s">
         <v>125</v>
       </c>
-      <c r="E37" s="153" t="s">
+      <c r="E37" s="151" t="s">
         <v>123</v>
       </c>
-      <c r="F37" s="153" t="s">
+      <c r="F37" s="151" t="s">
         <v>126</v>
       </c>
-      <c r="G37" s="154">
+      <c r="G37" s="152">
         <v>5000</v>
       </c>
-      <c r="H37" s="154">
+      <c r="H37" s="152">
         <v>684</v>
       </c>
-      <c r="I37" s="155">
+      <c r="I37" s="153">
         <f t="shared" si="0"/>
         <v>0.1368</v>
       </c>
@@ -8967,7 +9072,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="I7:I37">
-    <cfRule type="cellIs" dxfId="1" priority="1" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="7" priority="1" operator="greaterThan">
       <formula>0.1</formula>
     </cfRule>
   </conditionalFormatting>
@@ -9149,7 +9254,7 @@
       </c>
     </row>
     <row r="4" spans="2:3">
-      <c r="C4" s="115">
+      <c r="C4" s="113">
         <f>SUM(COGS:NonOpExp!B4:B14)</f>
         <v>302882</v>
       </c>
@@ -10335,6 +10440,7 @@
     <col min="4" max="4" width="27.453125" customWidth="1"/>
     <col min="5" max="5" width="14.54296875" customWidth="1"/>
     <col min="7" max="7" width="10.81640625" customWidth="1"/>
+    <col min="10" max="10" width="53.81640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8">
@@ -10426,7 +10532,10 @@
       <c r="C12" s="100" t="s">
         <v>287</v>
       </c>
-      <c r="D12" s="101"/>
+      <c r="D12" s="101" t="b">
+        <f t="shared" ref="D12:D43" si="0">ISNUMBER(MATCH(C12,$A$12:$A$104,0))</f>
+        <v>1</v>
+      </c>
     </row>
     <row r="13" spans="1:8">
       <c r="A13" s="100" t="s">
@@ -10435,7 +10544,10 @@
       <c r="C13" s="100" t="s">
         <v>289</v>
       </c>
-      <c r="D13" s="101"/>
+      <c r="D13" s="101" t="b">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
     </row>
     <row r="14" spans="1:8">
       <c r="A14" s="100" t="s">
@@ -10444,7 +10556,10 @@
       <c r="C14" s="100" t="s">
         <v>286</v>
       </c>
-      <c r="D14" s="101"/>
+      <c r="D14" s="101" t="b">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
     </row>
     <row r="15" spans="1:8">
       <c r="A15" s="100" t="s">
@@ -10453,7 +10568,10 @@
       <c r="C15" s="100" t="s">
         <v>292</v>
       </c>
-      <c r="D15" s="101"/>
+      <c r="D15" s="101" t="b">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
     </row>
     <row r="16" spans="1:8">
       <c r="A16" s="100" t="s">
@@ -10462,7 +10580,10 @@
       <c r="C16" s="100" t="s">
         <v>294</v>
       </c>
-      <c r="D16" s="101"/>
+      <c r="D16" s="101" t="b">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
     </row>
     <row r="17" spans="1:4">
       <c r="A17" s="100" t="s">
@@ -10471,7 +10592,10 @@
       <c r="C17" s="100" t="s">
         <v>295</v>
       </c>
-      <c r="D17" s="101"/>
+      <c r="D17" s="101" t="b">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
     </row>
     <row r="18" spans="1:4">
       <c r="A18" s="100" t="s">
@@ -10480,7 +10604,10 @@
       <c r="C18" s="100" t="s">
         <v>297</v>
       </c>
-      <c r="D18" s="101"/>
+      <c r="D18" s="101" t="b">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
     </row>
     <row r="19" spans="1:4">
       <c r="A19" s="100" t="s">
@@ -10489,7 +10616,10 @@
       <c r="C19" s="100" t="s">
         <v>299</v>
       </c>
-      <c r="D19" s="101"/>
+      <c r="D19" s="101" t="b">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
     </row>
     <row r="20" spans="1:4">
       <c r="A20" s="100" t="s">
@@ -10498,7 +10628,10 @@
       <c r="C20" s="100" t="s">
         <v>301</v>
       </c>
-      <c r="D20" s="101"/>
+      <c r="D20" s="101" t="b">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
     </row>
     <row r="21" spans="1:4">
       <c r="A21" s="100" t="s">
@@ -10507,7 +10640,10 @@
       <c r="C21" s="100" t="s">
         <v>303</v>
       </c>
-      <c r="D21" s="101"/>
+      <c r="D21" s="101" t="b">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
     </row>
     <row r="22" spans="1:4">
       <c r="A22" s="100" t="s">
@@ -10516,7 +10652,10 @@
       <c r="C22" s="100" t="s">
         <v>305</v>
       </c>
-      <c r="D22" s="101"/>
+      <c r="D22" s="101" t="b">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
     </row>
     <row r="23" spans="1:4">
       <c r="A23" s="100" t="s">
@@ -10525,7 +10664,10 @@
       <c r="C23" s="100" t="s">
         <v>307</v>
       </c>
-      <c r="D23" s="101"/>
+      <c r="D23" s="101" t="b">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
     </row>
     <row r="24" spans="1:4">
       <c r="A24" s="100" t="s">
@@ -10534,7 +10676,10 @@
       <c r="C24" s="100" t="s">
         <v>309</v>
       </c>
-      <c r="D24" s="101"/>
+      <c r="D24" s="101" t="b">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
     </row>
     <row r="25" spans="1:4">
       <c r="A25" s="100" t="s">
@@ -10543,7 +10688,10 @@
       <c r="C25" s="100" t="s">
         <v>311</v>
       </c>
-      <c r="D25" s="101"/>
+      <c r="D25" s="101" t="b">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
     </row>
     <row r="26" spans="1:4">
       <c r="A26" s="100" t="s">
@@ -10552,7 +10700,10 @@
       <c r="C26" s="100" t="s">
         <v>313</v>
       </c>
-      <c r="D26" s="101"/>
+      <c r="D26" s="101" t="b">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
     </row>
     <row r="27" spans="1:4">
       <c r="A27" s="100" t="s">
@@ -10561,7 +10712,10 @@
       <c r="C27" s="100" t="s">
         <v>312</v>
       </c>
-      <c r="D27" s="101"/>
+      <c r="D27" s="101" t="b">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
     </row>
     <row r="28" spans="1:4">
       <c r="A28" s="100" t="s">
@@ -10570,7 +10724,10 @@
       <c r="C28" s="100" t="s">
         <v>316</v>
       </c>
-      <c r="D28" s="101"/>
+      <c r="D28" s="101" t="b">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
     </row>
     <row r="29" spans="1:4">
       <c r="A29" s="100" t="s">
@@ -10579,7 +10736,10 @@
       <c r="C29" s="100" t="s">
         <v>318</v>
       </c>
-      <c r="D29" s="101"/>
+      <c r="D29" s="101" t="b">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
     </row>
     <row r="30" spans="1:4">
       <c r="A30" s="100" t="s">
@@ -10588,7 +10748,10 @@
       <c r="C30" s="100" t="s">
         <v>320</v>
       </c>
-      <c r="D30" s="101"/>
+      <c r="D30" s="101" t="b">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
     </row>
     <row r="31" spans="1:4">
       <c r="A31" s="100" t="s">
@@ -10597,7 +10760,10 @@
       <c r="C31" s="100" t="s">
         <v>322</v>
       </c>
-      <c r="D31" s="101"/>
+      <c r="D31" s="101" t="b">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
     </row>
     <row r="32" spans="1:4">
       <c r="A32" s="100" t="s">
@@ -10606,7 +10772,10 @@
       <c r="C32" s="100" t="s">
         <v>324</v>
       </c>
-      <c r="D32" s="101"/>
+      <c r="D32" s="101" t="b">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
     </row>
     <row r="33" spans="1:4">
       <c r="A33" s="100" t="s">
@@ -10615,7 +10784,10 @@
       <c r="C33" s="100" t="s">
         <v>300</v>
       </c>
-      <c r="D33" s="101"/>
+      <c r="D33" s="101" t="b">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
     </row>
     <row r="34" spans="1:4">
       <c r="A34" s="100" t="s">
@@ -10624,7 +10796,10 @@
       <c r="C34" s="100" t="s">
         <v>325</v>
       </c>
-      <c r="D34" s="101"/>
+      <c r="D34" s="101" t="b">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
     </row>
     <row r="35" spans="1:4">
       <c r="A35" s="100" t="s">
@@ -10633,7 +10808,10 @@
       <c r="C35" s="100" t="s">
         <v>327</v>
       </c>
-      <c r="D35" s="101"/>
+      <c r="D35" s="101" t="b">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
     </row>
     <row r="36" spans="1:4">
       <c r="A36" s="100" t="s">
@@ -10642,7 +10820,10 @@
       <c r="C36" s="100" t="s">
         <v>291</v>
       </c>
-      <c r="D36" s="101"/>
+      <c r="D36" s="101" t="b">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
     </row>
     <row r="37" spans="1:4">
       <c r="A37" s="100" t="s">
@@ -10651,7 +10832,10 @@
       <c r="C37" s="100" t="s">
         <v>298</v>
       </c>
-      <c r="D37" s="101"/>
+      <c r="D37" s="101" t="b">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
     </row>
     <row r="38" spans="1:4">
       <c r="A38" s="100" t="s">
@@ -10660,7 +10844,10 @@
       <c r="C38" s="100" t="s">
         <v>330</v>
       </c>
-      <c r="D38" s="101"/>
+      <c r="D38" s="101" t="b">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
     </row>
     <row r="39" spans="1:4">
       <c r="A39" s="100" t="s">
@@ -10669,7 +10856,10 @@
       <c r="C39" s="100" t="s">
         <v>332</v>
       </c>
-      <c r="D39" s="101"/>
+      <c r="D39" s="101" t="b">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
     </row>
     <row r="40" spans="1:4">
       <c r="A40" s="100" t="s">
@@ -10678,7 +10868,10 @@
       <c r="C40" s="100" t="s">
         <v>334</v>
       </c>
-      <c r="D40" s="101"/>
+      <c r="D40" s="101" t="b">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
     </row>
     <row r="41" spans="1:4">
       <c r="A41" s="100" t="s">
@@ -10687,7 +10880,10 @@
       <c r="C41" s="100" t="s">
         <v>336</v>
       </c>
-      <c r="D41" s="101"/>
+      <c r="D41" s="101" t="b">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
     </row>
     <row r="42" spans="1:4">
       <c r="A42" s="100" t="s">
@@ -10696,7 +10892,10 @@
       <c r="C42" s="100" t="s">
         <v>338</v>
       </c>
-      <c r="D42" s="101"/>
+      <c r="D42" s="101" t="b">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
     </row>
     <row r="43" spans="1:4">
       <c r="A43" s="100" t="s">
@@ -10705,7 +10904,10 @@
       <c r="C43" s="100" t="s">
         <v>340</v>
       </c>
-      <c r="D43" s="101"/>
+      <c r="D43" s="101" t="b">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
     </row>
     <row r="44" spans="1:4">
       <c r="A44" s="100" t="s">
@@ -10714,7 +10916,10 @@
       <c r="C44" s="100" t="s">
         <v>328</v>
       </c>
-      <c r="D44" s="101"/>
+      <c r="D44" s="101" t="b">
+        <f t="shared" ref="D44:D75" si="1">ISNUMBER(MATCH(C44,$A$12:$A$104,0))</f>
+        <v>1</v>
+      </c>
     </row>
     <row r="45" spans="1:4">
       <c r="A45" s="100" t="s">
@@ -10723,7 +10928,10 @@
       <c r="C45" s="100" t="s">
         <v>342</v>
       </c>
-      <c r="D45" s="101"/>
+      <c r="D45" s="101" t="b">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
     </row>
     <row r="46" spans="1:4">
       <c r="A46" s="100" t="s">
@@ -10732,7 +10940,10 @@
       <c r="C46" s="100" t="s">
         <v>344</v>
       </c>
-      <c r="D46" s="101"/>
+      <c r="D46" s="101" t="b">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
     </row>
     <row r="47" spans="1:4">
       <c r="A47" s="100" t="s">
@@ -10741,7 +10952,10 @@
       <c r="C47" s="100" t="s">
         <v>345</v>
       </c>
-      <c r="D47" s="101"/>
+      <c r="D47" s="101" t="b">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
     </row>
     <row r="48" spans="1:4">
       <c r="A48" s="100" t="s">
@@ -10750,7 +10964,10 @@
       <c r="C48" s="100" t="s">
         <v>347</v>
       </c>
-      <c r="D48" s="101"/>
+      <c r="D48" s="101" t="b">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
     </row>
     <row r="49" spans="1:4">
       <c r="A49" s="100" t="s">
@@ -10759,7 +10976,10 @@
       <c r="C49" s="100" t="s">
         <v>349</v>
       </c>
-      <c r="D49" s="101"/>
+      <c r="D49" s="101" t="b">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
     </row>
     <row r="50" spans="1:4">
       <c r="A50" s="100" t="s">
@@ -10768,7 +10988,10 @@
       <c r="C50" s="100" t="s">
         <v>304</v>
       </c>
-      <c r="D50" s="101"/>
+      <c r="D50" s="101" t="b">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
     </row>
     <row r="51" spans="1:4">
       <c r="A51" s="100" t="s">
@@ -10777,7 +11000,10 @@
       <c r="C51" s="100" t="s">
         <v>351</v>
       </c>
-      <c r="D51" s="101"/>
+      <c r="D51" s="101" t="b">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
     </row>
     <row r="52" spans="1:4">
       <c r="A52" s="100" t="s">
@@ -10786,7 +11012,10 @@
       <c r="C52" s="100" t="s">
         <v>352</v>
       </c>
-      <c r="D52" s="101"/>
+      <c r="D52" s="101" t="b">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
     </row>
     <row r="53" spans="1:4">
       <c r="A53" s="100" t="s">
@@ -10795,7 +11024,10 @@
       <c r="C53" s="100" t="s">
         <v>354</v>
       </c>
-      <c r="D53" s="101"/>
+      <c r="D53" s="101" t="b">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
     </row>
     <row r="54" spans="1:4">
       <c r="A54" s="100" t="s">
@@ -10804,7 +11036,10 @@
       <c r="C54" s="100" t="s">
         <v>302</v>
       </c>
-      <c r="D54" s="101"/>
+      <c r="D54" s="101" t="b">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
     </row>
     <row r="55" spans="1:4">
       <c r="A55" s="100" t="s">
@@ -10813,7 +11048,10 @@
       <c r="C55" s="100" t="s">
         <v>355</v>
       </c>
-      <c r="D55" s="101"/>
+      <c r="D55" s="101" t="b">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
     </row>
     <row r="56" spans="1:4">
       <c r="A56" s="100" t="s">
@@ -10822,7 +11060,10 @@
       <c r="C56" s="100" t="s">
         <v>293</v>
       </c>
-      <c r="D56" s="101"/>
+      <c r="D56" s="101" t="b">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
     </row>
     <row r="57" spans="1:4">
       <c r="A57" s="100" t="s">
@@ -10831,7 +11072,10 @@
       <c r="C57" s="100" t="s">
         <v>356</v>
       </c>
-      <c r="D57" s="101"/>
+      <c r="D57" s="101" t="b">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
     </row>
     <row r="58" spans="1:4">
       <c r="A58" s="100" t="s">
@@ -10840,7 +11084,10 @@
       <c r="C58" s="100" t="s">
         <v>326</v>
       </c>
-      <c r="D58" s="101"/>
+      <c r="D58" s="101" t="b">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
     </row>
     <row r="59" spans="1:4">
       <c r="A59" s="100" t="s">
@@ -10849,7 +11096,10 @@
       <c r="C59" s="100" t="s">
         <v>357</v>
       </c>
-      <c r="D59" s="101"/>
+      <c r="D59" s="101" t="b">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
     </row>
     <row r="60" spans="1:4">
       <c r="A60" s="100" t="s">
@@ -10858,7 +11108,10 @@
       <c r="C60" s="100" t="s">
         <v>308</v>
       </c>
-      <c r="D60" s="101"/>
+      <c r="D60" s="101" t="b">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
     </row>
     <row r="61" spans="1:4">
       <c r="A61" s="100" t="s">
@@ -10867,7 +11120,10 @@
       <c r="C61" s="100" t="s">
         <v>350</v>
       </c>
-      <c r="D61" s="101"/>
+      <c r="D61" s="101" t="b">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
     </row>
     <row r="62" spans="1:4">
       <c r="A62" s="100" t="s">
@@ -10876,7 +11132,10 @@
       <c r="C62" s="100" t="s">
         <v>360</v>
       </c>
-      <c r="D62" s="101"/>
+      <c r="D62" s="101" t="b">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
     </row>
     <row r="63" spans="1:4">
       <c r="A63" s="100" t="s">
@@ -10885,7 +11144,10 @@
       <c r="C63" s="100" t="s">
         <v>362</v>
       </c>
-      <c r="D63" s="101"/>
+      <c r="D63" s="101" t="b">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
     </row>
     <row r="64" spans="1:4">
       <c r="A64" s="100" t="s">
@@ -10894,7 +11156,10 @@
       <c r="C64" s="100" t="s">
         <v>337</v>
       </c>
-      <c r="D64" s="101"/>
+      <c r="D64" s="101" t="b">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
     </row>
     <row r="65" spans="1:4">
       <c r="A65" s="100" t="s">
@@ -10903,7 +11168,10 @@
       <c r="C65" s="100" t="s">
         <v>364</v>
       </c>
-      <c r="D65" s="101"/>
+      <c r="D65" s="101" t="b">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
     </row>
     <row r="66" spans="1:4">
       <c r="A66" s="100" t="s">
@@ -10912,7 +11180,10 @@
       <c r="C66" s="100" t="s">
         <v>358</v>
       </c>
-      <c r="D66" s="101"/>
+      <c r="D66" s="101" t="b">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
     </row>
     <row r="67" spans="1:4">
       <c r="A67" s="100" t="s">
@@ -10921,7 +11192,10 @@
       <c r="C67" s="100" t="s">
         <v>367</v>
       </c>
-      <c r="D67" s="101"/>
+      <c r="D67" s="101" t="b">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
     </row>
     <row r="68" spans="1:4">
       <c r="A68" s="100" t="s">
@@ -10930,7 +11204,10 @@
       <c r="C68" s="100" t="s">
         <v>314</v>
       </c>
-      <c r="D68" s="101"/>
+      <c r="D68" s="101" t="b">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
     </row>
     <row r="69" spans="1:4">
       <c r="A69" s="100" t="s">
@@ -10939,7 +11216,10 @@
       <c r="C69" s="100" t="s">
         <v>321</v>
       </c>
-      <c r="D69" s="101"/>
+      <c r="D69" s="101" t="b">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
     </row>
     <row r="70" spans="1:4">
       <c r="A70" s="100" t="s">
@@ -10948,7 +11228,10 @@
       <c r="C70" s="100" t="s">
         <v>288</v>
       </c>
-      <c r="D70" s="101"/>
+      <c r="D70" s="101" t="b">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
     </row>
     <row r="71" spans="1:4">
       <c r="A71" s="100" t="s">
@@ -10957,7 +11240,10 @@
       <c r="C71" s="100" t="s">
         <v>361</v>
       </c>
-      <c r="D71" s="101"/>
+      <c r="D71" s="101" t="b">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
     </row>
     <row r="72" spans="1:4">
       <c r="A72" s="100" t="s">
@@ -10966,7 +11252,10 @@
       <c r="C72" s="100" t="s">
         <v>359</v>
       </c>
-      <c r="D72" s="101"/>
+      <c r="D72" s="101" t="b">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
     </row>
     <row r="73" spans="1:4">
       <c r="A73" s="100" t="s">
@@ -10975,7 +11264,10 @@
       <c r="C73" s="100" t="s">
         <v>335</v>
       </c>
-      <c r="D73" s="101"/>
+      <c r="D73" s="101" t="b">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
     </row>
     <row r="74" spans="1:4">
       <c r="A74" s="100" t="s">
@@ -10984,7 +11276,10 @@
       <c r="C74" s="100" t="s">
         <v>323</v>
       </c>
-      <c r="D74" s="101"/>
+      <c r="D74" s="101" t="b">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
     </row>
     <row r="75" spans="1:4">
       <c r="A75" s="100" t="s">
@@ -10993,7 +11288,10 @@
       <c r="C75" s="100" t="s">
         <v>371</v>
       </c>
-      <c r="D75" s="101"/>
+      <c r="D75" s="101" t="b">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
     </row>
     <row r="76" spans="1:4">
       <c r="A76" s="100" t="s">
@@ -11002,7 +11300,10 @@
       <c r="C76" s="100" t="s">
         <v>365</v>
       </c>
-      <c r="D76" s="101"/>
+      <c r="D76" s="101" t="b">
+        <f t="shared" ref="D76:D107" si="2">ISNUMBER(MATCH(C76,$A$12:$A$104,0))</f>
+        <v>1</v>
+      </c>
     </row>
     <row r="77" spans="1:4">
       <c r="A77" s="100" t="s">
@@ -11011,7 +11312,10 @@
       <c r="C77" s="100" t="s">
         <v>348</v>
       </c>
-      <c r="D77" s="101"/>
+      <c r="D77" s="101" t="b">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
     </row>
     <row r="78" spans="1:4">
       <c r="A78" s="100" t="s">
@@ -11020,7 +11324,10 @@
       <c r="C78" s="100" t="s">
         <v>374</v>
       </c>
-      <c r="D78" s="101"/>
+      <c r="D78" s="101" t="b">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
     </row>
     <row r="79" spans="1:4">
       <c r="A79" s="100" t="s">
@@ -11029,7 +11336,10 @@
       <c r="C79" s="100" t="s">
         <v>331</v>
       </c>
-      <c r="D79" s="101"/>
+      <c r="D79" s="101" t="b">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
     </row>
     <row r="80" spans="1:4">
       <c r="A80" s="100" t="s">
@@ -11038,7 +11348,10 @@
       <c r="C80" s="100" t="s">
         <v>373</v>
       </c>
-      <c r="D80" s="101"/>
+      <c r="D80" s="101" t="b">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
     </row>
     <row r="81" spans="1:4">
       <c r="A81" s="100" t="s">
@@ -11047,7 +11360,10 @@
       <c r="C81" s="100" t="s">
         <v>306</v>
       </c>
-      <c r="D81" s="101"/>
+      <c r="D81" s="101" t="b">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
     </row>
     <row r="82" spans="1:4">
       <c r="A82" s="100" t="s">
@@ -11056,7 +11372,10 @@
       <c r="C82" s="100" t="s">
         <v>369</v>
       </c>
-      <c r="D82" s="101"/>
+      <c r="D82" s="101" t="b">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
     </row>
     <row r="83" spans="1:4">
       <c r="A83" s="100" t="s">
@@ -11065,7 +11384,10 @@
       <c r="C83" s="100" t="s">
         <v>377</v>
       </c>
-      <c r="D83" s="101"/>
+      <c r="D83" s="101" t="b">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
     </row>
     <row r="84" spans="1:4">
       <c r="A84" s="100" t="s">
@@ -11074,7 +11396,10 @@
       <c r="C84" s="100" t="s">
         <v>376</v>
       </c>
-      <c r="D84" s="101"/>
+      <c r="D84" s="101" t="b">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
     </row>
     <row r="85" spans="1:4">
       <c r="A85" s="100" t="s">
@@ -11083,7 +11408,10 @@
       <c r="C85" s="100" t="s">
         <v>353</v>
       </c>
-      <c r="D85" s="101"/>
+      <c r="D85" s="101" t="b">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
     </row>
     <row r="86" spans="1:4">
       <c r="A86" s="100" t="s">
@@ -11092,7 +11420,10 @@
       <c r="C86" s="100" t="s">
         <v>333</v>
       </c>
-      <c r="D86" s="101"/>
+      <c r="D86" s="101" t="b">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
     </row>
     <row r="87" spans="1:4">
       <c r="A87" s="100" t="s">
@@ -11101,7 +11432,10 @@
       <c r="C87" s="100" t="s">
         <v>366</v>
       </c>
-      <c r="D87" s="101"/>
+      <c r="D87" s="101" t="b">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
     </row>
     <row r="88" spans="1:4">
       <c r="A88" s="100" t="s">
@@ -11110,7 +11444,10 @@
       <c r="C88" s="100" t="s">
         <v>290</v>
       </c>
-      <c r="D88" s="101"/>
+      <c r="D88" s="101" t="b">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
     </row>
     <row r="89" spans="1:4">
       <c r="A89" s="100" t="s">
@@ -11119,7 +11456,10 @@
       <c r="C89" s="100" t="s">
         <v>319</v>
       </c>
-      <c r="D89" s="101"/>
+      <c r="D89" s="101" t="b">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
     </row>
     <row r="90" spans="1:4">
       <c r="A90" s="100" t="s">
@@ -11128,7 +11468,10 @@
       <c r="C90" s="100" t="s">
         <v>310</v>
       </c>
-      <c r="D90" s="101"/>
+      <c r="D90" s="101" t="b">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
     </row>
     <row r="91" spans="1:4">
       <c r="A91" s="100" t="s">
@@ -11137,7 +11480,10 @@
       <c r="C91" s="100" t="s">
         <v>296</v>
       </c>
-      <c r="D91" s="101"/>
+      <c r="D91" s="101" t="b">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
     </row>
     <row r="92" spans="1:4">
       <c r="A92" s="100" t="s">
@@ -11146,7 +11492,10 @@
       <c r="C92" s="100" t="s">
         <v>339</v>
       </c>
-      <c r="D92" s="101"/>
+      <c r="D92" s="101" t="b">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
     </row>
     <row r="93" spans="1:4">
       <c r="A93" s="100" t="s">
@@ -11155,7 +11504,10 @@
       <c r="C93" s="100" t="s">
         <v>382</v>
       </c>
-      <c r="D93" s="101"/>
+      <c r="D93" s="101" t="b">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
     </row>
     <row r="94" spans="1:4">
       <c r="A94" s="100" t="s">
@@ -11164,7 +11516,10 @@
       <c r="C94" s="100" t="s">
         <v>370</v>
       </c>
-      <c r="D94" s="101"/>
+      <c r="D94" s="101" t="b">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
     </row>
     <row r="95" spans="1:4">
       <c r="A95" s="100" t="s">
@@ -11173,7 +11528,10 @@
       <c r="C95" s="100" t="s">
         <v>383</v>
       </c>
-      <c r="D95" s="101"/>
+      <c r="D95" s="101" t="b">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
     </row>
     <row r="96" spans="1:4">
       <c r="A96" s="100" t="s">
@@ -11182,7 +11540,10 @@
       <c r="C96" s="100" t="s">
         <v>343</v>
       </c>
-      <c r="D96" s="101"/>
+      <c r="D96" s="101" t="b">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
     </row>
     <row r="97" spans="1:4">
       <c r="A97" s="100" t="s">
@@ -11191,7 +11552,10 @@
       <c r="C97" s="100" t="s">
         <v>341</v>
       </c>
-      <c r="D97" s="101"/>
+      <c r="D97" s="101" t="b">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
     </row>
     <row r="98" spans="1:4">
       <c r="A98" s="100" t="s">
@@ -11200,7 +11564,10 @@
       <c r="C98" s="100" t="s">
         <v>329</v>
       </c>
-      <c r="D98" s="101"/>
+      <c r="D98" s="101" t="b">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
     </row>
     <row r="99" spans="1:4">
       <c r="A99" s="100" t="s">
@@ -11209,7 +11576,10 @@
       <c r="C99" s="100" t="s">
         <v>368</v>
       </c>
-      <c r="D99" s="101"/>
+      <c r="D99" s="101" t="b">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
     </row>
     <row r="100" spans="1:4">
       <c r="A100" s="100" t="s">
@@ -11218,7 +11588,10 @@
       <c r="C100" s="100" t="s">
         <v>381</v>
       </c>
-      <c r="D100" s="101"/>
+      <c r="D100" s="101" t="b">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
     </row>
     <row r="101" spans="1:4">
       <c r="A101" s="100" t="s">
@@ -11227,7 +11600,10 @@
       <c r="C101" s="100" t="s">
         <v>363</v>
       </c>
-      <c r="D101" s="101"/>
+      <c r="D101" s="101" t="b">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
     </row>
     <row r="102" spans="1:4">
       <c r="A102" s="100" t="s">
@@ -11236,7 +11612,10 @@
       <c r="C102" s="100" t="s">
         <v>346</v>
       </c>
-      <c r="D102" s="101"/>
+      <c r="D102" s="101" t="b">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
     </row>
     <row r="103" spans="1:4">
       <c r="A103" s="100" t="s">
@@ -11245,7 +11624,10 @@
       <c r="C103" s="100" t="s">
         <v>372</v>
       </c>
-      <c r="D103" s="101"/>
+      <c r="D103" s="101" t="b">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
     </row>
     <row r="104" spans="1:4">
       <c r="A104" s="100" t="s">
@@ -11254,51 +11636,101 @@
       <c r="C104" s="100" t="s">
         <v>384</v>
       </c>
-      <c r="D104" s="101"/>
+      <c r="D104" s="101" t="b">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
     </row>
     <row r="105" spans="1:4">
       <c r="C105" s="100" t="s">
         <v>317</v>
       </c>
-      <c r="D105" s="101"/>
+      <c r="D105" s="101" t="b">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
     </row>
     <row r="106" spans="1:4">
       <c r="C106" s="100" t="s">
         <v>315</v>
       </c>
-      <c r="D106" s="101"/>
+      <c r="D106" s="101" t="b">
+        <f t="shared" ref="D106:D111" si="3">ISNUMBER(MATCH(C106,$A$12:$A$104,0))</f>
+        <v>1</v>
+      </c>
     </row>
     <row r="107" spans="1:4">
       <c r="C107" s="100" t="s">
         <v>379</v>
       </c>
-      <c r="D107" s="101"/>
+      <c r="D107" s="101" t="b">
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
     </row>
     <row r="108" spans="1:4">
       <c r="C108" s="100" t="s">
         <v>380</v>
       </c>
-      <c r="D108" s="101"/>
+      <c r="D108" s="101" t="b">
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
     </row>
     <row r="109" spans="1:4">
       <c r="C109" s="100" t="s">
         <v>385</v>
       </c>
-      <c r="D109" s="101"/>
+      <c r="D109" s="101" t="b">
+        <f>ISNUMBER(MATCH(C109,$A$12:$A$104,0))</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="110" spans="1:4">
       <c r="C110" s="100" t="s">
         <v>378</v>
       </c>
-      <c r="D110" s="101"/>
+      <c r="D110" s="101" t="b">
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
     </row>
     <row r="111" spans="1:4">
       <c r="C111" s="100" t="s">
         <v>375</v>
       </c>
-      <c r="D111" s="101"/>
+      <c r="D111" s="101" t="b">
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
     </row>
   </sheetData>
+  <autoFilter ref="A10:D10" xr:uid="{0C2A3C91-BFD6-416B-8BFA-9FB76CB32857}"/>
+  <conditionalFormatting sqref="D12:D111">
+    <cfRule type="containsText" dxfId="6" priority="1" operator="containsText" text="FALSE">
+      <formula>NOT(ISERROR(SEARCH("FALSE",D12)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G12:G111">
+    <cfRule type="containsText" dxfId="5" priority="4" operator="containsText" text="TRUE">
+      <formula>NOT(ISERROR(SEARCH("TRUE",G12)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H12:H111">
+    <cfRule type="containsText" dxfId="4" priority="5" operator="containsText" text="FALSE">
+      <formula>NOT(ISERROR(SEARCH("FALSE",H12)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I12:I111">
+    <cfRule type="containsText" dxfId="3" priority="3" operator="containsText" text="TRUE">
+      <formula>NOT(ISERROR(SEARCH("TRUE",I12)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K12:K111">
+    <cfRule type="containsText" dxfId="2" priority="2" operator="containsText" text="TRUE">
+      <formula>NOT(ISERROR(SEARCH("TRUE",K12)))</formula>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -11311,14 +11743,14 @@
   <dimension ref="A1:H30"/>
   <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="12" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="13.453125" customWidth="1"/>
-    <col min="3" max="3" width="19.54296875" customWidth="1"/>
-    <col min="4" max="4" width="14.54296875" customWidth="1"/>
+    <col min="1" max="1" width="9.453125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.26953125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="17.54296875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="14.1796875" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="2.1796875" customWidth="1"/>
     <col min="7" max="7" width="17.54296875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11.81640625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="11.54296875" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="2.1796875" customWidth="1"/>
     <col min="11" max="11" width="13.1796875" bestFit="1" customWidth="1"/>
@@ -11337,348 +11769,423 @@
       <c r="H1" s="104"/>
     </row>
     <row r="5" spans="1:8">
-      <c r="A5" s="105" t="s">
+      <c r="A5" s="163" t="s">
         <v>21</v>
       </c>
-      <c r="B5" s="105" t="s">
+      <c r="B5" s="163" t="s">
         <v>387</v>
       </c>
-      <c r="C5" s="105" t="s">
+      <c r="C5" s="163" t="s">
         <v>388</v>
       </c>
-      <c r="D5" s="105" t="s">
+      <c r="D5" s="163" t="s">
         <v>389</v>
       </c>
-      <c r="G5" s="105" t="s">
+      <c r="G5" s="163" t="s">
         <v>388</v>
       </c>
-      <c r="H5" s="105" t="s">
+      <c r="H5" s="163" t="s">
         <v>389</v>
       </c>
     </row>
     <row r="6" spans="1:8">
-      <c r="A6" s="106">
+      <c r="A6" s="164">
         <v>40308</v>
       </c>
-      <c r="B6" s="100" t="s">
+      <c r="B6" s="165" t="s">
         <v>390</v>
       </c>
-      <c r="C6" s="100">
+      <c r="C6" s="165">
         <v>73</v>
       </c>
-      <c r="D6" s="107"/>
-      <c r="G6" s="100">
+      <c r="D6" s="166">
+        <f>INDEX($H$6:$H$9,MATCH(C6,$G$6:$G$9,1))</f>
+        <v>50</v>
+      </c>
+      <c r="G6" s="165">
         <v>0</v>
       </c>
-      <c r="H6" s="108">
+      <c r="H6" s="167">
         <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:8">
-      <c r="A7" s="106">
+      <c r="A7" s="164">
         <v>40308</v>
       </c>
-      <c r="B7" s="100" t="s">
+      <c r="B7" s="165" t="s">
         <v>391</v>
       </c>
-      <c r="C7" s="100">
+      <c r="C7" s="165">
         <v>22</v>
       </c>
-      <c r="D7" s="107"/>
-      <c r="G7" s="100">
+      <c r="D7" s="166">
+        <f t="shared" ref="D7:D30" si="0">INDEX($H$6:$H$9,MATCH(C7,$G$6:$G$9,1))</f>
+        <v>0</v>
+      </c>
+      <c r="G7" s="165">
         <v>60</v>
       </c>
-      <c r="H7" s="108">
+      <c r="H7" s="167">
         <v>50</v>
       </c>
     </row>
     <row r="8" spans="1:8">
-      <c r="A8" s="106">
+      <c r="A8" s="164">
         <v>40308</v>
       </c>
-      <c r="B8" s="100" t="s">
+      <c r="B8" s="165" t="s">
         <v>392</v>
       </c>
-      <c r="C8" s="100">
+      <c r="C8" s="165">
         <v>92</v>
       </c>
-      <c r="D8" s="107"/>
-      <c r="G8" s="100">
+      <c r="D8" s="166">
+        <f t="shared" si="0"/>
+        <v>75</v>
+      </c>
+      <c r="G8" s="165">
         <v>90</v>
       </c>
-      <c r="H8" s="108">
+      <c r="H8" s="167">
         <v>75</v>
       </c>
     </row>
     <row r="9" spans="1:8">
-      <c r="A9" s="106">
+      <c r="A9" s="164">
         <v>40308</v>
       </c>
-      <c r="B9" s="100" t="s">
+      <c r="B9" s="165" t="s">
         <v>393</v>
       </c>
-      <c r="C9" s="100">
+      <c r="C9" s="165">
         <v>77</v>
       </c>
-      <c r="D9" s="107"/>
-      <c r="G9" s="100">
+      <c r="D9" s="166">
+        <f t="shared" si="0"/>
+        <v>50</v>
+      </c>
+      <c r="G9" s="165">
         <v>150</v>
       </c>
-      <c r="H9" s="108">
+      <c r="H9" s="167">
         <v>150</v>
       </c>
     </row>
     <row r="10" spans="1:8">
-      <c r="A10" s="106">
+      <c r="A10" s="164">
         <v>40308</v>
       </c>
-      <c r="B10" s="100" t="s">
+      <c r="B10" s="165" t="s">
         <v>394</v>
       </c>
-      <c r="C10" s="100">
+      <c r="C10" s="165">
         <v>78</v>
       </c>
-      <c r="D10" s="107"/>
+      <c r="D10" s="166">
+        <f t="shared" si="0"/>
+        <v>50</v>
+      </c>
     </row>
     <row r="11" spans="1:8">
-      <c r="A11" s="106">
+      <c r="A11" s="164">
         <v>40308</v>
       </c>
-      <c r="B11" s="100" t="s">
+      <c r="B11" s="165" t="s">
         <v>395</v>
       </c>
-      <c r="C11" s="100">
+      <c r="C11" s="165">
         <v>93</v>
       </c>
-      <c r="D11" s="107"/>
+      <c r="D11" s="166">
+        <f t="shared" si="0"/>
+        <v>75</v>
+      </c>
     </row>
     <row r="12" spans="1:8">
-      <c r="A12" s="106">
+      <c r="A12" s="164">
         <v>40308</v>
       </c>
-      <c r="B12" s="100" t="s">
+      <c r="B12" s="165" t="s">
         <v>396</v>
       </c>
-      <c r="C12" s="100">
+      <c r="C12" s="165">
         <v>90</v>
       </c>
-      <c r="D12" s="107"/>
+      <c r="D12" s="166">
+        <f t="shared" si="0"/>
+        <v>75</v>
+      </c>
     </row>
     <row r="13" spans="1:8">
-      <c r="A13" s="106">
+      <c r="A13" s="164">
         <v>40308</v>
       </c>
-      <c r="B13" s="100" t="s">
+      <c r="B13" s="165" t="s">
         <v>397</v>
       </c>
-      <c r="C13" s="100">
+      <c r="C13" s="165">
         <v>88</v>
       </c>
-      <c r="D13" s="107"/>
+      <c r="D13" s="166">
+        <f t="shared" si="0"/>
+        <v>50</v>
+      </c>
     </row>
     <row r="14" spans="1:8">
-      <c r="A14" s="106">
+      <c r="A14" s="164">
         <v>40308</v>
       </c>
-      <c r="B14" s="100" t="s">
+      <c r="B14" s="165" t="s">
         <v>398</v>
       </c>
-      <c r="C14" s="100">
+      <c r="C14" s="165">
         <v>77</v>
       </c>
-      <c r="D14" s="107"/>
+      <c r="D14" s="166">
+        <f t="shared" si="0"/>
+        <v>50</v>
+      </c>
     </row>
     <row r="15" spans="1:8">
-      <c r="A15" s="106">
+      <c r="A15" s="164">
         <v>40308</v>
       </c>
-      <c r="B15" s="100" t="s">
+      <c r="B15" s="165" t="s">
         <v>399</v>
       </c>
-      <c r="C15" s="100">
+      <c r="C15" s="165">
         <v>81</v>
       </c>
-      <c r="D15" s="107"/>
+      <c r="D15" s="166">
+        <f t="shared" si="0"/>
+        <v>50</v>
+      </c>
     </row>
     <row r="16" spans="1:8">
-      <c r="A16" s="106">
+      <c r="A16" s="164">
         <v>40308</v>
       </c>
-      <c r="B16" s="100" t="s">
+      <c r="B16" s="165" t="s">
         <v>400</v>
       </c>
-      <c r="C16" s="100">
+      <c r="C16" s="165">
         <v>81</v>
       </c>
-      <c r="D16" s="107"/>
+      <c r="D16" s="166">
+        <f t="shared" si="0"/>
+        <v>50</v>
+      </c>
     </row>
     <row r="17" spans="1:4">
-      <c r="A17" s="106">
+      <c r="A17" s="164">
         <v>40308</v>
       </c>
-      <c r="B17" s="100" t="s">
+      <c r="B17" s="165" t="s">
         <v>401</v>
       </c>
-      <c r="C17" s="100">
+      <c r="C17" s="165">
         <v>86</v>
       </c>
-      <c r="D17" s="107"/>
+      <c r="D17" s="166">
+        <f t="shared" si="0"/>
+        <v>50</v>
+      </c>
     </row>
     <row r="18" spans="1:4">
-      <c r="A18" s="106">
+      <c r="A18" s="164">
         <v>40308</v>
       </c>
-      <c r="B18" s="100" t="s">
+      <c r="B18" s="165" t="s">
         <v>402</v>
       </c>
-      <c r="C18" s="100">
+      <c r="C18" s="165">
         <v>91</v>
       </c>
-      <c r="D18" s="107"/>
+      <c r="D18" s="166">
+        <f t="shared" si="0"/>
+        <v>75</v>
+      </c>
     </row>
     <row r="19" spans="1:4">
-      <c r="A19" s="106">
+      <c r="A19" s="164">
         <v>40308</v>
       </c>
-      <c r="B19" s="100" t="s">
+      <c r="B19" s="165" t="s">
         <v>403</v>
       </c>
-      <c r="C19" s="100">
+      <c r="C19" s="165">
         <v>84</v>
       </c>
-      <c r="D19" s="107"/>
+      <c r="D19" s="166">
+        <f t="shared" si="0"/>
+        <v>50</v>
+      </c>
     </row>
     <row r="20" spans="1:4">
-      <c r="A20" s="106">
+      <c r="A20" s="164">
         <v>40308</v>
       </c>
-      <c r="B20" s="100" t="s">
+      <c r="B20" s="165" t="s">
         <v>404</v>
       </c>
-      <c r="C20" s="100">
+      <c r="C20" s="165">
         <v>89</v>
       </c>
-      <c r="D20" s="107"/>
+      <c r="D20" s="166">
+        <f t="shared" si="0"/>
+        <v>50</v>
+      </c>
     </row>
     <row r="21" spans="1:4">
-      <c r="A21" s="106">
+      <c r="A21" s="164">
         <v>40308</v>
       </c>
-      <c r="B21" s="100" t="s">
+      <c r="B21" s="165" t="s">
         <v>405</v>
       </c>
-      <c r="C21" s="100">
+      <c r="C21" s="165">
         <v>74</v>
       </c>
-      <c r="D21" s="107"/>
+      <c r="D21" s="166">
+        <f t="shared" si="0"/>
+        <v>50</v>
+      </c>
     </row>
     <row r="22" spans="1:4">
-      <c r="A22" s="106">
+      <c r="A22" s="164">
         <v>40308</v>
       </c>
-      <c r="B22" s="100" t="s">
+      <c r="B22" s="165" t="s">
         <v>406</v>
       </c>
-      <c r="C22" s="100">
+      <c r="C22" s="165">
         <v>86</v>
       </c>
-      <c r="D22" s="107"/>
+      <c r="D22" s="166">
+        <f t="shared" si="0"/>
+        <v>50</v>
+      </c>
     </row>
     <row r="23" spans="1:4">
-      <c r="A23" s="106">
+      <c r="A23" s="164">
         <v>40308</v>
       </c>
-      <c r="B23" s="100" t="s">
+      <c r="B23" s="165" t="s">
         <v>407</v>
       </c>
-      <c r="C23" s="100">
+      <c r="C23" s="165">
         <v>94</v>
       </c>
-      <c r="D23" s="107"/>
+      <c r="D23" s="166">
+        <f t="shared" si="0"/>
+        <v>75</v>
+      </c>
     </row>
     <row r="24" spans="1:4">
-      <c r="A24" s="106">
+      <c r="A24" s="164">
         <v>40308</v>
       </c>
-      <c r="B24" s="100" t="s">
+      <c r="B24" s="165" t="s">
         <v>408</v>
       </c>
-      <c r="C24" s="100">
+      <c r="C24" s="165">
         <v>70</v>
       </c>
-      <c r="D24" s="107"/>
+      <c r="D24" s="166">
+        <f t="shared" si="0"/>
+        <v>50</v>
+      </c>
     </row>
     <row r="25" spans="1:4">
-      <c r="A25" s="106">
+      <c r="A25" s="164">
         <v>40308</v>
       </c>
-      <c r="B25" s="100" t="s">
+      <c r="B25" s="165" t="s">
         <v>409</v>
       </c>
-      <c r="C25" s="100">
+      <c r="C25" s="165">
         <v>0</v>
       </c>
-      <c r="D25" s="107"/>
+      <c r="D25" s="166">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
     </row>
     <row r="26" spans="1:4">
-      <c r="A26" s="106">
+      <c r="A26" s="164">
         <v>40308</v>
       </c>
-      <c r="B26" s="100" t="s">
+      <c r="B26" s="165" t="s">
         <v>410</v>
       </c>
-      <c r="C26" s="100">
+      <c r="C26" s="165">
         <v>86</v>
       </c>
-      <c r="D26" s="107"/>
+      <c r="D26" s="166">
+        <f t="shared" si="0"/>
+        <v>50</v>
+      </c>
     </row>
     <row r="27" spans="1:4">
-      <c r="A27" s="106">
+      <c r="A27" s="164">
         <v>40308</v>
       </c>
-      <c r="B27" s="100" t="s">
+      <c r="B27" s="165" t="s">
         <v>411</v>
       </c>
-      <c r="C27" s="100">
+      <c r="C27" s="165">
         <v>88</v>
       </c>
-      <c r="D27" s="107"/>
+      <c r="D27" s="166">
+        <f t="shared" si="0"/>
+        <v>50</v>
+      </c>
     </row>
     <row r="28" spans="1:4">
-      <c r="A28" s="106">
+      <c r="A28" s="164">
         <v>40308</v>
       </c>
-      <c r="B28" s="100" t="s">
+      <c r="B28" s="165" t="s">
         <v>412</v>
       </c>
-      <c r="C28" s="100">
+      <c r="C28" s="165">
         <v>94</v>
       </c>
-      <c r="D28" s="107"/>
+      <c r="D28" s="166">
+        <f t="shared" si="0"/>
+        <v>75</v>
+      </c>
     </row>
     <row r="29" spans="1:4">
-      <c r="A29" s="106">
+      <c r="A29" s="164">
         <v>40308</v>
       </c>
-      <c r="B29" s="100" t="s">
+      <c r="B29" s="165" t="s">
         <v>413</v>
       </c>
-      <c r="C29" s="100">
+      <c r="C29" s="165">
         <v>84</v>
       </c>
-      <c r="D29" s="107"/>
+      <c r="D29" s="166">
+        <f t="shared" si="0"/>
+        <v>50</v>
+      </c>
     </row>
     <row r="30" spans="1:4">
-      <c r="A30" s="106">
+      <c r="A30" s="164">
         <v>40308</v>
       </c>
-      <c r="B30" s="100" t="s">
+      <c r="B30" s="165" t="s">
         <v>414</v>
       </c>
-      <c r="C30" s="100">
+      <c r="C30" s="165">
         <v>79</v>
       </c>
-      <c r="D30" s="107"/>
+      <c r="D30" s="166">
+        <f t="shared" si="0"/>
+        <v>50</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -11704,573 +12211,573 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="43.5">
-      <c r="A1" s="109" t="s">
+      <c r="A1" s="107" t="s">
         <v>415</v>
       </c>
-      <c r="B1" s="109"/>
-      <c r="C1" s="109"/>
-      <c r="D1" s="109"/>
-      <c r="E1" s="109"/>
-      <c r="F1" s="109"/>
-      <c r="G1" s="109"/>
-      <c r="H1" s="109"/>
-      <c r="I1" s="109"/>
-      <c r="J1" s="109"/>
+      <c r="B1" s="107"/>
+      <c r="C1" s="107"/>
+      <c r="D1" s="107"/>
+      <c r="E1" s="107"/>
+      <c r="F1" s="107"/>
+      <c r="G1" s="107"/>
+      <c r="H1" s="107"/>
+      <c r="I1" s="107"/>
+      <c r="J1" s="107"/>
     </row>
     <row r="4" spans="1:10">
-      <c r="A4" s="110" t="s">
+      <c r="A4" s="108" t="s">
         <v>416</v>
       </c>
-      <c r="B4" s="111" t="s">
+      <c r="B4" s="109" t="s">
         <v>417</v>
       </c>
-      <c r="C4" s="111" t="s">
+      <c r="C4" s="109" t="s">
         <v>418</v>
       </c>
-      <c r="D4" s="111" t="s">
+      <c r="D4" s="109" t="s">
         <v>419</v>
       </c>
-      <c r="E4" s="111" t="s">
+      <c r="E4" s="109" t="s">
         <v>420</v>
       </c>
-      <c r="F4" s="111" t="s">
+      <c r="F4" s="109" t="s">
         <v>421</v>
       </c>
-      <c r="G4" s="111" t="s">
+      <c r="G4" s="109" t="s">
         <v>422</v>
       </c>
-      <c r="H4" s="111" t="s">
+      <c r="H4" s="109" t="s">
         <v>423</v>
       </c>
-      <c r="I4" s="110" t="s">
+      <c r="I4" s="108" t="s">
         <v>424</v>
       </c>
-      <c r="J4" s="110" t="s">
+      <c r="J4" s="108" t="s">
         <v>425</v>
       </c>
     </row>
     <row r="5" spans="1:10">
-      <c r="A5" s="111" t="s">
+      <c r="A5" s="109" t="s">
         <v>426</v>
       </c>
-      <c r="B5" s="112">
+      <c r="B5" s="110">
         <v>57.97</v>
       </c>
-      <c r="C5" s="112">
+      <c r="C5" s="110">
         <v>72.2</v>
       </c>
-      <c r="D5" s="112">
+      <c r="D5" s="110">
         <v>39.01</v>
       </c>
-      <c r="E5" s="112">
+      <c r="E5" s="110">
         <v>60.33</v>
       </c>
-      <c r="F5" s="112">
+      <c r="F5" s="110">
         <v>71.400000000000006</v>
       </c>
-      <c r="G5" s="112">
+      <c r="G5" s="110">
         <v>72.819999999999993</v>
       </c>
-      <c r="H5" s="112">
+      <c r="H5" s="110">
         <v>60.93</v>
       </c>
-      <c r="I5" s="113">
+      <c r="I5" s="111">
         <f>MIN(B5:H5)</f>
         <v>39.01</v>
       </c>
       <c r="J5" s="101"/>
     </row>
     <row r="6" spans="1:10">
-      <c r="A6" s="111" t="s">
+      <c r="A6" s="109" t="s">
         <v>427</v>
       </c>
-      <c r="B6" s="112">
+      <c r="B6" s="110">
         <v>51.67</v>
       </c>
-      <c r="C6" s="112">
+      <c r="C6" s="110">
         <v>29.87</v>
       </c>
-      <c r="D6" s="112">
+      <c r="D6" s="110">
         <v>52.23</v>
       </c>
-      <c r="E6" s="112">
+      <c r="E6" s="110">
         <v>48.34</v>
       </c>
-      <c r="F6" s="112">
+      <c r="F6" s="110">
         <v>51.37</v>
       </c>
-      <c r="G6" s="112">
+      <c r="G6" s="110">
         <v>52.58</v>
       </c>
-      <c r="H6" s="112">
+      <c r="H6" s="110">
         <v>51.64</v>
       </c>
-      <c r="I6" s="113">
+      <c r="I6" s="111">
         <f t="shared" ref="I6:I21" si="0">MIN(B6:H6)</f>
         <v>29.87</v>
       </c>
       <c r="J6" s="101"/>
     </row>
     <row r="7" spans="1:10">
-      <c r="A7" s="111" t="s">
+      <c r="A7" s="109" t="s">
         <v>428</v>
       </c>
-      <c r="B7" s="112">
+      <c r="B7" s="110">
         <v>64.73</v>
       </c>
-      <c r="C7" s="112">
+      <c r="C7" s="110">
         <v>40.590000000000003</v>
       </c>
-      <c r="D7" s="112">
+      <c r="D7" s="110">
         <v>61.76</v>
       </c>
-      <c r="E7" s="112">
+      <c r="E7" s="110">
         <v>35.56</v>
       </c>
-      <c r="F7" s="112">
+      <c r="F7" s="110">
         <v>28.81</v>
       </c>
-      <c r="G7" s="112">
+      <c r="G7" s="110">
         <v>74.77</v>
       </c>
-      <c r="H7" s="112">
+      <c r="H7" s="110">
         <v>64.55</v>
       </c>
-      <c r="I7" s="113">
+      <c r="I7" s="111">
         <f t="shared" si="0"/>
         <v>28.81</v>
       </c>
       <c r="J7" s="101"/>
     </row>
     <row r="8" spans="1:10">
-      <c r="A8" s="111" t="s">
+      <c r="A8" s="109" t="s">
         <v>429</v>
       </c>
-      <c r="B8" s="112">
+      <c r="B8" s="110">
         <v>73.02</v>
       </c>
-      <c r="C8" s="112">
+      <c r="C8" s="110">
         <v>64.98</v>
       </c>
-      <c r="D8" s="112">
+      <c r="D8" s="110">
         <v>53.34</v>
       </c>
-      <c r="E8" s="112">
+      <c r="E8" s="110">
         <v>62.14</v>
       </c>
-      <c r="F8" s="112">
+      <c r="F8" s="110">
         <v>29.69</v>
       </c>
-      <c r="G8" s="112">
+      <c r="G8" s="110">
         <v>50.67</v>
       </c>
-      <c r="H8" s="112">
+      <c r="H8" s="110">
         <v>48.59</v>
       </c>
-      <c r="I8" s="113">
+      <c r="I8" s="111">
         <f t="shared" si="0"/>
         <v>29.69</v>
       </c>
       <c r="J8" s="101"/>
     </row>
     <row r="9" spans="1:10">
-      <c r="A9" s="111" t="s">
+      <c r="A9" s="109" t="s">
         <v>430</v>
       </c>
-      <c r="B9" s="112">
+      <c r="B9" s="110">
         <v>72.36</v>
       </c>
-      <c r="C9" s="112">
+      <c r="C9" s="110">
         <v>32.44</v>
       </c>
-      <c r="D9" s="112">
+      <c r="D9" s="110">
         <v>65.069999999999993</v>
       </c>
-      <c r="E9" s="112">
+      <c r="E9" s="110">
         <v>35.71</v>
       </c>
-      <c r="F9" s="112">
+      <c r="F9" s="110">
         <v>52.5</v>
       </c>
-      <c r="G9" s="112">
+      <c r="G9" s="110">
         <v>52.86</v>
       </c>
-      <c r="H9" s="112">
+      <c r="H9" s="110">
         <v>43</v>
       </c>
-      <c r="I9" s="113">
+      <c r="I9" s="111">
         <f t="shared" si="0"/>
         <v>32.44</v>
       </c>
       <c r="J9" s="101"/>
     </row>
     <row r="10" spans="1:10">
-      <c r="A10" s="111" t="s">
+      <c r="A10" s="109" t="s">
         <v>431</v>
       </c>
-      <c r="B10" s="112">
+      <c r="B10" s="110">
         <v>47.52</v>
       </c>
-      <c r="C10" s="112">
+      <c r="C10" s="110">
         <v>47.39</v>
       </c>
-      <c r="D10" s="112">
+      <c r="D10" s="110">
         <v>26.32</v>
       </c>
-      <c r="E10" s="112">
+      <c r="E10" s="110">
         <v>47.34</v>
       </c>
-      <c r="F10" s="112">
+      <c r="F10" s="110">
         <v>49.11</v>
       </c>
-      <c r="G10" s="112">
+      <c r="G10" s="110">
         <v>56.24</v>
       </c>
-      <c r="H10" s="112">
+      <c r="H10" s="110">
         <v>73.069999999999993</v>
       </c>
-      <c r="I10" s="113">
+      <c r="I10" s="111">
         <f t="shared" si="0"/>
         <v>26.32</v>
       </c>
       <c r="J10" s="101"/>
     </row>
     <row r="11" spans="1:10">
-      <c r="A11" s="111" t="s">
+      <c r="A11" s="109" t="s">
         <v>432</v>
       </c>
-      <c r="B11" s="112">
+      <c r="B11" s="110">
         <v>66.02</v>
       </c>
-      <c r="C11" s="112">
+      <c r="C11" s="110">
         <v>68.8</v>
       </c>
-      <c r="D11" s="112">
+      <c r="D11" s="110">
         <v>33.14</v>
       </c>
-      <c r="E11" s="112">
+      <c r="E11" s="110">
         <v>60.98</v>
       </c>
-      <c r="F11" s="112">
+      <c r="F11" s="110">
         <v>28.11</v>
       </c>
-      <c r="G11" s="112">
+      <c r="G11" s="110">
         <v>54.45</v>
       </c>
-      <c r="H11" s="112">
+      <c r="H11" s="110">
         <v>56.33</v>
       </c>
-      <c r="I11" s="113">
+      <c r="I11" s="111">
         <f t="shared" si="0"/>
         <v>28.11</v>
       </c>
       <c r="J11" s="101"/>
     </row>
     <row r="12" spans="1:10">
-      <c r="A12" s="111" t="s">
+      <c r="A12" s="109" t="s">
         <v>433</v>
       </c>
-      <c r="B12" s="112">
+      <c r="B12" s="110">
         <v>74.569999999999993</v>
       </c>
-      <c r="C12" s="112">
+      <c r="C12" s="110">
         <v>43.65</v>
       </c>
-      <c r="D12" s="112">
+      <c r="D12" s="110">
         <v>41.36</v>
       </c>
-      <c r="E12" s="112">
+      <c r="E12" s="110">
         <v>39.86</v>
       </c>
-      <c r="F12" s="112">
+      <c r="F12" s="110">
         <v>39.22</v>
       </c>
-      <c r="G12" s="112">
+      <c r="G12" s="110">
         <v>58.92</v>
       </c>
-      <c r="H12" s="112">
+      <c r="H12" s="110">
         <v>67.209999999999994</v>
       </c>
-      <c r="I12" s="113">
+      <c r="I12" s="111">
         <f t="shared" si="0"/>
         <v>39.22</v>
       </c>
       <c r="J12" s="101"/>
     </row>
     <row r="13" spans="1:10">
-      <c r="A13" s="111" t="s">
+      <c r="A13" s="109" t="s">
         <v>434</v>
       </c>
-      <c r="B13" s="112">
+      <c r="B13" s="110">
         <v>71.55</v>
       </c>
-      <c r="C13" s="112">
+      <c r="C13" s="110">
         <v>55.67</v>
       </c>
-      <c r="D13" s="112">
+      <c r="D13" s="110">
         <v>57.99</v>
       </c>
-      <c r="E13" s="112">
+      <c r="E13" s="110">
         <v>69.540000000000006</v>
       </c>
-      <c r="F13" s="112">
+      <c r="F13" s="110">
         <v>47.16</v>
       </c>
-      <c r="G13" s="112">
+      <c r="G13" s="110">
         <v>72.78</v>
       </c>
-      <c r="H13" s="112">
+      <c r="H13" s="110">
         <v>48.83</v>
       </c>
-      <c r="I13" s="113">
+      <c r="I13" s="111">
         <f t="shared" si="0"/>
         <v>47.16</v>
       </c>
       <c r="J13" s="101"/>
     </row>
     <row r="14" spans="1:10">
-      <c r="A14" s="111" t="s">
+      <c r="A14" s="109" t="s">
         <v>435</v>
       </c>
-      <c r="B14" s="112">
+      <c r="B14" s="110">
         <v>50.06</v>
       </c>
-      <c r="C14" s="112">
+      <c r="C14" s="110">
         <v>70.11</v>
       </c>
-      <c r="D14" s="112">
+      <c r="D14" s="110">
         <v>41.98</v>
       </c>
-      <c r="E14" s="112">
+      <c r="E14" s="110">
         <v>63.71</v>
       </c>
-      <c r="F14" s="112">
+      <c r="F14" s="110">
         <v>51.05</v>
       </c>
-      <c r="G14" s="112">
+      <c r="G14" s="110">
         <v>26.44</v>
       </c>
-      <c r="H14" s="112">
+      <c r="H14" s="110">
         <v>30.49</v>
       </c>
-      <c r="I14" s="113">
+      <c r="I14" s="111">
         <f t="shared" si="0"/>
         <v>26.44</v>
       </c>
       <c r="J14" s="101"/>
     </row>
     <row r="15" spans="1:10">
-      <c r="A15" s="111" t="s">
+      <c r="A15" s="109" t="s">
         <v>436</v>
       </c>
-      <c r="B15" s="112">
+      <c r="B15" s="110">
         <v>39.92</v>
       </c>
-      <c r="C15" s="112">
+      <c r="C15" s="110">
         <v>69.05</v>
       </c>
-      <c r="D15" s="112">
+      <c r="D15" s="110">
         <v>71.14</v>
       </c>
-      <c r="E15" s="112">
+      <c r="E15" s="110">
         <v>62.54</v>
       </c>
-      <c r="F15" s="112">
+      <c r="F15" s="110">
         <v>59.59</v>
       </c>
-      <c r="G15" s="112">
+      <c r="G15" s="110">
         <v>55.17</v>
       </c>
-      <c r="H15" s="112">
+      <c r="H15" s="110">
         <v>65.290000000000006</v>
       </c>
-      <c r="I15" s="113">
+      <c r="I15" s="111">
         <f t="shared" si="0"/>
         <v>39.92</v>
       </c>
       <c r="J15" s="101"/>
     </row>
     <row r="16" spans="1:10">
-      <c r="A16" s="111" t="s">
+      <c r="A16" s="109" t="s">
         <v>437</v>
       </c>
-      <c r="B16" s="112">
+      <c r="B16" s="110">
         <v>31.03</v>
       </c>
-      <c r="C16" s="112">
+      <c r="C16" s="110">
         <v>60.19</v>
       </c>
-      <c r="D16" s="112">
+      <c r="D16" s="110">
         <v>31.82</v>
       </c>
-      <c r="E16" s="112">
+      <c r="E16" s="110">
         <v>30.53</v>
       </c>
-      <c r="F16" s="112">
+      <c r="F16" s="110">
         <v>62.71</v>
       </c>
-      <c r="G16" s="112">
+      <c r="G16" s="110">
         <v>46.56</v>
       </c>
-      <c r="H16" s="112">
+      <c r="H16" s="110">
         <v>44.78</v>
       </c>
-      <c r="I16" s="113">
+      <c r="I16" s="111">
         <f t="shared" si="0"/>
         <v>30.53</v>
       </c>
       <c r="J16" s="101"/>
     </row>
     <row r="17" spans="1:10">
-      <c r="A17" s="111" t="s">
+      <c r="A17" s="109" t="s">
         <v>438</v>
       </c>
-      <c r="B17" s="112">
+      <c r="B17" s="110">
         <v>65.98</v>
       </c>
-      <c r="C17" s="112">
+      <c r="C17" s="110">
         <v>49.93</v>
       </c>
-      <c r="D17" s="112">
+      <c r="D17" s="110">
         <v>60.68</v>
       </c>
-      <c r="E17" s="112">
+      <c r="E17" s="110">
         <v>72.040000000000006</v>
       </c>
-      <c r="F17" s="112">
+      <c r="F17" s="110">
         <v>68.239999999999995</v>
       </c>
-      <c r="G17" s="112">
+      <c r="G17" s="110">
         <v>55.82</v>
       </c>
-      <c r="H17" s="112">
+      <c r="H17" s="110">
         <v>34.57</v>
       </c>
-      <c r="I17" s="113">
+      <c r="I17" s="111">
         <f t="shared" si="0"/>
         <v>34.57</v>
       </c>
       <c r="J17" s="101"/>
     </row>
     <row r="18" spans="1:10">
-      <c r="A18" s="111" t="s">
+      <c r="A18" s="109" t="s">
         <v>439</v>
       </c>
-      <c r="B18" s="112">
+      <c r="B18" s="110">
         <v>40.090000000000003</v>
       </c>
-      <c r="C18" s="112">
+      <c r="C18" s="110">
         <v>27.33</v>
       </c>
-      <c r="D18" s="112">
+      <c r="D18" s="110">
         <v>62.3</v>
       </c>
-      <c r="E18" s="112">
+      <c r="E18" s="110">
         <v>41.04</v>
       </c>
-      <c r="F18" s="112">
+      <c r="F18" s="110">
         <v>44.3</v>
       </c>
-      <c r="G18" s="112">
+      <c r="G18" s="110">
         <v>40.67</v>
       </c>
-      <c r="H18" s="112">
+      <c r="H18" s="110">
         <v>26.93</v>
       </c>
-      <c r="I18" s="113">
+      <c r="I18" s="111">
         <f t="shared" si="0"/>
         <v>26.93</v>
       </c>
       <c r="J18" s="101"/>
     </row>
     <row r="19" spans="1:10">
-      <c r="A19" s="111" t="s">
+      <c r="A19" s="109" t="s">
         <v>440</v>
       </c>
-      <c r="B19" s="112">
+      <c r="B19" s="110">
         <v>73.59</v>
       </c>
-      <c r="C19" s="112">
+      <c r="C19" s="110">
         <v>58.8</v>
       </c>
-      <c r="D19" s="112">
+      <c r="D19" s="110">
         <v>56.93</v>
       </c>
-      <c r="E19" s="112">
+      <c r="E19" s="110">
         <v>47.5</v>
       </c>
-      <c r="F19" s="112">
+      <c r="F19" s="110">
         <v>43.76</v>
       </c>
-      <c r="G19" s="112">
+      <c r="G19" s="110">
         <v>27.49</v>
       </c>
-      <c r="H19" s="112">
+      <c r="H19" s="110">
         <v>58.85</v>
       </c>
-      <c r="I19" s="113">
+      <c r="I19" s="111">
         <f t="shared" si="0"/>
         <v>27.49</v>
       </c>
       <c r="J19" s="101"/>
     </row>
     <row r="20" spans="1:10">
-      <c r="A20" s="111" t="s">
+      <c r="A20" s="109" t="s">
         <v>441</v>
       </c>
-      <c r="B20" s="112">
+      <c r="B20" s="110">
         <v>57.86</v>
       </c>
-      <c r="C20" s="112">
+      <c r="C20" s="110">
         <v>62.93</v>
       </c>
-      <c r="D20" s="112">
+      <c r="D20" s="110">
         <v>48.05</v>
       </c>
-      <c r="E20" s="112">
+      <c r="E20" s="110">
         <v>37.69</v>
       </c>
-      <c r="F20" s="112">
+      <c r="F20" s="110">
         <v>32.81</v>
       </c>
-      <c r="G20" s="112">
+      <c r="G20" s="110">
         <v>50.7</v>
       </c>
-      <c r="H20" s="112">
+      <c r="H20" s="110">
         <v>46.65</v>
       </c>
-      <c r="I20" s="113">
+      <c r="I20" s="111">
         <f t="shared" si="0"/>
         <v>32.81</v>
       </c>
       <c r="J20" s="101"/>
     </row>
     <row r="21" spans="1:10">
-      <c r="A21" s="111" t="s">
+      <c r="A21" s="109" t="s">
         <v>442</v>
       </c>
-      <c r="B21" s="112">
+      <c r="B21" s="110">
         <v>59.02</v>
       </c>
-      <c r="C21" s="112">
+      <c r="C21" s="110">
         <v>42.07</v>
       </c>
-      <c r="D21" s="112">
+      <c r="D21" s="110">
         <v>45.23</v>
       </c>
-      <c r="E21" s="112">
+      <c r="E21" s="110">
         <v>62.1</v>
       </c>
-      <c r="F21" s="112">
+      <c r="F21" s="110">
         <v>60.28</v>
       </c>
-      <c r="G21" s="112">
+      <c r="G21" s="110">
         <v>52.26</v>
       </c>
-      <c r="H21" s="112">
+      <c r="H21" s="110">
         <v>36.049999999999997</v>
       </c>
-      <c r="I21" s="113">
+      <c r="I21" s="111">
         <f t="shared" si="0"/>
         <v>36.049999999999997</v>
       </c>
@@ -12278,7 +12785,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B5:H21">
-    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -12300,16 +12807,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="29">
-      <c r="A1" s="109" t="s">
+      <c r="A1" s="107" t="s">
         <v>443</v>
       </c>
-      <c r="B1" s="109"/>
-      <c r="C1" s="109"/>
-      <c r="D1" s="109"/>
-      <c r="E1" s="109"/>
-      <c r="F1" s="109"/>
-      <c r="G1" s="109"/>
-      <c r="H1" s="109"/>
+      <c r="B1" s="107"/>
+      <c r="C1" s="107"/>
+      <c r="D1" s="107"/>
+      <c r="E1" s="107"/>
+      <c r="F1" s="107"/>
+      <c r="G1" s="107"/>
+      <c r="H1" s="107"/>
     </row>
     <row r="3" spans="1:12">
       <c r="A3" s="105" t="s">
@@ -12323,7 +12830,7 @@
       <c r="A4" s="105" t="s">
         <v>103</v>
       </c>
-      <c r="B4" s="114"/>
+      <c r="B4" s="112"/>
     </row>
     <row r="6" spans="1:12">
       <c r="A6" s="99" t="s">
@@ -12364,3308 +12871,3308 @@
       </c>
     </row>
     <row r="7" spans="1:12">
-      <c r="A7" s="108">
+      <c r="A7" s="106">
         <v>6236</v>
       </c>
-      <c r="B7" s="108">
+      <c r="B7" s="106">
         <v>7325</v>
       </c>
-      <c r="C7" s="108">
+      <c r="C7" s="106">
         <v>9421</v>
       </c>
-      <c r="D7" s="108">
+      <c r="D7" s="106">
         <v>6520</v>
       </c>
-      <c r="E7" s="108">
+      <c r="E7" s="106">
         <v>10403</v>
       </c>
-      <c r="F7" s="108">
+      <c r="F7" s="106">
         <v>10746</v>
       </c>
-      <c r="G7" s="108">
+      <c r="G7" s="106">
         <v>9700</v>
       </c>
-      <c r="H7" s="108">
+      <c r="H7" s="106">
         <v>8536</v>
       </c>
-      <c r="I7" s="108">
+      <c r="I7" s="106">
         <v>5199</v>
       </c>
-      <c r="J7" s="108">
+      <c r="J7" s="106">
         <v>10997</v>
       </c>
-      <c r="K7" s="108">
+      <c r="K7" s="106">
         <v>7730</v>
       </c>
-      <c r="L7" s="108">
+      <c r="L7" s="106">
         <v>10232</v>
       </c>
     </row>
     <row r="8" spans="1:12">
-      <c r="A8" s="108">
+      <c r="A8" s="106">
         <v>9620</v>
       </c>
-      <c r="B8" s="108">
+      <c r="B8" s="106">
         <v>8201</v>
       </c>
-      <c r="C8" s="108">
+      <c r="C8" s="106">
         <v>10415</v>
       </c>
-      <c r="D8" s="108">
+      <c r="D8" s="106">
         <v>10754</v>
       </c>
-      <c r="E8" s="108">
+      <c r="E8" s="106">
         <v>5134</v>
       </c>
-      <c r="F8" s="108">
+      <c r="F8" s="106">
         <v>9262</v>
       </c>
-      <c r="G8" s="108">
+      <c r="G8" s="106">
         <v>5648</v>
       </c>
-      <c r="H8" s="108">
+      <c r="H8" s="106">
         <v>6731</v>
       </c>
-      <c r="I8" s="108">
+      <c r="I8" s="106">
         <v>8529</v>
       </c>
-      <c r="J8" s="108">
+      <c r="J8" s="106">
         <v>8518</v>
       </c>
-      <c r="K8" s="108">
+      <c r="K8" s="106">
         <v>7593</v>
       </c>
-      <c r="L8" s="108">
+      <c r="L8" s="106">
         <v>8192</v>
       </c>
     </row>
     <row r="9" spans="1:12">
-      <c r="A9" s="108">
+      <c r="A9" s="106">
         <v>6422</v>
       </c>
-      <c r="B9" s="108">
+      <c r="B9" s="106">
         <v>8750</v>
       </c>
-      <c r="C9" s="108">
+      <c r="C9" s="106">
         <v>6679</v>
       </c>
-      <c r="D9" s="108">
+      <c r="D9" s="106">
         <v>6913</v>
       </c>
-      <c r="E9" s="108">
+      <c r="E9" s="106">
         <v>9010</v>
       </c>
-      <c r="F9" s="108">
+      <c r="F9" s="106">
         <v>9361</v>
       </c>
-      <c r="G9" s="108">
+      <c r="G9" s="106">
         <v>6262</v>
       </c>
-      <c r="H9" s="108">
+      <c r="H9" s="106">
         <v>6368</v>
       </c>
-      <c r="I9" s="108">
+      <c r="I9" s="106">
         <v>8294</v>
       </c>
-      <c r="J9" s="108">
+      <c r="J9" s="106">
         <v>6223</v>
       </c>
-      <c r="K9" s="108">
+      <c r="K9" s="106">
         <v>7005</v>
       </c>
-      <c r="L9" s="108">
+      <c r="L9" s="106">
         <v>10495</v>
       </c>
     </row>
     <row r="10" spans="1:12">
-      <c r="A10" s="108">
+      <c r="A10" s="106">
         <v>9808</v>
       </c>
-      <c r="B10" s="108">
+      <c r="B10" s="106">
         <v>5900</v>
       </c>
-      <c r="C10" s="108">
+      <c r="C10" s="106">
         <v>6554</v>
       </c>
-      <c r="D10" s="108">
+      <c r="D10" s="106">
         <v>8031</v>
       </c>
-      <c r="E10" s="108">
+      <c r="E10" s="106">
         <v>8231</v>
       </c>
-      <c r="F10" s="108">
+      <c r="F10" s="106">
         <v>9168</v>
       </c>
-      <c r="G10" s="108">
+      <c r="G10" s="106">
         <v>8678</v>
       </c>
-      <c r="H10" s="108">
+      <c r="H10" s="106">
         <v>8897</v>
       </c>
-      <c r="I10" s="108">
+      <c r="I10" s="106">
         <v>10017</v>
       </c>
-      <c r="J10" s="108">
+      <c r="J10" s="106">
         <v>6377</v>
       </c>
-      <c r="K10" s="108">
+      <c r="K10" s="106">
         <v>10319</v>
       </c>
-      <c r="L10" s="108">
+      <c r="L10" s="106">
         <v>9520</v>
       </c>
     </row>
     <row r="11" spans="1:12">
-      <c r="A11" s="108">
+      <c r="A11" s="106">
         <v>8884</v>
       </c>
-      <c r="B11" s="108">
+      <c r="B11" s="106">
         <v>8988</v>
       </c>
-      <c r="C11" s="108">
+      <c r="C11" s="106">
         <v>5520</v>
       </c>
-      <c r="D11" s="108">
+      <c r="D11" s="106">
         <v>8825</v>
       </c>
-      <c r="E11" s="108">
+      <c r="E11" s="106">
         <v>5522</v>
       </c>
-      <c r="F11" s="108">
+      <c r="F11" s="106">
         <v>5812</v>
       </c>
-      <c r="G11" s="108">
+      <c r="G11" s="106">
         <v>9472</v>
       </c>
-      <c r="H11" s="108">
+      <c r="H11" s="106">
         <v>8465</v>
       </c>
-      <c r="I11" s="108">
+      <c r="I11" s="106">
         <v>8909</v>
       </c>
-      <c r="J11" s="108">
+      <c r="J11" s="106">
         <v>7298</v>
       </c>
-      <c r="K11" s="108">
+      <c r="K11" s="106">
         <v>7283</v>
       </c>
-      <c r="L11" s="108">
+      <c r="L11" s="106">
         <v>7809</v>
       </c>
     </row>
     <row r="12" spans="1:12">
-      <c r="A12" s="108">
+      <c r="A12" s="106">
         <v>6147</v>
       </c>
-      <c r="B12" s="108">
+      <c r="B12" s="106">
         <v>6025</v>
       </c>
-      <c r="C12" s="108">
+      <c r="C12" s="106">
         <v>8787</v>
       </c>
-      <c r="D12" s="108">
+      <c r="D12" s="106">
         <v>6796</v>
       </c>
-      <c r="E12" s="108">
+      <c r="E12" s="106">
         <v>5286</v>
       </c>
-      <c r="F12" s="108">
+      <c r="F12" s="106">
         <v>9269</v>
       </c>
-      <c r="G12" s="108">
+      <c r="G12" s="106">
         <v>10571</v>
       </c>
-      <c r="H12" s="108">
+      <c r="H12" s="106">
         <v>6999</v>
       </c>
-      <c r="I12" s="108">
+      <c r="I12" s="106">
         <v>10085</v>
       </c>
-      <c r="J12" s="108">
+      <c r="J12" s="106">
         <v>6163</v>
       </c>
-      <c r="K12" s="108">
+      <c r="K12" s="106">
         <v>9024</v>
       </c>
-      <c r="L12" s="108">
+      <c r="L12" s="106">
         <v>6980</v>
       </c>
     </row>
     <row r="13" spans="1:12">
-      <c r="A13" s="108">
+      <c r="A13" s="106">
         <v>5000</v>
       </c>
-      <c r="B13" s="108">
+      <c r="B13" s="106">
         <v>9513</v>
       </c>
-      <c r="C13" s="108">
+      <c r="C13" s="106">
         <v>9272</v>
       </c>
-      <c r="D13" s="108">
+      <c r="D13" s="106">
         <v>5242</v>
       </c>
-      <c r="E13" s="108">
+      <c r="E13" s="106">
         <v>7492</v>
       </c>
-      <c r="F13" s="108">
+      <c r="F13" s="106">
         <v>6309</v>
       </c>
-      <c r="G13" s="108">
+      <c r="G13" s="106">
         <v>8721</v>
       </c>
-      <c r="H13" s="108">
+      <c r="H13" s="106">
         <v>8409</v>
       </c>
-      <c r="I13" s="108">
+      <c r="I13" s="106">
         <v>7660</v>
       </c>
-      <c r="J13" s="108">
+      <c r="J13" s="106">
         <v>9832</v>
       </c>
-      <c r="K13" s="108">
+      <c r="K13" s="106">
         <v>9017</v>
       </c>
-      <c r="L13" s="108">
+      <c r="L13" s="106">
         <v>5525</v>
       </c>
     </row>
     <row r="14" spans="1:12">
-      <c r="A14" s="108">
+      <c r="A14" s="106">
         <v>6970</v>
       </c>
-      <c r="B14" s="108">
+      <c r="B14" s="106">
         <v>9239</v>
       </c>
-      <c r="C14" s="108">
+      <c r="C14" s="106">
         <v>5181</v>
       </c>
-      <c r="D14" s="108">
+      <c r="D14" s="106">
         <v>10581</v>
       </c>
-      <c r="E14" s="108">
+      <c r="E14" s="106">
         <v>9348</v>
       </c>
-      <c r="F14" s="108">
+      <c r="F14" s="106">
         <v>10450</v>
       </c>
-      <c r="G14" s="108">
+      <c r="G14" s="106">
         <v>8428</v>
       </c>
-      <c r="H14" s="108">
+      <c r="H14" s="106">
         <v>5009</v>
       </c>
-      <c r="I14" s="108">
+      <c r="I14" s="106">
         <v>6717</v>
       </c>
-      <c r="J14" s="108">
+      <c r="J14" s="106">
         <v>10855</v>
       </c>
-      <c r="K14" s="108">
+      <c r="K14" s="106">
         <v>10702</v>
       </c>
-      <c r="L14" s="108">
+      <c r="L14" s="106">
         <v>5606</v>
       </c>
     </row>
     <row r="15" spans="1:12">
-      <c r="A15" s="108">
+      <c r="A15" s="106">
         <v>6273</v>
       </c>
-      <c r="B15" s="108">
+      <c r="B15" s="106">
         <v>5430</v>
       </c>
-      <c r="C15" s="108">
+      <c r="C15" s="106">
         <v>8289</v>
       </c>
-      <c r="D15" s="108">
+      <c r="D15" s="106">
         <v>10612</v>
       </c>
-      <c r="E15" s="108">
+      <c r="E15" s="106">
         <v>8322</v>
       </c>
-      <c r="F15" s="108">
+      <c r="F15" s="106">
         <v>7308</v>
       </c>
-      <c r="G15" s="108">
+      <c r="G15" s="106">
         <v>7147</v>
       </c>
-      <c r="H15" s="108">
+      <c r="H15" s="106">
         <v>8587</v>
       </c>
-      <c r="I15" s="108">
+      <c r="I15" s="106">
         <v>8432</v>
       </c>
-      <c r="J15" s="108">
+      <c r="J15" s="106">
         <v>8694</v>
       </c>
-      <c r="K15" s="108">
+      <c r="K15" s="106">
         <v>10120</v>
       </c>
-      <c r="L15" s="108">
+      <c r="L15" s="106">
         <v>10544</v>
       </c>
     </row>
     <row r="16" spans="1:12">
-      <c r="A16" s="108">
+      <c r="A16" s="106">
         <v>7001</v>
       </c>
-      <c r="B16" s="108">
+      <c r="B16" s="106">
         <v>9938</v>
       </c>
-      <c r="C16" s="108">
+      <c r="C16" s="106">
         <v>5568</v>
       </c>
-      <c r="D16" s="108">
+      <c r="D16" s="106">
         <v>5034</v>
       </c>
-      <c r="E16" s="108">
+      <c r="E16" s="106">
         <v>8396</v>
       </c>
-      <c r="F16" s="108">
+      <c r="F16" s="106">
         <v>10063</v>
       </c>
-      <c r="G16" s="108">
+      <c r="G16" s="106">
         <v>10443</v>
       </c>
-      <c r="H16" s="108">
+      <c r="H16" s="106">
         <v>8114</v>
       </c>
-      <c r="I16" s="108">
+      <c r="I16" s="106">
         <v>8211</v>
       </c>
-      <c r="J16" s="108">
+      <c r="J16" s="106">
         <v>10696</v>
       </c>
-      <c r="K16" s="108">
+      <c r="K16" s="106">
         <v>9500</v>
       </c>
-      <c r="L16" s="108">
+      <c r="L16" s="106">
         <v>8350</v>
       </c>
     </row>
     <row r="17" spans="1:12">
-      <c r="A17" s="108">
+      <c r="A17" s="106">
         <v>6653</v>
       </c>
-      <c r="B17" s="108">
+      <c r="B17" s="106">
         <v>6483</v>
       </c>
-      <c r="C17" s="108">
+      <c r="C17" s="106">
         <v>6388</v>
       </c>
-      <c r="D17" s="108">
+      <c r="D17" s="106">
         <v>6938</v>
       </c>
-      <c r="E17" s="108">
+      <c r="E17" s="106">
         <v>9610</v>
       </c>
-      <c r="F17" s="108">
+      <c r="F17" s="106">
         <v>9826</v>
       </c>
-      <c r="G17" s="108">
+      <c r="G17" s="106">
         <v>8223</v>
       </c>
-      <c r="H17" s="108">
+      <c r="H17" s="106">
         <v>5232</v>
       </c>
-      <c r="I17" s="108">
+      <c r="I17" s="106">
         <v>10847</v>
       </c>
-      <c r="J17" s="108">
+      <c r="J17" s="106">
         <v>5015</v>
       </c>
-      <c r="K17" s="108">
+      <c r="K17" s="106">
         <v>6125</v>
       </c>
-      <c r="L17" s="108">
+      <c r="L17" s="106">
         <v>6869</v>
       </c>
     </row>
     <row r="18" spans="1:12">
-      <c r="A18" s="108">
+      <c r="A18" s="106">
         <v>6600</v>
       </c>
-      <c r="B18" s="108">
+      <c r="B18" s="106">
         <v>5280</v>
       </c>
-      <c r="C18" s="108">
+      <c r="C18" s="106">
         <v>10331</v>
       </c>
-      <c r="D18" s="108">
+      <c r="D18" s="106">
         <v>9594</v>
       </c>
-      <c r="E18" s="108">
+      <c r="E18" s="106">
         <v>8125</v>
       </c>
-      <c r="F18" s="108">
+      <c r="F18" s="106">
         <v>7577</v>
       </c>
-      <c r="G18" s="108">
+      <c r="G18" s="106">
         <v>10658</v>
       </c>
-      <c r="H18" s="108">
+      <c r="H18" s="106">
         <v>8030</v>
       </c>
-      <c r="I18" s="108">
+      <c r="I18" s="106">
         <v>8402</v>
       </c>
-      <c r="J18" s="108">
+      <c r="J18" s="106">
         <v>6372</v>
       </c>
-      <c r="K18" s="108">
+      <c r="K18" s="106">
         <v>10345</v>
       </c>
-      <c r="L18" s="108">
+      <c r="L18" s="106">
         <v>5480</v>
       </c>
     </row>
     <row r="19" spans="1:12">
-      <c r="A19" s="108">
+      <c r="A19" s="106">
         <v>10889</v>
       </c>
-      <c r="B19" s="108">
+      <c r="B19" s="106">
         <v>10349</v>
       </c>
-      <c r="C19" s="108">
+      <c r="C19" s="106">
         <v>9273</v>
       </c>
-      <c r="D19" s="108">
+      <c r="D19" s="106">
         <v>8365</v>
       </c>
-      <c r="E19" s="108">
+      <c r="E19" s="106">
         <v>8120</v>
       </c>
-      <c r="F19" s="108">
+      <c r="F19" s="106">
         <v>5817</v>
       </c>
-      <c r="G19" s="108">
+      <c r="G19" s="106">
         <v>7853</v>
       </c>
-      <c r="H19" s="108">
+      <c r="H19" s="106">
         <v>6668</v>
       </c>
-      <c r="I19" s="108">
+      <c r="I19" s="106">
         <v>8918</v>
       </c>
-      <c r="J19" s="108">
+      <c r="J19" s="106">
         <v>7982</v>
       </c>
-      <c r="K19" s="108">
+      <c r="K19" s="106">
         <v>8951</v>
       </c>
-      <c r="L19" s="108">
+      <c r="L19" s="106">
         <v>10102</v>
       </c>
     </row>
     <row r="20" spans="1:12">
-      <c r="A20" s="108">
+      <c r="A20" s="106">
         <v>9564</v>
       </c>
-      <c r="B20" s="108">
+      <c r="B20" s="106">
         <v>6001</v>
       </c>
-      <c r="C20" s="108">
+      <c r="C20" s="106">
         <v>9006</v>
       </c>
-      <c r="D20" s="108">
+      <c r="D20" s="106">
         <v>9989</v>
       </c>
-      <c r="E20" s="108">
+      <c r="E20" s="106">
         <v>10201</v>
       </c>
-      <c r="F20" s="108">
+      <c r="F20" s="106">
         <v>9303</v>
       </c>
-      <c r="G20" s="108">
+      <c r="G20" s="106">
         <v>6515</v>
       </c>
-      <c r="H20" s="108">
+      <c r="H20" s="106">
         <v>6460</v>
       </c>
-      <c r="I20" s="108">
+      <c r="I20" s="106">
         <v>6466</v>
       </c>
-      <c r="J20" s="108">
+      <c r="J20" s="106">
         <v>5129</v>
       </c>
-      <c r="K20" s="108">
+      <c r="K20" s="106">
         <v>7976</v>
       </c>
-      <c r="L20" s="108">
+      <c r="L20" s="106">
         <v>8941</v>
       </c>
     </row>
     <row r="21" spans="1:12">
-      <c r="A21" s="108">
+      <c r="A21" s="106">
         <v>8082</v>
       </c>
-      <c r="B21" s="108">
+      <c r="B21" s="106">
         <v>8562</v>
       </c>
-      <c r="C21" s="108">
+      <c r="C21" s="106">
         <v>5421</v>
       </c>
-      <c r="D21" s="108">
+      <c r="D21" s="106">
         <v>6095</v>
       </c>
-      <c r="E21" s="108">
+      <c r="E21" s="106">
         <v>10853</v>
       </c>
-      <c r="F21" s="108">
+      <c r="F21" s="106">
         <v>10556</v>
       </c>
-      <c r="G21" s="108">
+      <c r="G21" s="106">
         <v>10823</v>
       </c>
-      <c r="H21" s="108">
+      <c r="H21" s="106">
         <v>7653</v>
       </c>
-      <c r="I21" s="108">
+      <c r="I21" s="106">
         <v>10535</v>
       </c>
-      <c r="J21" s="108">
+      <c r="J21" s="106">
         <v>10693</v>
       </c>
-      <c r="K21" s="108">
+      <c r="K21" s="106">
         <v>9098</v>
       </c>
-      <c r="L21" s="108">
+      <c r="L21" s="106">
         <v>7647</v>
       </c>
     </row>
     <row r="22" spans="1:12">
-      <c r="A22" s="108">
+      <c r="A22" s="106">
         <v>5831</v>
       </c>
-      <c r="B22" s="108">
+      <c r="B22" s="106">
         <v>9564</v>
       </c>
-      <c r="C22" s="108">
+      <c r="C22" s="106">
         <v>6204</v>
       </c>
-      <c r="D22" s="108">
+      <c r="D22" s="106">
         <v>9750</v>
       </c>
-      <c r="E22" s="108">
+      <c r="E22" s="106">
         <v>6835</v>
       </c>
-      <c r="F22" s="108">
+      <c r="F22" s="106">
         <v>6814</v>
       </c>
-      <c r="G22" s="108">
+      <c r="G22" s="106">
         <v>8862</v>
       </c>
-      <c r="H22" s="108">
+      <c r="H22" s="106">
         <v>5928</v>
       </c>
-      <c r="I22" s="108">
+      <c r="I22" s="106">
         <v>8710</v>
       </c>
-      <c r="J22" s="108">
+      <c r="J22" s="106">
         <v>5087</v>
       </c>
-      <c r="K22" s="108">
+      <c r="K22" s="106">
         <v>8656</v>
       </c>
-      <c r="L22" s="108">
+      <c r="L22" s="106">
         <v>7148</v>
       </c>
     </row>
     <row r="23" spans="1:12">
-      <c r="A23" s="108">
+      <c r="A23" s="106">
         <v>5677</v>
       </c>
-      <c r="B23" s="108">
+      <c r="B23" s="106">
         <v>10487</v>
       </c>
-      <c r="C23" s="108">
+      <c r="C23" s="106">
         <v>6848</v>
       </c>
-      <c r="D23" s="108">
+      <c r="D23" s="106">
         <v>10646</v>
       </c>
-      <c r="E23" s="108">
+      <c r="E23" s="106">
         <v>7557</v>
       </c>
-      <c r="F23" s="108">
+      <c r="F23" s="106">
         <v>6390</v>
       </c>
-      <c r="G23" s="108">
+      <c r="G23" s="106">
         <v>10581</v>
       </c>
-      <c r="H23" s="108">
+      <c r="H23" s="106">
         <v>8137</v>
       </c>
-      <c r="I23" s="108">
+      <c r="I23" s="106">
         <v>8313</v>
       </c>
-      <c r="J23" s="108">
+      <c r="J23" s="106">
         <v>7896</v>
       </c>
-      <c r="K23" s="108">
+      <c r="K23" s="106">
         <v>9983</v>
       </c>
-      <c r="L23" s="108">
+      <c r="L23" s="106">
         <v>6373</v>
       </c>
     </row>
     <row r="24" spans="1:12">
-      <c r="A24" s="108">
+      <c r="A24" s="106">
         <v>9478</v>
       </c>
-      <c r="B24" s="108">
+      <c r="B24" s="106">
         <v>8797</v>
       </c>
-      <c r="C24" s="108">
+      <c r="C24" s="106">
         <v>5542</v>
       </c>
-      <c r="D24" s="108">
+      <c r="D24" s="106">
         <v>8969</v>
       </c>
-      <c r="E24" s="108">
+      <c r="E24" s="106">
         <v>5056</v>
       </c>
-      <c r="F24" s="108">
+      <c r="F24" s="106">
         <v>8407</v>
       </c>
-      <c r="G24" s="108">
+      <c r="G24" s="106">
         <v>8940</v>
       </c>
-      <c r="H24" s="108">
+      <c r="H24" s="106">
         <v>8411</v>
       </c>
-      <c r="I24" s="108">
+      <c r="I24" s="106">
         <v>10406</v>
       </c>
-      <c r="J24" s="108">
+      <c r="J24" s="106">
         <v>9858</v>
       </c>
-      <c r="K24" s="108">
+      <c r="K24" s="106">
         <v>6926</v>
       </c>
-      <c r="L24" s="108">
+      <c r="L24" s="106">
         <v>9089</v>
       </c>
     </row>
     <row r="25" spans="1:12">
-      <c r="A25" s="108">
+      <c r="A25" s="106">
         <v>6859</v>
       </c>
-      <c r="B25" s="108">
+      <c r="B25" s="106">
         <v>9917</v>
       </c>
-      <c r="C25" s="108">
+      <c r="C25" s="106">
         <v>7619</v>
       </c>
-      <c r="D25" s="108">
+      <c r="D25" s="106">
         <v>7734</v>
       </c>
-      <c r="E25" s="108">
+      <c r="E25" s="106">
         <v>6525</v>
       </c>
-      <c r="F25" s="108">
+      <c r="F25" s="106">
         <v>9793</v>
       </c>
-      <c r="G25" s="108">
+      <c r="G25" s="106">
         <v>7033</v>
       </c>
-      <c r="H25" s="108">
+      <c r="H25" s="106">
         <v>6777</v>
       </c>
-      <c r="I25" s="108">
+      <c r="I25" s="106">
         <v>10766</v>
       </c>
-      <c r="J25" s="108">
+      <c r="J25" s="106">
         <v>10046</v>
       </c>
-      <c r="K25" s="108">
+      <c r="K25" s="106">
         <v>9938</v>
       </c>
-      <c r="L25" s="108">
+      <c r="L25" s="106">
         <v>8298</v>
       </c>
     </row>
     <row r="26" spans="1:12">
-      <c r="A26" s="108">
+      <c r="A26" s="106">
         <v>8288</v>
       </c>
-      <c r="B26" s="108">
+      <c r="B26" s="106">
         <v>5945</v>
       </c>
-      <c r="C26" s="108">
+      <c r="C26" s="106">
         <v>7375</v>
       </c>
-      <c r="D26" s="108">
+      <c r="D26" s="106">
         <v>10576</v>
       </c>
-      <c r="E26" s="108">
+      <c r="E26" s="106">
         <v>5915</v>
       </c>
-      <c r="F26" s="108">
+      <c r="F26" s="106">
         <v>9080</v>
       </c>
-      <c r="G26" s="108">
+      <c r="G26" s="106">
         <v>9214</v>
       </c>
-      <c r="H26" s="108">
+      <c r="H26" s="106">
         <v>8065</v>
       </c>
-      <c r="I26" s="108">
+      <c r="I26" s="106">
         <v>7026</v>
       </c>
-      <c r="J26" s="108">
+      <c r="J26" s="106">
         <v>6991</v>
       </c>
-      <c r="K26" s="108">
+      <c r="K26" s="106">
         <v>5121</v>
       </c>
-      <c r="L26" s="108">
+      <c r="L26" s="106">
         <v>7195</v>
       </c>
     </row>
     <row r="27" spans="1:12">
-      <c r="A27" s="108">
+      <c r="A27" s="106">
         <v>9669</v>
       </c>
-      <c r="B27" s="108">
+      <c r="B27" s="106">
         <v>7469</v>
       </c>
-      <c r="C27" s="108">
+      <c r="C27" s="106">
         <v>9715</v>
       </c>
-      <c r="D27" s="108">
+      <c r="D27" s="106">
         <v>10633</v>
       </c>
-      <c r="E27" s="108">
+      <c r="E27" s="106">
         <v>5135</v>
       </c>
-      <c r="F27" s="108">
+      <c r="F27" s="106">
         <v>7888</v>
       </c>
-      <c r="G27" s="108">
+      <c r="G27" s="106">
         <v>8621</v>
       </c>
-      <c r="H27" s="108">
+      <c r="H27" s="106">
         <v>6117</v>
       </c>
-      <c r="I27" s="108">
+      <c r="I27" s="106">
         <v>7201</v>
       </c>
-      <c r="J27" s="108">
+      <c r="J27" s="106">
         <v>10343</v>
       </c>
-      <c r="K27" s="108">
+      <c r="K27" s="106">
         <v>6098</v>
       </c>
-      <c r="L27" s="108">
+      <c r="L27" s="106">
         <v>6133</v>
       </c>
     </row>
     <row r="28" spans="1:12">
-      <c r="A28" s="108">
+      <c r="A28" s="106">
         <v>10725</v>
       </c>
-      <c r="B28" s="108">
+      <c r="B28" s="106">
         <v>8769</v>
       </c>
-      <c r="C28" s="108">
+      <c r="C28" s="106">
         <v>8528</v>
       </c>
-      <c r="D28" s="108">
+      <c r="D28" s="106">
         <v>10395</v>
       </c>
-      <c r="E28" s="108">
+      <c r="E28" s="106">
         <v>10712</v>
       </c>
-      <c r="F28" s="108">
+      <c r="F28" s="106">
         <v>10709</v>
       </c>
-      <c r="G28" s="108">
+      <c r="G28" s="106">
         <v>5323</v>
       </c>
-      <c r="H28" s="108">
+      <c r="H28" s="106">
         <v>6036</v>
       </c>
-      <c r="I28" s="108">
+      <c r="I28" s="106">
         <v>8737</v>
       </c>
-      <c r="J28" s="108">
+      <c r="J28" s="106">
         <v>10579</v>
       </c>
-      <c r="K28" s="108">
+      <c r="K28" s="106">
         <v>8188</v>
       </c>
-      <c r="L28" s="108">
+      <c r="L28" s="106">
         <v>9057</v>
       </c>
     </row>
     <row r="29" spans="1:12">
-      <c r="A29" s="108">
+      <c r="A29" s="106">
         <v>7803</v>
       </c>
-      <c r="B29" s="108">
+      <c r="B29" s="106">
         <v>8620</v>
       </c>
-      <c r="C29" s="108">
+      <c r="C29" s="106">
         <v>5792</v>
       </c>
-      <c r="D29" s="108">
+      <c r="D29" s="106">
         <v>7557</v>
       </c>
-      <c r="E29" s="108">
+      <c r="E29" s="106">
         <v>8041</v>
       </c>
-      <c r="F29" s="108">
+      <c r="F29" s="106">
         <v>8900</v>
       </c>
-      <c r="G29" s="108">
+      <c r="G29" s="106">
         <v>5315</v>
       </c>
-      <c r="H29" s="108">
+      <c r="H29" s="106">
         <v>5582</v>
       </c>
-      <c r="I29" s="108">
+      <c r="I29" s="106">
         <v>8763</v>
       </c>
-      <c r="J29" s="108">
+      <c r="J29" s="106">
         <v>10205</v>
       </c>
-      <c r="K29" s="108">
+      <c r="K29" s="106">
         <v>5407</v>
       </c>
-      <c r="L29" s="108">
+      <c r="L29" s="106">
         <v>8462</v>
       </c>
     </row>
     <row r="30" spans="1:12">
-      <c r="A30" s="108">
+      <c r="A30" s="106">
         <v>5955</v>
       </c>
-      <c r="B30" s="108">
+      <c r="B30" s="106">
         <v>9963</v>
       </c>
-      <c r="C30" s="108">
+      <c r="C30" s="106">
         <v>10361</v>
       </c>
-      <c r="D30" s="108">
+      <c r="D30" s="106">
         <v>8478</v>
       </c>
-      <c r="E30" s="108">
+      <c r="E30" s="106">
         <v>10925</v>
       </c>
-      <c r="F30" s="108">
+      <c r="F30" s="106">
         <v>8152</v>
       </c>
-      <c r="G30" s="108">
+      <c r="G30" s="106">
         <v>8468</v>
       </c>
-      <c r="H30" s="108">
+      <c r="H30" s="106">
         <v>10058</v>
       </c>
-      <c r="I30" s="108">
+      <c r="I30" s="106">
         <v>9755</v>
       </c>
-      <c r="J30" s="108">
+      <c r="J30" s="106">
         <v>9742</v>
       </c>
-      <c r="K30" s="108">
+      <c r="K30" s="106">
         <v>6815</v>
       </c>
-      <c r="L30" s="108">
+      <c r="L30" s="106">
         <v>5824</v>
       </c>
     </row>
     <row r="31" spans="1:12">
-      <c r="A31" s="108">
+      <c r="A31" s="106">
         <v>9067</v>
       </c>
-      <c r="B31" s="108">
+      <c r="B31" s="106">
         <v>9963</v>
       </c>
-      <c r="C31" s="108">
+      <c r="C31" s="106">
         <v>9323</v>
       </c>
-      <c r="D31" s="108">
+      <c r="D31" s="106">
         <v>10270</v>
       </c>
-      <c r="E31" s="108">
+      <c r="E31" s="106">
         <v>7507</v>
       </c>
-      <c r="F31" s="108">
+      <c r="F31" s="106">
         <v>9542</v>
       </c>
-      <c r="G31" s="108">
+      <c r="G31" s="106">
         <v>10199</v>
       </c>
-      <c r="H31" s="108">
+      <c r="H31" s="106">
         <v>5233</v>
       </c>
-      <c r="I31" s="108">
+      <c r="I31" s="106">
         <v>8017</v>
       </c>
-      <c r="J31" s="108">
+      <c r="J31" s="106">
         <v>6163</v>
       </c>
-      <c r="K31" s="108">
+      <c r="K31" s="106">
         <v>9665</v>
       </c>
-      <c r="L31" s="108">
+      <c r="L31" s="106">
         <v>7921</v>
       </c>
     </row>
     <row r="32" spans="1:12">
-      <c r="A32" s="108">
+      <c r="A32" s="106">
         <v>10099</v>
       </c>
-      <c r="B32" s="108">
+      <c r="B32" s="106">
         <v>5820</v>
       </c>
-      <c r="C32" s="108">
+      <c r="C32" s="106">
         <v>7802</v>
       </c>
-      <c r="D32" s="108">
+      <c r="D32" s="106">
         <v>10962</v>
       </c>
-      <c r="E32" s="108">
+      <c r="E32" s="106">
         <v>9983</v>
       </c>
-      <c r="F32" s="108">
+      <c r="F32" s="106">
         <v>5911</v>
       </c>
-      <c r="G32" s="108">
+      <c r="G32" s="106">
         <v>10803</v>
       </c>
-      <c r="H32" s="108">
+      <c r="H32" s="106">
         <v>8710</v>
       </c>
-      <c r="I32" s="108">
+      <c r="I32" s="106">
         <v>6103</v>
       </c>
-      <c r="J32" s="108">
+      <c r="J32" s="106">
         <v>9535</v>
       </c>
-      <c r="K32" s="108">
+      <c r="K32" s="106">
         <v>6056</v>
       </c>
-      <c r="L32" s="108">
+      <c r="L32" s="106">
         <v>8117</v>
       </c>
     </row>
     <row r="33" spans="1:12">
-      <c r="A33" s="108">
+      <c r="A33" s="106">
         <v>6723</v>
       </c>
-      <c r="B33" s="108">
+      <c r="B33" s="106">
         <v>8518</v>
       </c>
-      <c r="C33" s="108">
+      <c r="C33" s="106">
         <v>5653</v>
       </c>
-      <c r="D33" s="108">
+      <c r="D33" s="106">
         <v>8361</v>
       </c>
-      <c r="E33" s="108">
+      <c r="E33" s="106">
         <v>7281</v>
       </c>
-      <c r="F33" s="108">
+      <c r="F33" s="106">
         <v>6605</v>
       </c>
-      <c r="G33" s="108">
+      <c r="G33" s="106">
         <v>6285</v>
       </c>
-      <c r="H33" s="108">
+      <c r="H33" s="106">
         <v>9135</v>
       </c>
-      <c r="I33" s="108">
+      <c r="I33" s="106">
         <v>5703</v>
       </c>
-      <c r="J33" s="108">
+      <c r="J33" s="106">
         <v>5288</v>
       </c>
-      <c r="K33" s="108">
+      <c r="K33" s="106">
         <v>10974</v>
       </c>
-      <c r="L33" s="108">
+      <c r="L33" s="106">
         <v>5193</v>
       </c>
     </row>
     <row r="34" spans="1:12">
-      <c r="A34" s="108">
+      <c r="A34" s="106">
         <v>7207</v>
       </c>
-      <c r="B34" s="108">
+      <c r="B34" s="106">
         <v>5930</v>
       </c>
-      <c r="C34" s="108">
+      <c r="C34" s="106">
         <v>8186</v>
       </c>
-      <c r="D34" s="108">
+      <c r="D34" s="106">
         <v>7540</v>
       </c>
-      <c r="E34" s="108">
+      <c r="E34" s="106">
         <v>7646</v>
       </c>
-      <c r="F34" s="108">
+      <c r="F34" s="106">
         <v>10343</v>
       </c>
-      <c r="G34" s="108">
+      <c r="G34" s="106">
         <v>7318</v>
       </c>
-      <c r="H34" s="108">
+      <c r="H34" s="106">
         <v>10269</v>
       </c>
-      <c r="I34" s="108">
+      <c r="I34" s="106">
         <v>8261</v>
       </c>
-      <c r="J34" s="108">
+      <c r="J34" s="106">
         <v>9231</v>
       </c>
-      <c r="K34" s="108">
+      <c r="K34" s="106">
         <v>6262</v>
       </c>
-      <c r="L34" s="108">
+      <c r="L34" s="106">
         <v>8783</v>
       </c>
     </row>
     <row r="35" spans="1:12">
-      <c r="A35" s="108">
+      <c r="A35" s="106">
         <v>10694</v>
       </c>
-      <c r="B35" s="108">
+      <c r="B35" s="106">
         <v>6816</v>
       </c>
-      <c r="C35" s="108">
+      <c r="C35" s="106">
         <v>7906</v>
       </c>
-      <c r="D35" s="108">
+      <c r="D35" s="106">
         <v>6746</v>
       </c>
-      <c r="E35" s="108">
+      <c r="E35" s="106">
         <v>8555</v>
       </c>
-      <c r="F35" s="108">
+      <c r="F35" s="106">
         <v>9635</v>
       </c>
-      <c r="G35" s="108">
+      <c r="G35" s="106">
         <v>5324</v>
       </c>
-      <c r="H35" s="108">
+      <c r="H35" s="106">
         <v>10640</v>
       </c>
-      <c r="I35" s="108">
+      <c r="I35" s="106">
         <v>8480</v>
       </c>
-      <c r="J35" s="108">
+      <c r="J35" s="106">
         <v>9433</v>
       </c>
-      <c r="K35" s="108">
+      <c r="K35" s="106">
         <v>5078</v>
       </c>
-      <c r="L35" s="108">
+      <c r="L35" s="106">
         <v>6709</v>
       </c>
     </row>
     <row r="36" spans="1:12">
-      <c r="A36" s="108">
+      <c r="A36" s="106">
         <v>9856</v>
       </c>
-      <c r="B36" s="108">
+      <c r="B36" s="106">
         <v>6677</v>
       </c>
-      <c r="C36" s="108">
+      <c r="C36" s="106">
         <v>6320</v>
       </c>
-      <c r="D36" s="108">
+      <c r="D36" s="106">
         <v>10218</v>
       </c>
-      <c r="E36" s="108">
+      <c r="E36" s="106">
         <v>10143</v>
       </c>
-      <c r="F36" s="108">
+      <c r="F36" s="106">
         <v>10677</v>
       </c>
-      <c r="G36" s="108">
+      <c r="G36" s="106">
         <v>10932</v>
       </c>
-      <c r="H36" s="108">
+      <c r="H36" s="106">
         <v>7506</v>
       </c>
-      <c r="I36" s="108">
+      <c r="I36" s="106">
         <v>5781</v>
       </c>
-      <c r="J36" s="108">
+      <c r="J36" s="106">
         <v>8607</v>
       </c>
-      <c r="K36" s="108">
+      <c r="K36" s="106">
         <v>5302</v>
       </c>
-      <c r="L36" s="108">
+      <c r="L36" s="106">
         <v>6566</v>
       </c>
     </row>
     <row r="37" spans="1:12">
-      <c r="A37" s="108">
+      <c r="A37" s="106">
         <v>5839</v>
       </c>
-      <c r="B37" s="108">
+      <c r="B37" s="106">
         <v>9320</v>
       </c>
-      <c r="C37" s="108">
+      <c r="C37" s="106">
         <v>7714</v>
       </c>
-      <c r="D37" s="108">
+      <c r="D37" s="106">
         <v>10772</v>
       </c>
-      <c r="E37" s="108">
+      <c r="E37" s="106">
         <v>9676</v>
       </c>
-      <c r="F37" s="108">
+      <c r="F37" s="106">
         <v>7711</v>
       </c>
-      <c r="G37" s="108">
+      <c r="G37" s="106">
         <v>10201</v>
       </c>
-      <c r="H37" s="108">
+      <c r="H37" s="106">
         <v>7722</v>
       </c>
-      <c r="I37" s="108">
+      <c r="I37" s="106">
         <v>10587</v>
       </c>
-      <c r="J37" s="108">
+      <c r="J37" s="106">
         <v>10056</v>
       </c>
-      <c r="K37" s="108">
+      <c r="K37" s="106">
         <v>6142</v>
       </c>
-      <c r="L37" s="108">
+      <c r="L37" s="106">
         <v>5635</v>
       </c>
     </row>
     <row r="38" spans="1:12">
-      <c r="A38" s="108">
+      <c r="A38" s="106">
         <v>8767</v>
       </c>
-      <c r="B38" s="108">
+      <c r="B38" s="106">
         <v>5606</v>
       </c>
-      <c r="C38" s="108">
+      <c r="C38" s="106">
         <v>8493</v>
       </c>
-      <c r="D38" s="108">
+      <c r="D38" s="106">
         <v>6999</v>
       </c>
-      <c r="E38" s="108">
+      <c r="E38" s="106">
         <v>10751</v>
       </c>
-      <c r="F38" s="108">
+      <c r="F38" s="106">
         <v>5093</v>
       </c>
-      <c r="G38" s="108">
+      <c r="G38" s="106">
         <v>5923</v>
       </c>
-      <c r="H38" s="108">
+      <c r="H38" s="106">
         <v>7325</v>
       </c>
-      <c r="I38" s="108">
+      <c r="I38" s="106">
         <v>7753</v>
       </c>
-      <c r="J38" s="108">
+      <c r="J38" s="106">
         <v>5402</v>
       </c>
-      <c r="K38" s="108">
+      <c r="K38" s="106">
         <v>6531</v>
       </c>
-      <c r="L38" s="108">
+      <c r="L38" s="106">
         <v>6653</v>
       </c>
     </row>
     <row r="39" spans="1:12">
-      <c r="A39" s="108">
+      <c r="A39" s="106">
         <v>5527</v>
       </c>
-      <c r="B39" s="108">
+      <c r="B39" s="106">
         <v>6553</v>
       </c>
-      <c r="C39" s="108">
+      <c r="C39" s="106">
         <v>5506</v>
       </c>
-      <c r="D39" s="108">
+      <c r="D39" s="106">
         <v>5356</v>
       </c>
-      <c r="E39" s="108">
+      <c r="E39" s="106">
         <v>7604</v>
       </c>
-      <c r="F39" s="108">
+      <c r="F39" s="106">
         <v>8403</v>
       </c>
-      <c r="G39" s="108">
+      <c r="G39" s="106">
         <v>7412</v>
       </c>
-      <c r="H39" s="108">
+      <c r="H39" s="106">
         <v>10653</v>
       </c>
-      <c r="I39" s="108">
+      <c r="I39" s="106">
         <v>10499</v>
       </c>
-      <c r="J39" s="108">
+      <c r="J39" s="106">
         <v>9016</v>
       </c>
-      <c r="K39" s="108">
+      <c r="K39" s="106">
         <v>6178</v>
       </c>
-      <c r="L39" s="108">
+      <c r="L39" s="106">
         <v>9519</v>
       </c>
     </row>
     <row r="40" spans="1:12">
-      <c r="A40" s="108">
+      <c r="A40" s="106">
         <v>10380</v>
       </c>
-      <c r="B40" s="108">
+      <c r="B40" s="106">
         <v>10553</v>
       </c>
-      <c r="C40" s="108">
+      <c r="C40" s="106">
         <v>9508</v>
       </c>
-      <c r="D40" s="108">
+      <c r="D40" s="106">
         <v>5176</v>
       </c>
-      <c r="E40" s="108">
+      <c r="E40" s="106">
         <v>5568</v>
       </c>
-      <c r="F40" s="108">
+      <c r="F40" s="106">
         <v>7057</v>
       </c>
-      <c r="G40" s="108">
+      <c r="G40" s="106">
         <v>6104</v>
       </c>
-      <c r="H40" s="108">
+      <c r="H40" s="106">
         <v>8382</v>
       </c>
-      <c r="I40" s="108">
+      <c r="I40" s="106">
         <v>6503</v>
       </c>
-      <c r="J40" s="108">
+      <c r="J40" s="106">
         <v>5257</v>
       </c>
-      <c r="K40" s="108">
+      <c r="K40" s="106">
         <v>9170</v>
       </c>
-      <c r="L40" s="108">
+      <c r="L40" s="106">
         <v>10531</v>
       </c>
     </row>
     <row r="41" spans="1:12">
-      <c r="A41" s="108">
+      <c r="A41" s="106">
         <v>8687</v>
       </c>
-      <c r="B41" s="108">
+      <c r="B41" s="106">
         <v>5385</v>
       </c>
-      <c r="C41" s="108">
+      <c r="C41" s="106">
         <v>5803</v>
       </c>
-      <c r="D41" s="108">
+      <c r="D41" s="106">
         <v>8389</v>
       </c>
-      <c r="E41" s="108">
+      <c r="E41" s="106">
         <v>5721</v>
       </c>
-      <c r="F41" s="108">
+      <c r="F41" s="106">
         <v>10325</v>
       </c>
-      <c r="G41" s="108">
+      <c r="G41" s="106">
         <v>9424</v>
       </c>
-      <c r="H41" s="108">
+      <c r="H41" s="106">
         <v>8919</v>
       </c>
-      <c r="I41" s="108">
+      <c r="I41" s="106">
         <v>5596</v>
       </c>
-      <c r="J41" s="108">
+      <c r="J41" s="106">
         <v>10318</v>
       </c>
-      <c r="K41" s="108">
+      <c r="K41" s="106">
         <v>5455</v>
       </c>
-      <c r="L41" s="108">
+      <c r="L41" s="106">
         <v>9570</v>
       </c>
     </row>
     <row r="42" spans="1:12">
-      <c r="A42" s="108">
+      <c r="A42" s="106">
         <v>7862</v>
       </c>
-      <c r="B42" s="108">
+      <c r="B42" s="106">
         <v>10443</v>
       </c>
-      <c r="C42" s="108">
+      <c r="C42" s="106">
         <v>9210</v>
       </c>
-      <c r="D42" s="108">
+      <c r="D42" s="106">
         <v>5633</v>
       </c>
-      <c r="E42" s="108">
+      <c r="E42" s="106">
         <v>10208</v>
       </c>
-      <c r="F42" s="108">
+      <c r="F42" s="106">
         <v>8908</v>
       </c>
-      <c r="G42" s="108">
+      <c r="G42" s="106">
         <v>8957</v>
       </c>
-      <c r="H42" s="108">
+      <c r="H42" s="106">
         <v>5358</v>
       </c>
-      <c r="I42" s="108">
+      <c r="I42" s="106">
         <v>5199</v>
       </c>
-      <c r="J42" s="108">
+      <c r="J42" s="106">
         <v>8822</v>
       </c>
-      <c r="K42" s="108">
+      <c r="K42" s="106">
         <v>5698</v>
       </c>
-      <c r="L42" s="108">
+      <c r="L42" s="106">
         <v>5152</v>
       </c>
     </row>
     <row r="43" spans="1:12">
-      <c r="A43" s="108">
+      <c r="A43" s="106">
         <v>5622</v>
       </c>
-      <c r="B43" s="108">
+      <c r="B43" s="106">
         <v>10077</v>
       </c>
-      <c r="C43" s="108">
+      <c r="C43" s="106">
         <v>10398</v>
       </c>
-      <c r="D43" s="108">
+      <c r="D43" s="106">
         <v>8886</v>
       </c>
-      <c r="E43" s="108">
+      <c r="E43" s="106">
         <v>7422</v>
       </c>
-      <c r="F43" s="108">
+      <c r="F43" s="106">
         <v>6182</v>
       </c>
-      <c r="G43" s="108">
+      <c r="G43" s="106">
         <v>10160</v>
       </c>
-      <c r="H43" s="108">
+      <c r="H43" s="106">
         <v>10709</v>
       </c>
-      <c r="I43" s="108">
+      <c r="I43" s="106">
         <v>10829</v>
       </c>
-      <c r="J43" s="108">
+      <c r="J43" s="106">
         <v>9018</v>
       </c>
-      <c r="K43" s="108">
+      <c r="K43" s="106">
         <v>10974</v>
       </c>
-      <c r="L43" s="108">
+      <c r="L43" s="106">
         <v>5576</v>
       </c>
     </row>
     <row r="44" spans="1:12">
-      <c r="A44" s="108">
+      <c r="A44" s="106">
         <v>8316</v>
       </c>
-      <c r="B44" s="108">
+      <c r="B44" s="106">
         <v>9216</v>
       </c>
-      <c r="C44" s="108">
+      <c r="C44" s="106">
         <v>7441</v>
       </c>
-      <c r="D44" s="108">
+      <c r="D44" s="106">
         <v>6054</v>
       </c>
-      <c r="E44" s="108">
+      <c r="E44" s="106">
         <v>9222</v>
       </c>
-      <c r="F44" s="108">
+      <c r="F44" s="106">
         <v>6135</v>
       </c>
-      <c r="G44" s="108">
+      <c r="G44" s="106">
         <v>6539</v>
       </c>
-      <c r="H44" s="108">
+      <c r="H44" s="106">
         <v>6065</v>
       </c>
-      <c r="I44" s="108">
+      <c r="I44" s="106">
         <v>5267</v>
       </c>
-      <c r="J44" s="108">
+      <c r="J44" s="106">
         <v>5043</v>
       </c>
-      <c r="K44" s="108">
+      <c r="K44" s="106">
         <v>8933</v>
       </c>
-      <c r="L44" s="108">
+      <c r="L44" s="106">
         <v>7704</v>
       </c>
     </row>
     <row r="45" spans="1:12">
-      <c r="A45" s="108">
+      <c r="A45" s="106">
         <v>6577</v>
       </c>
-      <c r="B45" s="108">
+      <c r="B45" s="106">
         <v>10584</v>
       </c>
-      <c r="C45" s="108">
+      <c r="C45" s="106">
         <v>9889</v>
       </c>
-      <c r="D45" s="108">
+      <c r="D45" s="106">
         <v>9061</v>
       </c>
-      <c r="E45" s="108">
+      <c r="E45" s="106">
         <v>5038</v>
       </c>
-      <c r="F45" s="108">
+      <c r="F45" s="106">
         <v>8350</v>
       </c>
-      <c r="G45" s="108">
+      <c r="G45" s="106">
         <v>10187</v>
       </c>
-      <c r="H45" s="108">
+      <c r="H45" s="106">
         <v>10585</v>
       </c>
-      <c r="I45" s="108">
+      <c r="I45" s="106">
         <v>5242</v>
       </c>
-      <c r="J45" s="108">
+      <c r="J45" s="106">
         <v>7416</v>
       </c>
-      <c r="K45" s="108">
+      <c r="K45" s="106">
         <v>8290</v>
       </c>
-      <c r="L45" s="108">
+      <c r="L45" s="106">
         <v>8367</v>
       </c>
     </row>
     <row r="46" spans="1:12">
-      <c r="A46" s="108">
+      <c r="A46" s="106">
         <v>5783</v>
       </c>
-      <c r="B46" s="108">
+      <c r="B46" s="106">
         <v>5431</v>
       </c>
-      <c r="C46" s="108">
+      <c r="C46" s="106">
         <v>8667</v>
       </c>
-      <c r="D46" s="108">
+      <c r="D46" s="106">
         <v>10798</v>
       </c>
-      <c r="E46" s="108">
+      <c r="E46" s="106">
         <v>9103</v>
       </c>
-      <c r="F46" s="108">
+      <c r="F46" s="106">
         <v>6088</v>
       </c>
-      <c r="G46" s="108">
+      <c r="G46" s="106">
         <v>7433</v>
       </c>
-      <c r="H46" s="108">
+      <c r="H46" s="106">
         <v>7934</v>
       </c>
-      <c r="I46" s="108">
+      <c r="I46" s="106">
         <v>9899</v>
       </c>
-      <c r="J46" s="108">
+      <c r="J46" s="106">
         <v>10737</v>
       </c>
-      <c r="K46" s="108">
+      <c r="K46" s="106">
         <v>8537</v>
       </c>
-      <c r="L46" s="108">
+      <c r="L46" s="106">
         <v>6871</v>
       </c>
     </row>
     <row r="47" spans="1:12">
-      <c r="A47" s="108">
+      <c r="A47" s="106">
         <v>6085</v>
       </c>
-      <c r="B47" s="108">
+      <c r="B47" s="106">
         <v>5407</v>
       </c>
-      <c r="C47" s="108">
+      <c r="C47" s="106">
         <v>5046</v>
       </c>
-      <c r="D47" s="108">
+      <c r="D47" s="106">
         <v>5715</v>
       </c>
-      <c r="E47" s="108">
+      <c r="E47" s="106">
         <v>5745</v>
       </c>
-      <c r="F47" s="108">
+      <c r="F47" s="106">
         <v>6213</v>
       </c>
-      <c r="G47" s="108">
+      <c r="G47" s="106">
         <v>7689</v>
       </c>
-      <c r="H47" s="108">
+      <c r="H47" s="106">
         <v>9691</v>
       </c>
-      <c r="I47" s="108">
+      <c r="I47" s="106">
         <v>7095</v>
       </c>
-      <c r="J47" s="108">
+      <c r="J47" s="106">
         <v>9151</v>
       </c>
-      <c r="K47" s="108">
+      <c r="K47" s="106">
         <v>7501</v>
       </c>
-      <c r="L47" s="108">
+      <c r="L47" s="106">
         <v>10396</v>
       </c>
     </row>
     <row r="48" spans="1:12">
-      <c r="A48" s="108">
+      <c r="A48" s="106">
         <v>10573</v>
       </c>
-      <c r="B48" s="108">
+      <c r="B48" s="106">
         <v>6705</v>
       </c>
-      <c r="C48" s="108">
+      <c r="C48" s="106">
         <v>7038</v>
       </c>
-      <c r="D48" s="108">
+      <c r="D48" s="106">
         <v>9209</v>
       </c>
-      <c r="E48" s="108">
+      <c r="E48" s="106">
         <v>6971</v>
       </c>
-      <c r="F48" s="108">
+      <c r="F48" s="106">
         <v>6833</v>
       </c>
-      <c r="G48" s="108">
+      <c r="G48" s="106">
         <v>8174</v>
       </c>
-      <c r="H48" s="108">
+      <c r="H48" s="106">
         <v>5169</v>
       </c>
-      <c r="I48" s="108">
+      <c r="I48" s="106">
         <v>9714</v>
       </c>
-      <c r="J48" s="108">
+      <c r="J48" s="106">
         <v>6930</v>
       </c>
-      <c r="K48" s="108">
+      <c r="K48" s="106">
         <v>6941</v>
       </c>
-      <c r="L48" s="108">
+      <c r="L48" s="106">
         <v>6595</v>
       </c>
     </row>
     <row r="49" spans="1:12">
-      <c r="A49" s="108">
+      <c r="A49" s="106">
         <v>10475</v>
       </c>
-      <c r="B49" s="108">
+      <c r="B49" s="106">
         <v>5938</v>
       </c>
-      <c r="C49" s="108">
+      <c r="C49" s="106">
         <v>8564</v>
       </c>
-      <c r="D49" s="108">
+      <c r="D49" s="106">
         <v>6740</v>
       </c>
-      <c r="E49" s="108">
+      <c r="E49" s="106">
         <v>6894</v>
       </c>
-      <c r="F49" s="108">
+      <c r="F49" s="106">
         <v>6488</v>
       </c>
-      <c r="G49" s="108">
+      <c r="G49" s="106">
         <v>10489</v>
       </c>
-      <c r="H49" s="108">
+      <c r="H49" s="106">
         <v>8067</v>
       </c>
-      <c r="I49" s="108">
+      <c r="I49" s="106">
         <v>7002</v>
       </c>
-      <c r="J49" s="108">
+      <c r="J49" s="106">
         <v>10261</v>
       </c>
-      <c r="K49" s="108">
+      <c r="K49" s="106">
         <v>5881</v>
       </c>
-      <c r="L49" s="108">
+      <c r="L49" s="106">
         <v>7296</v>
       </c>
     </row>
     <row r="50" spans="1:12">
-      <c r="A50" s="108">
+      <c r="A50" s="106">
         <v>5893</v>
       </c>
-      <c r="B50" s="108">
+      <c r="B50" s="106">
         <v>7072</v>
       </c>
-      <c r="C50" s="108">
+      <c r="C50" s="106">
         <v>10097</v>
       </c>
-      <c r="D50" s="108">
+      <c r="D50" s="106">
         <v>8190</v>
       </c>
-      <c r="E50" s="108">
+      <c r="E50" s="106">
         <v>6348</v>
       </c>
-      <c r="F50" s="108">
+      <c r="F50" s="106">
         <v>10381</v>
       </c>
-      <c r="G50" s="108">
+      <c r="G50" s="106">
         <v>8656</v>
       </c>
-      <c r="H50" s="108">
+      <c r="H50" s="106">
         <v>10974</v>
       </c>
-      <c r="I50" s="108">
+      <c r="I50" s="106">
         <v>7685</v>
       </c>
-      <c r="J50" s="108">
+      <c r="J50" s="106">
         <v>8039</v>
       </c>
-      <c r="K50" s="108">
+      <c r="K50" s="106">
         <v>5945</v>
       </c>
-      <c r="L50" s="108">
+      <c r="L50" s="106">
         <v>6147</v>
       </c>
     </row>
     <row r="51" spans="1:12">
-      <c r="A51" s="108">
+      <c r="A51" s="106">
         <v>6201</v>
       </c>
-      <c r="B51" s="108">
+      <c r="B51" s="106">
         <v>8515</v>
       </c>
-      <c r="C51" s="108">
+      <c r="C51" s="106">
         <v>8224</v>
       </c>
-      <c r="D51" s="108">
+      <c r="D51" s="106">
         <v>5499</v>
       </c>
-      <c r="E51" s="108">
+      <c r="E51" s="106">
         <v>8892</v>
       </c>
-      <c r="F51" s="108">
+      <c r="F51" s="106">
         <v>6661</v>
       </c>
-      <c r="G51" s="108">
+      <c r="G51" s="106">
         <v>5364</v>
       </c>
-      <c r="H51" s="108">
+      <c r="H51" s="106">
         <v>7057</v>
       </c>
-      <c r="I51" s="108">
+      <c r="I51" s="106">
         <v>9208</v>
       </c>
-      <c r="J51" s="108">
+      <c r="J51" s="106">
         <v>8075</v>
       </c>
-      <c r="K51" s="108">
+      <c r="K51" s="106">
         <v>5149</v>
       </c>
-      <c r="L51" s="108">
+      <c r="L51" s="106">
         <v>5221</v>
       </c>
     </row>
     <row r="52" spans="1:12">
-      <c r="A52" s="108">
+      <c r="A52" s="106">
         <v>5543</v>
       </c>
-      <c r="B52" s="108">
+      <c r="B52" s="106">
         <v>7428</v>
       </c>
-      <c r="C52" s="108">
+      <c r="C52" s="106">
         <v>7400</v>
       </c>
-      <c r="D52" s="108">
+      <c r="D52" s="106">
         <v>6944</v>
       </c>
-      <c r="E52" s="108">
+      <c r="E52" s="106">
         <v>6634</v>
       </c>
-      <c r="F52" s="108">
+      <c r="F52" s="106">
         <v>7560</v>
       </c>
-      <c r="G52" s="108">
+      <c r="G52" s="106">
         <v>9809</v>
       </c>
-      <c r="H52" s="108">
+      <c r="H52" s="106">
         <v>6869</v>
       </c>
-      <c r="I52" s="108">
+      <c r="I52" s="106">
         <v>9620</v>
       </c>
-      <c r="J52" s="108">
+      <c r="J52" s="106">
         <v>8122</v>
       </c>
-      <c r="K52" s="108">
+      <c r="K52" s="106">
         <v>7036</v>
       </c>
-      <c r="L52" s="108">
+      <c r="L52" s="106">
         <v>5462</v>
       </c>
     </row>
     <row r="53" spans="1:12">
-      <c r="A53" s="108">
+      <c r="A53" s="106">
         <v>7199</v>
       </c>
-      <c r="B53" s="108">
+      <c r="B53" s="106">
         <v>10718</v>
       </c>
-      <c r="C53" s="108">
+      <c r="C53" s="106">
         <v>8306</v>
       </c>
-      <c r="D53" s="108">
+      <c r="D53" s="106">
         <v>10986</v>
       </c>
-      <c r="E53" s="108">
+      <c r="E53" s="106">
         <v>7630</v>
       </c>
-      <c r="F53" s="108">
+      <c r="F53" s="106">
         <v>6939</v>
       </c>
-      <c r="G53" s="108">
+      <c r="G53" s="106">
         <v>6492</v>
       </c>
-      <c r="H53" s="108">
+      <c r="H53" s="106">
         <v>6450</v>
       </c>
-      <c r="I53" s="108">
+      <c r="I53" s="106">
         <v>6206</v>
       </c>
-      <c r="J53" s="108">
+      <c r="J53" s="106">
         <v>8209</v>
       </c>
-      <c r="K53" s="108">
+      <c r="K53" s="106">
         <v>9126</v>
       </c>
-      <c r="L53" s="108">
+      <c r="L53" s="106">
         <v>8768</v>
       </c>
     </row>
     <row r="54" spans="1:12">
-      <c r="A54" s="108">
+      <c r="A54" s="106">
         <v>5714</v>
       </c>
-      <c r="B54" s="108">
+      <c r="B54" s="106">
         <v>7847</v>
       </c>
-      <c r="C54" s="108">
+      <c r="C54" s="106">
         <v>10759</v>
       </c>
-      <c r="D54" s="108">
+      <c r="D54" s="106">
         <v>10310</v>
       </c>
-      <c r="E54" s="108">
+      <c r="E54" s="106">
         <v>6089</v>
       </c>
-      <c r="F54" s="108">
+      <c r="F54" s="106">
         <v>8883</v>
       </c>
-      <c r="G54" s="108">
+      <c r="G54" s="106">
         <v>8957</v>
       </c>
-      <c r="H54" s="108">
+      <c r="H54" s="106">
         <v>7882</v>
       </c>
-      <c r="I54" s="108">
+      <c r="I54" s="106">
         <v>7393</v>
       </c>
-      <c r="J54" s="108">
+      <c r="J54" s="106">
         <v>7414</v>
       </c>
-      <c r="K54" s="108">
+      <c r="K54" s="106">
         <v>8610</v>
       </c>
-      <c r="L54" s="108">
+      <c r="L54" s="106">
         <v>6987</v>
       </c>
     </row>
     <row r="55" spans="1:12">
-      <c r="A55" s="108">
+      <c r="A55" s="106">
         <v>5041</v>
       </c>
-      <c r="B55" s="108">
+      <c r="B55" s="106">
         <v>6151</v>
       </c>
-      <c r="C55" s="108">
+      <c r="C55" s="106">
         <v>9561</v>
       </c>
-      <c r="D55" s="108">
+      <c r="D55" s="106">
         <v>10389</v>
       </c>
-      <c r="E55" s="108">
+      <c r="E55" s="106">
         <v>6116</v>
       </c>
-      <c r="F55" s="108">
+      <c r="F55" s="106">
         <v>5689</v>
       </c>
-      <c r="G55" s="108">
+      <c r="G55" s="106">
         <v>7578</v>
       </c>
-      <c r="H55" s="108">
+      <c r="H55" s="106">
         <v>10632</v>
       </c>
-      <c r="I55" s="108">
+      <c r="I55" s="106">
         <v>7232</v>
       </c>
-      <c r="J55" s="108">
+      <c r="J55" s="106">
         <v>5412</v>
       </c>
-      <c r="K55" s="108">
+      <c r="K55" s="106">
         <v>8541</v>
       </c>
-      <c r="L55" s="108">
+      <c r="L55" s="106">
         <v>9035</v>
       </c>
     </row>
     <row r="56" spans="1:12">
-      <c r="A56" s="108">
+      <c r="A56" s="106">
         <v>10940</v>
       </c>
-      <c r="B56" s="108">
+      <c r="B56" s="106">
         <v>10930</v>
       </c>
-      <c r="C56" s="108">
+      <c r="C56" s="106">
         <v>10705</v>
       </c>
-      <c r="D56" s="108">
+      <c r="D56" s="106">
         <v>9756</v>
       </c>
-      <c r="E56" s="108">
+      <c r="E56" s="106">
         <v>9032</v>
       </c>
-      <c r="F56" s="108">
+      <c r="F56" s="106">
         <v>10534</v>
       </c>
-      <c r="G56" s="108">
+      <c r="G56" s="106">
         <v>8613</v>
       </c>
-      <c r="H56" s="108">
+      <c r="H56" s="106">
         <v>5959</v>
       </c>
-      <c r="I56" s="108">
+      <c r="I56" s="106">
         <v>7703</v>
       </c>
-      <c r="J56" s="108">
+      <c r="J56" s="106">
         <v>8422</v>
       </c>
-      <c r="K56" s="108">
+      <c r="K56" s="106">
         <v>5125</v>
       </c>
-      <c r="L56" s="108">
+      <c r="L56" s="106">
         <v>6586</v>
       </c>
     </row>
     <row r="57" spans="1:12">
-      <c r="A57" s="108">
+      <c r="A57" s="106">
         <v>8610</v>
       </c>
-      <c r="B57" s="108">
+      <c r="B57" s="106">
         <v>7654</v>
       </c>
-      <c r="C57" s="108">
+      <c r="C57" s="106">
         <v>9423</v>
       </c>
-      <c r="D57" s="108">
+      <c r="D57" s="106">
         <v>6143</v>
       </c>
-      <c r="E57" s="108">
+      <c r="E57" s="106">
         <v>8633</v>
       </c>
-      <c r="F57" s="108">
+      <c r="F57" s="106">
         <v>9066</v>
       </c>
-      <c r="G57" s="108">
+      <c r="G57" s="106">
         <v>9974</v>
       </c>
-      <c r="H57" s="108">
+      <c r="H57" s="106">
         <v>5364</v>
       </c>
-      <c r="I57" s="108">
+      <c r="I57" s="106">
         <v>10523</v>
       </c>
-      <c r="J57" s="108">
+      <c r="J57" s="106">
         <v>9424</v>
       </c>
-      <c r="K57" s="108">
+      <c r="K57" s="106">
         <v>9902</v>
       </c>
-      <c r="L57" s="108">
+      <c r="L57" s="106">
         <v>5021</v>
       </c>
     </row>
     <row r="58" spans="1:12">
-      <c r="A58" s="108">
+      <c r="A58" s="106">
         <v>6799</v>
       </c>
-      <c r="B58" s="108">
+      <c r="B58" s="106">
         <v>8994</v>
       </c>
-      <c r="C58" s="108">
+      <c r="C58" s="106">
         <v>10979</v>
       </c>
-      <c r="D58" s="108">
+      <c r="D58" s="106">
         <v>7621</v>
       </c>
-      <c r="E58" s="108">
+      <c r="E58" s="106">
         <v>8199</v>
       </c>
-      <c r="F58" s="108">
+      <c r="F58" s="106">
         <v>5484</v>
       </c>
-      <c r="G58" s="108">
+      <c r="G58" s="106">
         <v>10970</v>
       </c>
-      <c r="H58" s="108">
+      <c r="H58" s="106">
         <v>5748</v>
       </c>
-      <c r="I58" s="108">
+      <c r="I58" s="106">
         <v>10551</v>
       </c>
-      <c r="J58" s="108">
+      <c r="J58" s="106">
         <v>8249</v>
       </c>
-      <c r="K58" s="108">
+      <c r="K58" s="106">
         <v>6679</v>
       </c>
-      <c r="L58" s="108">
+      <c r="L58" s="106">
         <v>10395</v>
       </c>
     </row>
     <row r="59" spans="1:12">
-      <c r="A59" s="108">
+      <c r="A59" s="106">
         <v>6108</v>
       </c>
-      <c r="B59" s="108">
+      <c r="B59" s="106">
         <v>9274</v>
       </c>
-      <c r="C59" s="108">
+      <c r="C59" s="106">
         <v>9192</v>
       </c>
-      <c r="D59" s="108">
+      <c r="D59" s="106">
         <v>8314</v>
       </c>
-      <c r="E59" s="108">
+      <c r="E59" s="106">
         <v>8205</v>
       </c>
-      <c r="F59" s="108">
+      <c r="F59" s="106">
         <v>6760</v>
       </c>
-      <c r="G59" s="108">
+      <c r="G59" s="106">
         <v>9780</v>
       </c>
-      <c r="H59" s="108">
+      <c r="H59" s="106">
         <v>9122</v>
       </c>
-      <c r="I59" s="108">
+      <c r="I59" s="106">
         <v>8893</v>
       </c>
-      <c r="J59" s="108">
+      <c r="J59" s="106">
         <v>9733</v>
       </c>
-      <c r="K59" s="108">
+      <c r="K59" s="106">
         <v>7655</v>
       </c>
-      <c r="L59" s="108">
+      <c r="L59" s="106">
         <v>9477</v>
       </c>
     </row>
     <row r="60" spans="1:12">
-      <c r="A60" s="108">
+      <c r="A60" s="106">
         <v>9141</v>
       </c>
-      <c r="B60" s="108">
+      <c r="B60" s="106">
         <v>9583</v>
       </c>
-      <c r="C60" s="108">
+      <c r="C60" s="106">
         <v>6746</v>
       </c>
-      <c r="D60" s="108">
+      <c r="D60" s="106">
         <v>9708</v>
       </c>
-      <c r="E60" s="108">
+      <c r="E60" s="106">
         <v>8224</v>
       </c>
-      <c r="F60" s="108">
+      <c r="F60" s="106">
         <v>10122</v>
       </c>
-      <c r="G60" s="108">
+      <c r="G60" s="106">
         <v>7471</v>
       </c>
-      <c r="H60" s="108">
+      <c r="H60" s="106">
         <v>6017</v>
       </c>
-      <c r="I60" s="108">
+      <c r="I60" s="106">
         <v>9524</v>
       </c>
-      <c r="J60" s="108">
+      <c r="J60" s="106">
         <v>9577</v>
       </c>
-      <c r="K60" s="108">
+      <c r="K60" s="106">
         <v>9359</v>
       </c>
-      <c r="L60" s="108">
+      <c r="L60" s="106">
         <v>6654</v>
       </c>
     </row>
     <row r="61" spans="1:12">
-      <c r="A61" s="108">
+      <c r="A61" s="106">
         <v>7429</v>
       </c>
-      <c r="B61" s="108">
+      <c r="B61" s="106">
         <v>5336</v>
       </c>
-      <c r="C61" s="108">
+      <c r="C61" s="106">
         <v>7822</v>
       </c>
-      <c r="D61" s="108">
+      <c r="D61" s="106">
         <v>10218</v>
       </c>
-      <c r="E61" s="108">
+      <c r="E61" s="106">
         <v>6126</v>
       </c>
-      <c r="F61" s="108">
+      <c r="F61" s="106">
         <v>5391</v>
       </c>
-      <c r="G61" s="108">
+      <c r="G61" s="106">
         <v>5976</v>
       </c>
-      <c r="H61" s="108">
+      <c r="H61" s="106">
         <v>6860</v>
       </c>
-      <c r="I61" s="108">
+      <c r="I61" s="106">
         <v>9387</v>
       </c>
-      <c r="J61" s="108">
+      <c r="J61" s="106">
         <v>5702</v>
       </c>
-      <c r="K61" s="108">
+      <c r="K61" s="106">
         <v>10424</v>
       </c>
-      <c r="L61" s="108">
+      <c r="L61" s="106">
         <v>9813</v>
       </c>
     </row>
     <row r="62" spans="1:12">
-      <c r="A62" s="108">
+      <c r="A62" s="106">
         <v>6112</v>
       </c>
-      <c r="B62" s="108">
+      <c r="B62" s="106">
         <v>10210</v>
       </c>
-      <c r="C62" s="108">
+      <c r="C62" s="106">
         <v>9782</v>
       </c>
-      <c r="D62" s="108">
+      <c r="D62" s="106">
         <v>5657</v>
       </c>
-      <c r="E62" s="108">
+      <c r="E62" s="106">
         <v>5177</v>
       </c>
-      <c r="F62" s="108">
+      <c r="F62" s="106">
         <v>7614</v>
       </c>
-      <c r="G62" s="108">
+      <c r="G62" s="106">
         <v>6191</v>
       </c>
-      <c r="H62" s="108">
+      <c r="H62" s="106">
         <v>9633</v>
       </c>
-      <c r="I62" s="108">
+      <c r="I62" s="106">
         <v>5761</v>
       </c>
-      <c r="J62" s="108">
+      <c r="J62" s="106">
         <v>8541</v>
       </c>
-      <c r="K62" s="108">
+      <c r="K62" s="106">
         <v>10509</v>
       </c>
-      <c r="L62" s="108">
+      <c r="L62" s="106">
         <v>9978</v>
       </c>
     </row>
     <row r="63" spans="1:12">
-      <c r="A63" s="108">
+      <c r="A63" s="106">
         <v>5754</v>
       </c>
-      <c r="B63" s="108">
+      <c r="B63" s="106">
         <v>5040</v>
       </c>
-      <c r="C63" s="108">
+      <c r="C63" s="106">
         <v>6313</v>
       </c>
-      <c r="D63" s="108">
+      <c r="D63" s="106">
         <v>8787</v>
       </c>
-      <c r="E63" s="108">
+      <c r="E63" s="106">
         <v>9227</v>
       </c>
-      <c r="F63" s="108">
+      <c r="F63" s="106">
         <v>5588</v>
       </c>
-      <c r="G63" s="108">
+      <c r="G63" s="106">
         <v>9154</v>
       </c>
-      <c r="H63" s="108">
+      <c r="H63" s="106">
         <v>10466</v>
       </c>
-      <c r="I63" s="108">
+      <c r="I63" s="106">
         <v>9784</v>
       </c>
-      <c r="J63" s="108">
+      <c r="J63" s="106">
         <v>7477</v>
       </c>
-      <c r="K63" s="108">
+      <c r="K63" s="106">
         <v>10121</v>
       </c>
-      <c r="L63" s="108">
+      <c r="L63" s="106">
         <v>10823</v>
       </c>
     </row>
     <row r="64" spans="1:12">
-      <c r="A64" s="108">
+      <c r="A64" s="106">
         <v>10569</v>
       </c>
-      <c r="B64" s="108">
+      <c r="B64" s="106">
         <v>9007</v>
       </c>
-      <c r="C64" s="108">
+      <c r="C64" s="106">
         <v>10103</v>
       </c>
-      <c r="D64" s="108">
+      <c r="D64" s="106">
         <v>7714</v>
       </c>
-      <c r="E64" s="108">
+      <c r="E64" s="106">
         <v>7292</v>
       </c>
-      <c r="F64" s="108">
+      <c r="F64" s="106">
         <v>7159</v>
       </c>
-      <c r="G64" s="108">
+      <c r="G64" s="106">
         <v>10620</v>
       </c>
-      <c r="H64" s="108">
+      <c r="H64" s="106">
         <v>10813</v>
       </c>
-      <c r="I64" s="108">
+      <c r="I64" s="106">
         <v>6973</v>
       </c>
-      <c r="J64" s="108">
+      <c r="J64" s="106">
         <v>7580</v>
       </c>
-      <c r="K64" s="108">
+      <c r="K64" s="106">
         <v>5545</v>
       </c>
-      <c r="L64" s="108">
+      <c r="L64" s="106">
         <v>8207</v>
       </c>
     </row>
     <row r="65" spans="1:12">
-      <c r="A65" s="108">
+      <c r="A65" s="106">
         <v>7080</v>
       </c>
-      <c r="B65" s="108">
+      <c r="B65" s="106">
         <v>6470</v>
       </c>
-      <c r="C65" s="108">
+      <c r="C65" s="106">
         <v>9881</v>
       </c>
-      <c r="D65" s="108">
+      <c r="D65" s="106">
         <v>8594</v>
       </c>
-      <c r="E65" s="108">
+      <c r="E65" s="106">
         <v>9732</v>
       </c>
-      <c r="F65" s="108">
+      <c r="F65" s="106">
         <v>7823</v>
       </c>
-      <c r="G65" s="108">
+      <c r="G65" s="106">
         <v>5981</v>
       </c>
-      <c r="H65" s="108">
+      <c r="H65" s="106">
         <v>8934</v>
       </c>
-      <c r="I65" s="108">
+      <c r="I65" s="106">
         <v>10831</v>
       </c>
-      <c r="J65" s="108">
+      <c r="J65" s="106">
         <v>5724</v>
       </c>
-      <c r="K65" s="108">
+      <c r="K65" s="106">
         <v>9097</v>
       </c>
-      <c r="L65" s="108">
+      <c r="L65" s="106">
         <v>8696</v>
       </c>
     </row>
     <row r="66" spans="1:12">
-      <c r="A66" s="108">
+      <c r="A66" s="106">
         <v>8856</v>
       </c>
-      <c r="B66" s="108">
+      <c r="B66" s="106">
         <v>5447</v>
       </c>
-      <c r="C66" s="108">
+      <c r="C66" s="106">
         <v>7827</v>
       </c>
-      <c r="D66" s="108">
+      <c r="D66" s="106">
         <v>9986</v>
       </c>
-      <c r="E66" s="108">
+      <c r="E66" s="106">
         <v>10496</v>
       </c>
-      <c r="F66" s="108">
+      <c r="F66" s="106">
         <v>10696</v>
       </c>
-      <c r="G66" s="108">
+      <c r="G66" s="106">
         <v>7580</v>
       </c>
-      <c r="H66" s="108">
+      <c r="H66" s="106">
         <v>9407</v>
       </c>
-      <c r="I66" s="108">
+      <c r="I66" s="106">
         <v>7278</v>
       </c>
-      <c r="J66" s="108">
+      <c r="J66" s="106">
         <v>8109</v>
       </c>
-      <c r="K66" s="108">
+      <c r="K66" s="106">
         <v>6336</v>
       </c>
-      <c r="L66" s="108">
+      <c r="L66" s="106">
         <v>8425</v>
       </c>
     </row>
     <row r="67" spans="1:12">
-      <c r="A67" s="108">
+      <c r="A67" s="106">
         <v>6376</v>
       </c>
-      <c r="B67" s="108">
+      <c r="B67" s="106">
         <v>7309</v>
       </c>
-      <c r="C67" s="108">
+      <c r="C67" s="106">
         <v>9808</v>
       </c>
-      <c r="D67" s="108">
+      <c r="D67" s="106">
         <v>6437</v>
       </c>
-      <c r="E67" s="108">
+      <c r="E67" s="106">
         <v>5896</v>
       </c>
-      <c r="F67" s="108">
+      <c r="F67" s="106">
         <v>10135</v>
       </c>
-      <c r="G67" s="108">
+      <c r="G67" s="106">
         <v>9752</v>
       </c>
-      <c r="H67" s="108">
+      <c r="H67" s="106">
         <v>10295</v>
       </c>
-      <c r="I67" s="108">
+      <c r="I67" s="106">
         <v>7642</v>
       </c>
-      <c r="J67" s="108">
+      <c r="J67" s="106">
         <v>7856</v>
       </c>
-      <c r="K67" s="108">
+      <c r="K67" s="106">
         <v>9723</v>
       </c>
-      <c r="L67" s="108">
+      <c r="L67" s="106">
         <v>8865</v>
       </c>
     </row>
     <row r="68" spans="1:12">
-      <c r="A68" s="108">
+      <c r="A68" s="106">
         <v>10973</v>
       </c>
-      <c r="B68" s="108">
+      <c r="B68" s="106">
         <v>6174</v>
       </c>
-      <c r="C68" s="108">
+      <c r="C68" s="106">
         <v>6574</v>
       </c>
-      <c r="D68" s="108">
+      <c r="D68" s="106">
         <v>6126</v>
       </c>
-      <c r="E68" s="108">
+      <c r="E68" s="106">
         <v>9661</v>
       </c>
-      <c r="F68" s="108">
+      <c r="F68" s="106">
         <v>5387</v>
       </c>
-      <c r="G68" s="108">
+      <c r="G68" s="106">
         <v>7163</v>
       </c>
-      <c r="H68" s="108">
+      <c r="H68" s="106">
         <v>8763</v>
       </c>
-      <c r="I68" s="108">
+      <c r="I68" s="106">
         <v>8096</v>
       </c>
-      <c r="J68" s="108">
+      <c r="J68" s="106">
         <v>8942</v>
       </c>
-      <c r="K68" s="108">
+      <c r="K68" s="106">
         <v>8643</v>
       </c>
-      <c r="L68" s="108">
+      <c r="L68" s="106">
         <v>9210</v>
       </c>
     </row>
     <row r="69" spans="1:12">
-      <c r="A69" s="108">
+      <c r="A69" s="106">
         <v>6136</v>
       </c>
-      <c r="B69" s="108">
+      <c r="B69" s="106">
         <v>9777</v>
       </c>
-      <c r="C69" s="108">
+      <c r="C69" s="106">
         <v>10664</v>
       </c>
-      <c r="D69" s="108">
+      <c r="D69" s="106">
         <v>10663</v>
       </c>
-      <c r="E69" s="108">
+      <c r="E69" s="106">
         <v>8552</v>
       </c>
-      <c r="F69" s="108">
+      <c r="F69" s="106">
         <v>10339</v>
       </c>
-      <c r="G69" s="108">
+      <c r="G69" s="106">
         <v>8769</v>
       </c>
-      <c r="H69" s="108">
+      <c r="H69" s="106">
         <v>7051</v>
       </c>
-      <c r="I69" s="108">
+      <c r="I69" s="106">
         <v>10373</v>
       </c>
-      <c r="J69" s="108">
+      <c r="J69" s="106">
         <v>9736</v>
       </c>
-      <c r="K69" s="108">
+      <c r="K69" s="106">
         <v>5523</v>
       </c>
-      <c r="L69" s="108">
+      <c r="L69" s="106">
         <v>8970</v>
       </c>
     </row>
     <row r="70" spans="1:12">
-      <c r="A70" s="108">
+      <c r="A70" s="106">
         <v>9992</v>
       </c>
-      <c r="B70" s="108">
+      <c r="B70" s="106">
         <v>9994</v>
       </c>
-      <c r="C70" s="108">
+      <c r="C70" s="106">
         <v>7573</v>
       </c>
-      <c r="D70" s="108">
+      <c r="D70" s="106">
         <v>6083</v>
       </c>
-      <c r="E70" s="108">
+      <c r="E70" s="106">
         <v>9628</v>
       </c>
-      <c r="F70" s="108">
+      <c r="F70" s="106">
         <v>6713</v>
       </c>
-      <c r="G70" s="108">
+      <c r="G70" s="106">
         <v>7882</v>
       </c>
-      <c r="H70" s="108">
+      <c r="H70" s="106">
         <v>6217</v>
       </c>
-      <c r="I70" s="108">
+      <c r="I70" s="106">
         <v>10926</v>
       </c>
-      <c r="J70" s="108">
+      <c r="J70" s="106">
         <v>9669</v>
       </c>
-      <c r="K70" s="108">
+      <c r="K70" s="106">
         <v>8310</v>
       </c>
-      <c r="L70" s="108">
+      <c r="L70" s="106">
         <v>7930</v>
       </c>
     </row>
     <row r="71" spans="1:12">
-      <c r="A71" s="108">
+      <c r="A71" s="106">
         <v>6851</v>
       </c>
-      <c r="B71" s="108">
+      <c r="B71" s="106">
         <v>7123</v>
       </c>
-      <c r="C71" s="108">
+      <c r="C71" s="106">
         <v>7944</v>
       </c>
-      <c r="D71" s="108">
+      <c r="D71" s="106">
         <v>8882</v>
       </c>
-      <c r="E71" s="108">
+      <c r="E71" s="106">
         <v>6235</v>
       </c>
-      <c r="F71" s="108">
+      <c r="F71" s="106">
         <v>5999</v>
       </c>
-      <c r="G71" s="108">
+      <c r="G71" s="106">
         <v>6743</v>
       </c>
-      <c r="H71" s="108">
+      <c r="H71" s="106">
         <v>8199</v>
       </c>
-      <c r="I71" s="108">
+      <c r="I71" s="106">
         <v>8830</v>
       </c>
-      <c r="J71" s="108">
+      <c r="J71" s="106">
         <v>10375</v>
       </c>
-      <c r="K71" s="108">
+      <c r="K71" s="106">
         <v>9131</v>
       </c>
-      <c r="L71" s="108">
+      <c r="L71" s="106">
         <v>7042</v>
       </c>
     </row>
     <row r="72" spans="1:12">
-      <c r="A72" s="108">
+      <c r="A72" s="106">
         <v>6813</v>
       </c>
-      <c r="B72" s="108">
+      <c r="B72" s="106">
         <v>10583</v>
       </c>
-      <c r="C72" s="108">
+      <c r="C72" s="106">
         <v>5784</v>
       </c>
-      <c r="D72" s="108">
+      <c r="D72" s="106">
         <v>8908</v>
       </c>
-      <c r="E72" s="108">
+      <c r="E72" s="106">
         <v>7771</v>
       </c>
-      <c r="F72" s="108">
+      <c r="F72" s="106">
         <v>5690</v>
       </c>
-      <c r="G72" s="108">
+      <c r="G72" s="106">
         <v>7205</v>
       </c>
-      <c r="H72" s="108">
+      <c r="H72" s="106">
         <v>9404</v>
       </c>
-      <c r="I72" s="108">
+      <c r="I72" s="106">
         <v>9851</v>
       </c>
-      <c r="J72" s="108">
+      <c r="J72" s="106">
         <v>10462</v>
       </c>
-      <c r="K72" s="108">
+      <c r="K72" s="106">
         <v>8025</v>
       </c>
-      <c r="L72" s="108">
+      <c r="L72" s="106">
         <v>8553</v>
       </c>
     </row>
     <row r="73" spans="1:12">
-      <c r="A73" s="108">
+      <c r="A73" s="106">
         <v>9743</v>
       </c>
-      <c r="B73" s="108">
+      <c r="B73" s="106">
         <v>8962</v>
       </c>
-      <c r="C73" s="108">
+      <c r="C73" s="106">
         <v>6553</v>
       </c>
-      <c r="D73" s="108">
+      <c r="D73" s="106">
         <v>9053</v>
       </c>
-      <c r="E73" s="108">
+      <c r="E73" s="106">
         <v>8147</v>
       </c>
-      <c r="F73" s="108">
+      <c r="F73" s="106">
         <v>10191</v>
       </c>
-      <c r="G73" s="108">
+      <c r="G73" s="106">
         <v>9062</v>
       </c>
-      <c r="H73" s="108">
+      <c r="H73" s="106">
         <v>8416</v>
       </c>
-      <c r="I73" s="108">
+      <c r="I73" s="106">
         <v>10735</v>
       </c>
-      <c r="J73" s="108">
+      <c r="J73" s="106">
         <v>9307</v>
       </c>
-      <c r="K73" s="108">
+      <c r="K73" s="106">
         <v>5447</v>
       </c>
-      <c r="L73" s="108">
+      <c r="L73" s="106">
         <v>7266</v>
       </c>
     </row>
     <row r="74" spans="1:12">
-      <c r="A74" s="108">
+      <c r="A74" s="106">
         <v>8483</v>
       </c>
-      <c r="B74" s="108">
+      <c r="B74" s="106">
         <v>10760</v>
       </c>
-      <c r="C74" s="108">
+      <c r="C74" s="106">
         <v>8233</v>
       </c>
-      <c r="D74" s="108">
+      <c r="D74" s="106">
         <v>9798</v>
       </c>
-      <c r="E74" s="108">
+      <c r="E74" s="106">
         <v>9090</v>
       </c>
-      <c r="F74" s="108">
+      <c r="F74" s="106">
         <v>7706</v>
       </c>
-      <c r="G74" s="108">
+      <c r="G74" s="106">
         <v>8442</v>
       </c>
-      <c r="H74" s="108">
+      <c r="H74" s="106">
         <v>7968</v>
       </c>
-      <c r="I74" s="108">
+      <c r="I74" s="106">
         <v>5179</v>
       </c>
-      <c r="J74" s="108">
+      <c r="J74" s="106">
         <v>5384</v>
       </c>
-      <c r="K74" s="108">
+      <c r="K74" s="106">
         <v>5923</v>
       </c>
-      <c r="L74" s="108">
+      <c r="L74" s="106">
         <v>6882</v>
       </c>
     </row>
     <row r="75" spans="1:12">
-      <c r="A75" s="108">
+      <c r="A75" s="106">
         <v>6899</v>
       </c>
-      <c r="B75" s="108">
+      <c r="B75" s="106">
         <v>5679</v>
       </c>
-      <c r="C75" s="108">
+      <c r="C75" s="106">
         <v>10017</v>
       </c>
-      <c r="D75" s="108">
+      <c r="D75" s="106">
         <v>8439</v>
       </c>
-      <c r="E75" s="108">
+      <c r="E75" s="106">
         <v>9433</v>
       </c>
-      <c r="F75" s="108">
+      <c r="F75" s="106">
         <v>7254</v>
       </c>
-      <c r="G75" s="108">
+      <c r="G75" s="106">
         <v>7284</v>
       </c>
-      <c r="H75" s="108">
+      <c r="H75" s="106">
         <v>6339</v>
       </c>
-      <c r="I75" s="108">
+      <c r="I75" s="106">
         <v>10863</v>
       </c>
-      <c r="J75" s="108">
+      <c r="J75" s="106">
         <v>8176</v>
       </c>
-      <c r="K75" s="108">
+      <c r="K75" s="106">
         <v>10687</v>
       </c>
-      <c r="L75" s="108">
+      <c r="L75" s="106">
         <v>9063</v>
       </c>
     </row>
     <row r="76" spans="1:12">
-      <c r="A76" s="108">
+      <c r="A76" s="106">
         <v>8106</v>
       </c>
-      <c r="B76" s="108">
+      <c r="B76" s="106">
         <v>10650</v>
       </c>
-      <c r="C76" s="108">
+      <c r="C76" s="106">
         <v>8178</v>
       </c>
-      <c r="D76" s="108">
+      <c r="D76" s="106">
         <v>7876</v>
       </c>
-      <c r="E76" s="108">
+      <c r="E76" s="106">
         <v>9829</v>
       </c>
-      <c r="F76" s="108">
+      <c r="F76" s="106">
         <v>6548</v>
       </c>
-      <c r="G76" s="108">
+      <c r="G76" s="106">
         <v>6575</v>
       </c>
-      <c r="H76" s="108">
+      <c r="H76" s="106">
         <v>8053</v>
       </c>
-      <c r="I76" s="108">
+      <c r="I76" s="106">
         <v>9427</v>
       </c>
-      <c r="J76" s="108">
+      <c r="J76" s="106">
         <v>8111</v>
       </c>
-      <c r="K76" s="108">
+      <c r="K76" s="106">
         <v>8342</v>
       </c>
-      <c r="L76" s="108">
+      <c r="L76" s="106">
         <v>10532</v>
       </c>
     </row>
     <row r="77" spans="1:12">
-      <c r="A77" s="108">
+      <c r="A77" s="106">
         <v>8146</v>
       </c>
-      <c r="B77" s="108">
+      <c r="B77" s="106">
         <v>7744</v>
       </c>
-      <c r="C77" s="108">
+      <c r="C77" s="106">
         <v>8731</v>
       </c>
-      <c r="D77" s="108">
+      <c r="D77" s="106">
         <v>7498</v>
       </c>
-      <c r="E77" s="108">
+      <c r="E77" s="106">
         <v>9243</v>
       </c>
-      <c r="F77" s="108">
+      <c r="F77" s="106">
         <v>8319</v>
       </c>
-      <c r="G77" s="108">
+      <c r="G77" s="106">
         <v>7574</v>
       </c>
-      <c r="H77" s="108">
+      <c r="H77" s="106">
         <v>5218</v>
       </c>
-      <c r="I77" s="108">
+      <c r="I77" s="106">
         <v>5189</v>
       </c>
-      <c r="J77" s="108">
+      <c r="J77" s="106">
         <v>10405</v>
       </c>
-      <c r="K77" s="108">
+      <c r="K77" s="106">
         <v>10305</v>
       </c>
-      <c r="L77" s="108">
+      <c r="L77" s="106">
         <v>8265</v>
       </c>
     </row>
     <row r="78" spans="1:12">
-      <c r="A78" s="108">
+      <c r="A78" s="106">
         <v>5518</v>
       </c>
-      <c r="B78" s="108">
+      <c r="B78" s="106">
         <v>9323</v>
       </c>
-      <c r="C78" s="108">
+      <c r="C78" s="106">
         <v>5653</v>
       </c>
-      <c r="D78" s="108">
+      <c r="D78" s="106">
         <v>8862</v>
       </c>
-      <c r="E78" s="108">
+      <c r="E78" s="106">
         <v>7571</v>
       </c>
-      <c r="F78" s="108">
+      <c r="F78" s="106">
         <v>7112</v>
       </c>
-      <c r="G78" s="108">
+      <c r="G78" s="106">
         <v>7339</v>
       </c>
-      <c r="H78" s="108">
+      <c r="H78" s="106">
         <v>7289</v>
       </c>
-      <c r="I78" s="108">
+      <c r="I78" s="106">
         <v>6825</v>
       </c>
-      <c r="J78" s="108">
+      <c r="J78" s="106">
         <v>5180</v>
       </c>
-      <c r="K78" s="108">
+      <c r="K78" s="106">
         <v>6886</v>
       </c>
-      <c r="L78" s="108">
+      <c r="L78" s="106">
         <v>10461</v>
       </c>
     </row>
     <row r="79" spans="1:12">
-      <c r="A79" s="108">
+      <c r="A79" s="106">
         <v>10253</v>
       </c>
-      <c r="B79" s="108">
+      <c r="B79" s="106">
         <v>8111</v>
       </c>
-      <c r="C79" s="108">
+      <c r="C79" s="106">
         <v>9810</v>
       </c>
-      <c r="D79" s="108">
+      <c r="D79" s="106">
         <v>7848</v>
       </c>
-      <c r="E79" s="108">
+      <c r="E79" s="106">
         <v>6282</v>
       </c>
-      <c r="F79" s="108">
+      <c r="F79" s="106">
         <v>5947</v>
       </c>
-      <c r="G79" s="108">
+      <c r="G79" s="106">
         <v>5000</v>
       </c>
-      <c r="H79" s="108">
+      <c r="H79" s="106">
         <v>10066</v>
       </c>
-      <c r="I79" s="108">
+      <c r="I79" s="106">
         <v>7665</v>
       </c>
-      <c r="J79" s="108">
+      <c r="J79" s="106">
         <v>9510</v>
       </c>
-      <c r="K79" s="108">
+      <c r="K79" s="106">
         <v>9590</v>
       </c>
-      <c r="L79" s="108">
+      <c r="L79" s="106">
         <v>10301</v>
       </c>
     </row>
     <row r="80" spans="1:12">
-      <c r="A80" s="108">
+      <c r="A80" s="106">
         <v>9637</v>
       </c>
-      <c r="B80" s="108">
+      <c r="B80" s="106">
         <v>8864</v>
       </c>
-      <c r="C80" s="108">
+      <c r="C80" s="106">
         <v>10424</v>
       </c>
-      <c r="D80" s="108">
+      <c r="D80" s="106">
         <v>10403</v>
       </c>
-      <c r="E80" s="108">
+      <c r="E80" s="106">
         <v>7919</v>
       </c>
-      <c r="F80" s="108">
+      <c r="F80" s="106">
         <v>10148</v>
       </c>
-      <c r="G80" s="108">
+      <c r="G80" s="106">
         <v>8062</v>
       </c>
-      <c r="H80" s="108">
+      <c r="H80" s="106">
         <v>9030</v>
       </c>
-      <c r="I80" s="108">
+      <c r="I80" s="106">
         <v>10532</v>
       </c>
-      <c r="J80" s="108">
+      <c r="J80" s="106">
         <v>8626</v>
       </c>
-      <c r="K80" s="108">
+      <c r="K80" s="106">
         <v>5194</v>
       </c>
-      <c r="L80" s="108">
+      <c r="L80" s="106">
         <v>6461</v>
       </c>
     </row>
     <row r="81" spans="1:12">
-      <c r="A81" s="108">
+      <c r="A81" s="106">
         <v>6267</v>
       </c>
-      <c r="B81" s="108">
+      <c r="B81" s="106">
         <v>5823</v>
       </c>
-      <c r="C81" s="108">
+      <c r="C81" s="106">
         <v>9020</v>
       </c>
-      <c r="D81" s="108">
+      <c r="D81" s="106">
         <v>9163</v>
       </c>
-      <c r="E81" s="108">
+      <c r="E81" s="106">
         <v>6344</v>
       </c>
-      <c r="F81" s="108">
+      <c r="F81" s="106">
         <v>10287</v>
       </c>
-      <c r="G81" s="108">
+      <c r="G81" s="106">
         <v>7060</v>
       </c>
-      <c r="H81" s="108">
+      <c r="H81" s="106">
         <v>8040</v>
       </c>
-      <c r="I81" s="108">
+      <c r="I81" s="106">
         <v>6949</v>
       </c>
-      <c r="J81" s="108">
+      <c r="J81" s="106">
         <v>6830</v>
       </c>
-      <c r="K81" s="108">
+      <c r="K81" s="106">
         <v>7887</v>
       </c>
-      <c r="L81" s="108">
+      <c r="L81" s="106">
         <v>9961</v>
       </c>
     </row>
     <row r="82" spans="1:12">
-      <c r="A82" s="108">
+      <c r="A82" s="106">
         <v>8630</v>
       </c>
-      <c r="B82" s="108">
+      <c r="B82" s="106">
         <v>6570</v>
       </c>
-      <c r="C82" s="108">
+      <c r="C82" s="106">
         <v>5495</v>
       </c>
-      <c r="D82" s="108">
+      <c r="D82" s="106">
         <v>10687</v>
       </c>
-      <c r="E82" s="108">
+      <c r="E82" s="106">
         <v>10295</v>
       </c>
-      <c r="F82" s="108">
+      <c r="F82" s="106">
         <v>8115</v>
       </c>
-      <c r="G82" s="108">
+      <c r="G82" s="106">
         <v>7353</v>
       </c>
-      <c r="H82" s="108">
+      <c r="H82" s="106">
         <v>5100</v>
       </c>
-      <c r="I82" s="108">
+      <c r="I82" s="106">
         <v>8095</v>
       </c>
-      <c r="J82" s="108">
+      <c r="J82" s="106">
         <v>10700</v>
       </c>
-      <c r="K82" s="108">
+      <c r="K82" s="106">
         <v>9868</v>
       </c>
-      <c r="L82" s="108">
+      <c r="L82" s="106">
         <v>9221</v>
       </c>
     </row>
     <row r="83" spans="1:12">
-      <c r="A83" s="108">
+      <c r="A83" s="106">
         <v>8397</v>
       </c>
-      <c r="B83" s="108">
+      <c r="B83" s="106">
         <v>10051</v>
       </c>
-      <c r="C83" s="108">
+      <c r="C83" s="106">
         <v>5834</v>
       </c>
-      <c r="D83" s="108">
+      <c r="D83" s="106">
         <v>7947</v>
       </c>
-      <c r="E83" s="108">
+      <c r="E83" s="106">
         <v>10564</v>
       </c>
-      <c r="F83" s="108">
+      <c r="F83" s="106">
         <v>8093</v>
       </c>
-      <c r="G83" s="108">
+      <c r="G83" s="106">
         <v>8634</v>
       </c>
-      <c r="H83" s="108">
+      <c r="H83" s="106">
         <v>9843</v>
       </c>
-      <c r="I83" s="108">
+      <c r="I83" s="106">
         <v>9625</v>
       </c>
-      <c r="J83" s="108">
+      <c r="J83" s="106">
         <v>9210</v>
       </c>
-      <c r="K83" s="108">
+      <c r="K83" s="106">
         <v>10045</v>
       </c>
-      <c r="L83" s="108">
+      <c r="L83" s="106">
         <v>7591</v>
       </c>
     </row>
     <row r="84" spans="1:12">
-      <c r="A84" s="108">
+      <c r="A84" s="106">
         <v>9600</v>
       </c>
-      <c r="B84" s="108">
+      <c r="B84" s="106">
         <v>10578</v>
       </c>
-      <c r="C84" s="108">
+      <c r="C84" s="106">
         <v>9519</v>
       </c>
-      <c r="D84" s="108">
+      <c r="D84" s="106">
         <v>7399</v>
       </c>
-      <c r="E84" s="108">
+      <c r="E84" s="106">
         <v>5081</v>
       </c>
-      <c r="F84" s="108">
+      <c r="F84" s="106">
         <v>5807</v>
       </c>
-      <c r="G84" s="108">
+      <c r="G84" s="106">
         <v>7287</v>
       </c>
-      <c r="H84" s="108">
+      <c r="H84" s="106">
         <v>9268</v>
       </c>
-      <c r="I84" s="108">
+      <c r="I84" s="106">
         <v>5999</v>
       </c>
-      <c r="J84" s="108">
+      <c r="J84" s="106">
         <v>9895</v>
       </c>
-      <c r="K84" s="108">
+      <c r="K84" s="106">
         <v>5311</v>
       </c>
-      <c r="L84" s="108">
+      <c r="L84" s="106">
         <v>8741</v>
       </c>
     </row>
     <row r="85" spans="1:12">
-      <c r="A85" s="108">
+      <c r="A85" s="106">
         <v>8378</v>
       </c>
-      <c r="B85" s="108">
+      <c r="B85" s="106">
         <v>5199</v>
       </c>
-      <c r="C85" s="108">
+      <c r="C85" s="106">
         <v>7359</v>
       </c>
-      <c r="D85" s="108">
+      <c r="D85" s="106">
         <v>10834</v>
       </c>
-      <c r="E85" s="108">
+      <c r="E85" s="106">
         <v>5026</v>
       </c>
-      <c r="F85" s="108">
+      <c r="F85" s="106">
         <v>6688</v>
       </c>
-      <c r="G85" s="108">
+      <c r="G85" s="106">
         <v>10761</v>
       </c>
-      <c r="H85" s="108">
+      <c r="H85" s="106">
         <v>10501</v>
       </c>
-      <c r="I85" s="108">
+      <c r="I85" s="106">
         <v>8772</v>
       </c>
-      <c r="J85" s="108">
+      <c r="J85" s="106">
         <v>9265</v>
       </c>
-      <c r="K85" s="108">
+      <c r="K85" s="106">
         <v>9447</v>
       </c>
-      <c r="L85" s="108">
+      <c r="L85" s="106">
         <v>9940</v>
       </c>
     </row>
     <row r="86" spans="1:12">
-      <c r="A86" s="108">
+      <c r="A86" s="106">
         <v>8691</v>
       </c>
-      <c r="B86" s="108">
+      <c r="B86" s="106">
         <v>7229</v>
       </c>
-      <c r="C86" s="108">
+      <c r="C86" s="106">
         <v>10668</v>
       </c>
-      <c r="D86" s="108">
+      <c r="D86" s="106">
         <v>8616</v>
       </c>
-      <c r="E86" s="108">
+      <c r="E86" s="106">
         <v>5666</v>
       </c>
-      <c r="F86" s="108">
+      <c r="F86" s="106">
         <v>5447</v>
       </c>
-      <c r="G86" s="108">
+      <c r="G86" s="106">
         <v>8357</v>
       </c>
-      <c r="H86" s="108">
+      <c r="H86" s="106">
         <v>8922</v>
       </c>
-      <c r="I86" s="108">
+      <c r="I86" s="106">
         <v>8512</v>
       </c>
-      <c r="J86" s="108">
+      <c r="J86" s="106">
         <v>6040</v>
       </c>
-      <c r="K86" s="108">
+      <c r="K86" s="106">
         <v>7259</v>
       </c>
-      <c r="L86" s="108">
+      <c r="L86" s="106">
         <v>8085</v>
       </c>
     </row>
     <row r="87" spans="1:12">
-      <c r="A87" s="108">
+      <c r="A87" s="106">
         <v>10197</v>
       </c>
-      <c r="B87" s="108">
+      <c r="B87" s="106">
         <v>8030</v>
       </c>
-      <c r="C87" s="108">
+      <c r="C87" s="106">
         <v>6882</v>
       </c>
-      <c r="D87" s="108">
+      <c r="D87" s="106">
         <v>9062</v>
       </c>
-      <c r="E87" s="108">
+      <c r="E87" s="106">
         <v>6523</v>
       </c>
-      <c r="F87" s="108">
+      <c r="F87" s="106">
         <v>5968</v>
       </c>
-      <c r="G87" s="108">
+      <c r="G87" s="106">
         <v>10205</v>
       </c>
-      <c r="H87" s="108">
+      <c r="H87" s="106">
         <v>6758</v>
       </c>
-      <c r="I87" s="108">
+      <c r="I87" s="106">
         <v>9867</v>
       </c>
-      <c r="J87" s="108">
+      <c r="J87" s="106">
         <v>6595</v>
       </c>
-      <c r="K87" s="108">
+      <c r="K87" s="106">
         <v>8181</v>
       </c>
-      <c r="L87" s="108">
+      <c r="L87" s="106">
         <v>5567</v>
       </c>
     </row>
     <row r="88" spans="1:12">
-      <c r="A88" s="108">
+      <c r="A88" s="106">
         <v>9510</v>
       </c>
-      <c r="B88" s="108">
+      <c r="B88" s="106">
         <v>5977</v>
       </c>
-      <c r="C88" s="108">
+      <c r="C88" s="106">
         <v>8299</v>
       </c>
-      <c r="D88" s="108">
+      <c r="D88" s="106">
         <v>9160</v>
       </c>
-      <c r="E88" s="108">
+      <c r="E88" s="106">
         <v>10221</v>
       </c>
-      <c r="F88" s="108">
+      <c r="F88" s="106">
         <v>10660</v>
       </c>
-      <c r="G88" s="108">
+      <c r="G88" s="106">
         <v>6597</v>
       </c>
-      <c r="H88" s="108">
+      <c r="H88" s="106">
         <v>5041</v>
       </c>
-      <c r="I88" s="108">
+      <c r="I88" s="106">
         <v>8684</v>
       </c>
-      <c r="J88" s="108">
+      <c r="J88" s="106">
         <v>10142</v>
       </c>
-      <c r="K88" s="108">
+      <c r="K88" s="106">
         <v>8562</v>
       </c>
-      <c r="L88" s="108">
+      <c r="L88" s="106">
         <v>5680</v>
       </c>
     </row>
     <row r="89" spans="1:12">
-      <c r="A89" s="108">
+      <c r="A89" s="106">
         <v>10451</v>
       </c>
-      <c r="B89" s="108">
+      <c r="B89" s="106">
         <v>8614</v>
       </c>
-      <c r="C89" s="108">
+      <c r="C89" s="106">
         <v>7491</v>
       </c>
-      <c r="D89" s="108">
+      <c r="D89" s="106">
         <v>10297</v>
       </c>
-      <c r="E89" s="108">
+      <c r="E89" s="106">
         <v>10742</v>
       </c>
-      <c r="F89" s="108">
+      <c r="F89" s="106">
         <v>9807</v>
       </c>
-      <c r="G89" s="108">
+      <c r="G89" s="106">
         <v>8809</v>
       </c>
-      <c r="H89" s="108">
+      <c r="H89" s="106">
         <v>7113</v>
       </c>
-      <c r="I89" s="108">
+      <c r="I89" s="106">
         <v>6656</v>
       </c>
-      <c r="J89" s="108">
+      <c r="J89" s="106">
         <v>5548</v>
       </c>
-      <c r="K89" s="108">
+      <c r="K89" s="106">
         <v>5455</v>
       </c>
-      <c r="L89" s="108">
+      <c r="L89" s="106">
         <v>7283</v>
       </c>
     </row>
     <row r="90" spans="1:12">
-      <c r="A90" s="108">
+      <c r="A90" s="106">
         <v>8091</v>
       </c>
-      <c r="B90" s="108">
+      <c r="B90" s="106">
         <v>10399</v>
       </c>
-      <c r="C90" s="108">
+      <c r="C90" s="106">
         <v>6479</v>
       </c>
-      <c r="D90" s="108">
+      <c r="D90" s="106">
         <v>5125</v>
       </c>
-      <c r="E90" s="108">
+      <c r="E90" s="106">
         <v>5082</v>
       </c>
-      <c r="F90" s="108">
+      <c r="F90" s="106">
         <v>8935</v>
       </c>
-      <c r="G90" s="108">
+      <c r="G90" s="106">
         <v>7320</v>
       </c>
-      <c r="H90" s="108">
+      <c r="H90" s="106">
         <v>5207</v>
       </c>
-      <c r="I90" s="108">
+      <c r="I90" s="106">
         <v>6756</v>
       </c>
-      <c r="J90" s="108">
+      <c r="J90" s="106">
         <v>10471</v>
       </c>
-      <c r="K90" s="108">
+      <c r="K90" s="106">
         <v>8719</v>
       </c>
-      <c r="L90" s="108">
+      <c r="L90" s="106">
         <v>9300</v>
       </c>
     </row>
     <row r="91" spans="1:12">
-      <c r="A91" s="108">
+      <c r="A91" s="106">
         <v>5581</v>
       </c>
-      <c r="B91" s="108">
+      <c r="B91" s="106">
         <v>9638</v>
       </c>
-      <c r="C91" s="108">
+      <c r="C91" s="106">
         <v>6755</v>
       </c>
-      <c r="D91" s="108">
+      <c r="D91" s="106">
         <v>6132</v>
       </c>
-      <c r="E91" s="108">
+      <c r="E91" s="106">
         <v>10926</v>
       </c>
-      <c r="F91" s="108">
+      <c r="F91" s="106">
         <v>5755</v>
       </c>
-      <c r="G91" s="108">
+      <c r="G91" s="106">
         <v>5168</v>
       </c>
-      <c r="H91" s="108">
+      <c r="H91" s="106">
         <v>5588</v>
       </c>
-      <c r="I91" s="108">
+      <c r="I91" s="106">
         <v>10821</v>
       </c>
-      <c r="J91" s="108">
+      <c r="J91" s="106">
         <v>8076</v>
       </c>
-      <c r="K91" s="108">
+      <c r="K91" s="106">
         <v>10119</v>
       </c>
-      <c r="L91" s="108">
+      <c r="L91" s="106">
         <v>9636</v>
       </c>
     </row>
     <row r="92" spans="1:12">
-      <c r="A92" s="108">
+      <c r="A92" s="106">
         <v>6094</v>
       </c>
-      <c r="B92" s="108">
+      <c r="B92" s="106">
         <v>9679</v>
       </c>
-      <c r="C92" s="108">
+      <c r="C92" s="106">
         <v>8169</v>
       </c>
-      <c r="D92" s="108">
+      <c r="D92" s="106">
         <v>9225</v>
       </c>
-      <c r="E92" s="108">
+      <c r="E92" s="106">
         <v>7124</v>
       </c>
-      <c r="F92" s="108">
+      <c r="F92" s="106">
         <v>9908</v>
       </c>
-      <c r="G92" s="108">
+      <c r="G92" s="106">
         <v>9047</v>
       </c>
-      <c r="H92" s="108">
+      <c r="H92" s="106">
         <v>6069</v>
       </c>
-      <c r="I92" s="108">
+      <c r="I92" s="106">
         <v>6994</v>
       </c>
-      <c r="J92" s="108">
+      <c r="J92" s="106">
         <v>10209</v>
       </c>
-      <c r="K92" s="108">
+      <c r="K92" s="106">
         <v>6806</v>
       </c>
-      <c r="L92" s="108">
+      <c r="L92" s="106">
         <v>10216</v>
       </c>
     </row>
     <row r="93" spans="1:12">
-      <c r="A93" s="108">
+      <c r="A93" s="106">
         <v>10378</v>
       </c>
-      <c r="B93" s="108">
+      <c r="B93" s="106">
         <v>7378</v>
       </c>
-      <c r="C93" s="108">
+      <c r="C93" s="106">
         <v>7850</v>
       </c>
-      <c r="D93" s="108">
+      <c r="D93" s="106">
         <v>7193</v>
       </c>
-      <c r="E93" s="108">
+      <c r="E93" s="106">
         <v>9162</v>
       </c>
-      <c r="F93" s="108">
+      <c r="F93" s="106">
         <v>8156</v>
       </c>
-      <c r="G93" s="108">
+      <c r="G93" s="106">
         <v>8714</v>
       </c>
-      <c r="H93" s="108">
+      <c r="H93" s="106">
         <v>6988</v>
       </c>
-      <c r="I93" s="108">
+      <c r="I93" s="106">
         <v>10249</v>
       </c>
-      <c r="J93" s="108">
+      <c r="J93" s="106">
         <v>5320</v>
       </c>
-      <c r="K93" s="108">
+      <c r="K93" s="106">
         <v>9584</v>
       </c>
-      <c r="L93" s="108">
+      <c r="L93" s="106">
         <v>9095</v>
       </c>
     </row>
@@ -15742,7 +16249,7 @@
         <v>17883</v>
       </c>
       <c r="E8" t="str">
-        <f t="shared" ref="E8:E21" si="0">IF(D8&gt;15000, "Positive")</f>
+        <f>IF(D8&gt;15000, "Positive")</f>
         <v>Positive</v>
       </c>
     </row>
@@ -15760,7 +16267,7 @@
         <v>17704</v>
       </c>
       <c r="E9" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" ref="E9:E21" si="0">IF(D9&gt;15000, "Positive")</f>
         <v>Positive</v>
       </c>
     </row>
@@ -16444,16 +16951,16 @@
       <c r="E6" s="52"/>
     </row>
     <row r="7" spans="2:7" ht="15" thickBot="1">
-      <c r="B7" s="120" t="s">
+      <c r="B7" s="118" t="s">
         <v>5</v>
       </c>
-      <c r="C7" s="121" t="s">
+      <c r="C7" s="119" t="s">
         <v>6</v>
       </c>
       <c r="D7" s="44" t="s">
         <v>7</v>
       </c>
-      <c r="E7" s="118" t="s">
+      <c r="E7" s="116" t="s">
         <v>8</v>
       </c>
       <c r="F7" t="s">
@@ -16461,99 +16968,99 @@
       </c>
     </row>
     <row r="8" spans="2:7" ht="15.5" thickTop="1" thickBot="1">
-      <c r="B8" s="122" t="s">
+      <c r="B8" s="120" t="s">
         <v>10</v>
       </c>
-      <c r="C8" s="123">
+      <c r="C8" s="121">
         <v>16</v>
       </c>
       <c r="D8" s="50">
         <v>245</v>
       </c>
-      <c r="E8" s="119"/>
-      <c r="F8" s="126"/>
+      <c r="E8" s="117"/>
+      <c r="F8" s="124"/>
     </row>
     <row r="9" spans="2:7" ht="15.5" thickTop="1" thickBot="1">
-      <c r="B9" s="122" t="s">
+      <c r="B9" s="120" t="s">
         <v>11</v>
       </c>
-      <c r="C9" s="123">
+      <c r="C9" s="121">
         <v>32</v>
       </c>
       <c r="D9" s="50">
         <v>202</v>
       </c>
-      <c r="E9" s="119"/>
-      <c r="F9" s="126"/>
+      <c r="E9" s="117"/>
+      <c r="F9" s="124"/>
     </row>
     <row r="10" spans="2:7" ht="15.5" thickTop="1" thickBot="1">
-      <c r="B10" s="122" t="s">
+      <c r="B10" s="120" t="s">
         <v>12</v>
       </c>
-      <c r="C10" s="123">
+      <c r="C10" s="121">
         <v>80</v>
       </c>
       <c r="D10" s="50">
         <v>195</v>
       </c>
-      <c r="E10" s="119"/>
-      <c r="F10" s="126"/>
+      <c r="E10" s="117"/>
+      <c r="F10" s="124"/>
     </row>
     <row r="11" spans="2:7" ht="15.5" thickTop="1" thickBot="1">
-      <c r="B11" s="122" t="s">
+      <c r="B11" s="120" t="s">
         <v>13</v>
       </c>
-      <c r="C11" s="123">
+      <c r="C11" s="121">
         <v>16</v>
       </c>
       <c r="D11" s="50">
         <v>126</v>
       </c>
-      <c r="E11" s="119"/>
-      <c r="F11" s="126"/>
+      <c r="E11" s="117"/>
+      <c r="F11" s="124"/>
     </row>
     <row r="12" spans="2:7" ht="15.5" thickTop="1" thickBot="1">
-      <c r="B12" s="122" t="s">
+      <c r="B12" s="120" t="s">
         <v>14</v>
       </c>
-      <c r="C12" s="123">
+      <c r="C12" s="121">
         <v>48</v>
       </c>
       <c r="D12" s="50">
         <v>89</v>
       </c>
-      <c r="E12" s="119"/>
-      <c r="F12" s="126"/>
+      <c r="E12" s="117"/>
+      <c r="F12" s="124"/>
     </row>
     <row r="13" spans="2:7" ht="15.5" thickTop="1" thickBot="1">
-      <c r="B13" s="122" t="s">
+      <c r="B13" s="120" t="s">
         <v>15</v>
       </c>
-      <c r="C13" s="123">
+      <c r="C13" s="121">
         <v>48</v>
       </c>
       <c r="D13" s="50">
         <v>49</v>
       </c>
-      <c r="E13" s="119"/>
-      <c r="F13" s="126"/>
+      <c r="E13" s="117"/>
+      <c r="F13" s="124"/>
     </row>
     <row r="14" spans="2:7" ht="15.5" thickTop="1" thickBot="1">
-      <c r="B14" s="122" t="s">
+      <c r="B14" s="120" t="s">
         <v>16</v>
       </c>
-      <c r="C14" s="123">
+      <c r="C14" s="121">
         <v>32</v>
       </c>
       <c r="D14" s="50">
         <v>49</v>
       </c>
-      <c r="E14" s="119"/>
-      <c r="F14" s="126"/>
+      <c r="E14" s="117"/>
+      <c r="F14" s="124"/>
     </row>
     <row r="15" spans="2:7" ht="15" thickBot="1">
-      <c r="B15" s="124"/>
-      <c r="C15" s="125"/>
+      <c r="B15" s="122"/>
+      <c r="C15" s="123"/>
       <c r="D15" s="45">
         <f>SUM(D8:D14)</f>
         <v>955</v>
@@ -16572,10 +17079,10 @@
     </row>
     <row r="17" spans="2:7">
       <c r="B17" s="49"/>
-      <c r="C17" s="117" t="s">
+      <c r="C17" s="115" t="s">
         <v>17</v>
       </c>
-      <c r="D17" s="156">
+      <c r="D17" s="154">
         <f>SUMPRODUCT(C8:C14, D8:D14)</f>
         <v>36192</v>
       </c>
@@ -16596,436 +17103,436 @@
   <cols>
     <col min="1" max="1" width="36.54296875" bestFit="1" customWidth="1"/>
     <col min="2" max="3" width="16.1796875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9.54296875" style="157" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.54296875" style="155" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="8" spans="1:4">
-      <c r="A8" s="142"/>
-      <c r="B8" s="141">
+      <c r="A8" s="140"/>
+      <c r="B8" s="139">
         <v>45261</v>
       </c>
-      <c r="C8" s="141">
+      <c r="C8" s="139">
         <v>45261</v>
       </c>
-      <c r="D8" s="165" t="s">
+      <c r="D8" s="168" t="s">
         <v>457</v>
       </c>
     </row>
     <row r="9" spans="1:4">
-      <c r="A9" s="143" t="s">
+      <c r="A9" s="141" t="s">
         <v>458</v>
       </c>
-      <c r="B9" s="129" t="s">
+      <c r="B9" s="127" t="s">
         <v>194</v>
       </c>
-      <c r="C9" s="129" t="s">
+      <c r="C9" s="127" t="s">
         <v>195</v>
       </c>
-      <c r="D9" s="166"/>
+      <c r="D9" s="169"/>
     </row>
     <row r="10" spans="1:4">
-      <c r="A10" s="144" t="s">
+      <c r="A10" s="142" t="s">
         <v>459</v>
       </c>
-      <c r="B10" s="130">
+      <c r="B10" s="128">
         <v>13700829950</v>
       </c>
-      <c r="C10" s="131">
+      <c r="C10" s="129">
         <v>14049768711</v>
       </c>
-      <c r="D10" s="158">
+      <c r="D10" s="156">
         <f>IF(AND(B10="",C10=""),"",IFERROR((B10-C10)/ABS(C10),0))</f>
         <v>-2.4835907848561593E-2</v>
       </c>
     </row>
     <row r="11" spans="1:4">
-      <c r="A11" s="144" t="s">
+      <c r="A11" s="142" t="s">
         <v>460</v>
       </c>
-      <c r="B11" s="130">
+      <c r="B11" s="128">
         <v>-2373899857</v>
       </c>
-      <c r="C11" s="131">
+      <c r="C11" s="129">
         <v>-1528832977</v>
       </c>
-      <c r="D11" s="159">
+      <c r="D11" s="157">
         <f>IF(AND(B11="",C11=""),"",IFERROR((ABS(B11)-ABS(C11))/ABS(B11),0))</f>
         <v>0.3559825312378373</v>
       </c>
     </row>
     <row r="12" spans="1:4">
-      <c r="A12" s="145" t="s">
+      <c r="A12" s="143" t="s">
         <v>461</v>
       </c>
-      <c r="B12" s="128">
+      <c r="B12" s="126">
         <v>11326930093</v>
       </c>
-      <c r="C12" s="132">
+      <c r="C12" s="130">
         <v>12520935734</v>
       </c>
-      <c r="D12" s="158"/>
+      <c r="D12" s="156"/>
     </row>
     <row r="13" spans="1:4">
-      <c r="A13" s="144"/>
-      <c r="B13" s="130"/>
-      <c r="C13" s="131"/>
-      <c r="D13" s="158" t="str">
+      <c r="A13" s="142"/>
+      <c r="B13" s="128"/>
+      <c r="C13" s="129"/>
+      <c r="D13" s="156" t="str">
         <f t="shared" ref="D13:D41" si="0">IF(AND(B13="",C13=""),"",IFERROR((B13-C13)/ABS(C13),0))</f>
         <v/>
       </c>
     </row>
     <row r="14" spans="1:4">
-      <c r="A14" s="144" t="s">
+      <c r="A14" s="142" t="s">
         <v>462</v>
       </c>
-      <c r="B14" s="130">
+      <c r="B14" s="128">
         <v>0</v>
       </c>
-      <c r="C14" s="131">
+      <c r="C14" s="129">
         <v>0</v>
       </c>
-      <c r="D14" s="158">
+      <c r="D14" s="156">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:4">
-      <c r="A15" s="144" t="s">
+      <c r="A15" s="142" t="s">
         <v>463</v>
       </c>
-      <c r="B15" s="130">
+      <c r="B15" s="128">
         <v>0</v>
       </c>
-      <c r="C15" s="131">
+      <c r="C15" s="129">
         <v>0</v>
       </c>
-      <c r="D15" s="158">
+      <c r="D15" s="156">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:4">
-      <c r="A16" s="145" t="s">
+      <c r="A16" s="143" t="s">
         <v>464</v>
       </c>
-      <c r="B16" s="128">
+      <c r="B16" s="126">
         <v>0</v>
       </c>
-      <c r="C16" s="132">
+      <c r="C16" s="130">
         <v>0</v>
       </c>
-      <c r="D16" s="158">
+      <c r="D16" s="156">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:4">
-      <c r="A17" s="144"/>
-      <c r="B17" s="130"/>
-      <c r="C17" s="131"/>
-      <c r="D17" s="158" t="str">
+      <c r="A17" s="142"/>
+      <c r="B17" s="128"/>
+      <c r="C17" s="129"/>
+      <c r="D17" s="156" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
     <row r="18" spans="1:4">
-      <c r="A18" s="144" t="s">
+      <c r="A18" s="142" t="s">
         <v>465</v>
       </c>
-      <c r="B18" s="130">
+      <c r="B18" s="128">
         <v>2089453588</v>
       </c>
-      <c r="C18" s="131">
+      <c r="C18" s="129">
         <v>2767118175</v>
       </c>
-      <c r="D18" s="158">
+      <c r="D18" s="156">
         <f t="shared" si="0"/>
         <v>-0.24489904085863626</v>
       </c>
     </row>
     <row r="19" spans="1:4">
-      <c r="A19" s="144" t="s">
+      <c r="A19" s="142" t="s">
         <v>466</v>
       </c>
-      <c r="B19" s="130">
+      <c r="B19" s="128">
         <v>0</v>
       </c>
-      <c r="C19" s="131">
+      <c r="C19" s="129">
         <v>0</v>
       </c>
-      <c r="D19" s="158">
+      <c r="D19" s="156">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="20" spans="1:4">
-      <c r="A20" s="144" t="s">
+      <c r="A20" s="142" t="s">
         <v>467</v>
       </c>
-      <c r="B20" s="130">
+      <c r="B20" s="128">
         <v>0</v>
       </c>
-      <c r="C20" s="131">
+      <c r="C20" s="129">
         <v>0</v>
       </c>
-      <c r="D20" s="158">
+      <c r="D20" s="156">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="21" spans="1:4">
-      <c r="A21" s="144"/>
-      <c r="B21" s="130"/>
-      <c r="C21" s="131"/>
-      <c r="D21" s="158" t="str">
+      <c r="A21" s="142"/>
+      <c r="B21" s="128"/>
+      <c r="C21" s="129"/>
+      <c r="D21" s="156" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
     <row r="22" spans="1:4">
-      <c r="A22" s="145" t="s">
+      <c r="A22" s="143" t="s">
         <v>468</v>
       </c>
-      <c r="B22" s="128">
+      <c r="B22" s="126">
         <v>13416383681</v>
       </c>
-      <c r="C22" s="132">
+      <c r="C22" s="130">
         <v>15288053909</v>
       </c>
-      <c r="D22" s="158">
+      <c r="D22" s="156">
         <f t="shared" si="0"/>
         <v>-0.12242697724254865</v>
       </c>
     </row>
     <row r="23" spans="1:4">
-      <c r="A23" s="144"/>
-      <c r="B23" s="130"/>
-      <c r="C23" s="131"/>
-      <c r="D23" s="158" t="str">
+      <c r="A23" s="142"/>
+      <c r="B23" s="128"/>
+      <c r="C23" s="129"/>
+      <c r="D23" s="156" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
     <row r="24" spans="1:4">
-      <c r="A24" s="144" t="s">
+      <c r="A24" s="142" t="s">
         <v>469</v>
       </c>
-      <c r="B24" s="130">
+      <c r="B24" s="128">
         <v>0</v>
       </c>
-      <c r="C24" s="131">
+      <c r="C24" s="129">
         <v>0</v>
       </c>
-      <c r="D24" s="158">
+      <c r="D24" s="156">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="25" spans="1:4">
-      <c r="A25" s="144"/>
-      <c r="B25" s="130"/>
-      <c r="C25" s="131"/>
-      <c r="D25" s="158" t="str">
+      <c r="A25" s="142"/>
+      <c r="B25" s="128"/>
+      <c r="C25" s="129"/>
+      <c r="D25" s="156" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
     <row r="26" spans="1:4">
-      <c r="A26" s="144" t="s">
+      <c r="A26" s="142" t="s">
         <v>470</v>
       </c>
-      <c r="B26" s="130">
+      <c r="B26" s="128">
         <v>-116539153.09090909</v>
       </c>
-      <c r="C26" s="131">
+      <c r="C26" s="129">
         <v>-246121200</v>
       </c>
-      <c r="D26" s="160">
+      <c r="D26" s="158">
         <f>IF(AND(B26="",C26=""),"",IFERROR((ABS(B26)-ABS(C26))/ABS(B26),0))</f>
         <v>-1.1119185567446797</v>
       </c>
     </row>
     <row r="27" spans="1:4">
-      <c r="A27" s="144" t="s">
+      <c r="A27" s="142" t="s">
         <v>471</v>
       </c>
-      <c r="B27" s="130">
+      <c r="B27" s="128">
         <v>-103070886.54545453</v>
       </c>
-      <c r="C27" s="131">
+      <c r="C27" s="129">
         <v>-427020000</v>
       </c>
-      <c r="D27" s="160">
+      <c r="D27" s="158">
         <f t="shared" ref="D27:D29" si="1">IF(AND(B27="",C27=""),"",IFERROR((ABS(B27)-ABS(C27))/ABS(B27),0))</f>
         <v>-3.1429739697803325</v>
       </c>
     </row>
     <row r="28" spans="1:4">
-      <c r="A28" s="144" t="s">
+      <c r="A28" s="142" t="s">
         <v>472</v>
       </c>
-      <c r="B28" s="130">
+      <c r="B28" s="128">
         <v>-2983032.2424242422</v>
       </c>
-      <c r="C28" s="131">
+      <c r="C28" s="129">
         <v>-900000</v>
       </c>
-      <c r="D28" s="161">
+      <c r="D28" s="159">
         <f t="shared" si="1"/>
         <v>0.69829357282823379</v>
       </c>
     </row>
     <row r="29" spans="1:4">
-      <c r="A29" s="144" t="s">
+      <c r="A29" s="142" t="s">
         <v>473</v>
       </c>
-      <c r="B29" s="130">
+      <c r="B29" s="128">
         <v>-7354800</v>
       </c>
-      <c r="C29" s="131">
+      <c r="C29" s="129">
         <v>-14880000</v>
       </c>
-      <c r="D29" s="160">
+      <c r="D29" s="158">
         <f t="shared" si="1"/>
         <v>-1.0231685429923316</v>
       </c>
     </row>
     <row r="30" spans="1:4">
-      <c r="A30" s="145" t="s">
+      <c r="A30" s="143" t="s">
         <v>474</v>
       </c>
-      <c r="B30" s="128">
+      <c r="B30" s="126">
         <v>-229947871.87878788</v>
       </c>
-      <c r="C30" s="132">
+      <c r="C30" s="130">
         <v>-688921200</v>
       </c>
-      <c r="D30" s="160">
+      <c r="D30" s="158">
         <f>IF(AND(B30="",C30=""),"",IFERROR((ABS(B30)-ABS(C30))/ABS(B30),0))</f>
         <v>-1.9959885880707351</v>
       </c>
     </row>
     <row r="31" spans="1:4">
-      <c r="A31" s="146"/>
-      <c r="B31" s="135"/>
-      <c r="C31" s="136"/>
-      <c r="D31" s="158" t="str">
+      <c r="A31" s="144"/>
+      <c r="B31" s="133"/>
+      <c r="C31" s="134"/>
+      <c r="D31" s="156" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
     <row r="32" spans="1:4" ht="15" thickBot="1">
-      <c r="A32" s="147" t="s">
+      <c r="A32" s="145" t="s">
         <v>41</v>
       </c>
-      <c r="B32" s="139">
+      <c r="B32" s="137">
         <v>13186435809.121212</v>
       </c>
-      <c r="C32" s="140">
+      <c r="C32" s="138">
         <v>14599132709</v>
       </c>
-      <c r="D32" s="158">
+      <c r="D32" s="156">
         <f t="shared" si="0"/>
         <v>-9.6765809862656815E-2</v>
       </c>
     </row>
     <row r="33" spans="1:4" ht="15" thickTop="1">
-      <c r="A33" s="148"/>
-      <c r="B33" s="137"/>
-      <c r="C33" s="138"/>
-      <c r="D33" s="158" t="str">
+      <c r="A33" s="146"/>
+      <c r="B33" s="135"/>
+      <c r="C33" s="136"/>
+      <c r="D33" s="156" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
     <row r="34" spans="1:4">
-      <c r="A34" s="144"/>
-      <c r="B34" s="130"/>
-      <c r="C34" s="131"/>
-      <c r="D34" s="158" t="str">
+      <c r="A34" s="142"/>
+      <c r="B34" s="128"/>
+      <c r="C34" s="129"/>
+      <c r="D34" s="156" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
     <row r="35" spans="1:4">
-      <c r="A35" s="144"/>
-      <c r="B35" s="130"/>
-      <c r="C35" s="131"/>
-      <c r="D35" s="158" t="str">
+      <c r="A35" s="142"/>
+      <c r="B35" s="128"/>
+      <c r="C35" s="129"/>
+      <c r="D35" s="156" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
     <row r="36" spans="1:4">
-      <c r="A36" s="145" t="s">
+      <c r="A36" s="143" t="s">
         <v>475</v>
       </c>
-      <c r="B36" s="130"/>
-      <c r="C36" s="131"/>
-      <c r="D36" s="158" t="str">
+      <c r="B36" s="128"/>
+      <c r="C36" s="129"/>
+      <c r="D36" s="156" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
     <row r="37" spans="1:4">
-      <c r="A37" s="144" t="s">
+      <c r="A37" s="142" t="s">
         <v>476</v>
       </c>
-      <c r="B37" s="130">
+      <c r="B37" s="128">
         <v>2800000000</v>
       </c>
-      <c r="C37" s="131">
+      <c r="C37" s="129">
         <v>2909995061</v>
       </c>
-      <c r="D37" s="158">
+      <c r="D37" s="156">
         <f t="shared" si="0"/>
         <v>-3.7799054188841455E-2</v>
       </c>
     </row>
     <row r="38" spans="1:4">
-      <c r="A38" s="144" t="s">
+      <c r="A38" s="142" t="s">
         <v>477</v>
       </c>
-      <c r="B38" s="130">
+      <c r="B38" s="128">
         <v>146302135788</v>
       </c>
-      <c r="C38" s="131">
+      <c r="C38" s="129">
         <v>167631708652</v>
       </c>
-      <c r="D38" s="158">
+      <c r="D38" s="156">
         <f t="shared" si="0"/>
         <v>-0.12724068158417307</v>
       </c>
     </row>
     <row r="39" spans="1:4">
-      <c r="A39" s="144" t="s">
+      <c r="A39" s="142" t="s">
         <v>478</v>
       </c>
-      <c r="B39" s="130">
+      <c r="B39" s="128">
         <v>20005161795</v>
       </c>
-      <c r="C39" s="131">
+      <c r="C39" s="129">
         <v>0</v>
       </c>
-      <c r="D39" s="158">
+      <c r="D39" s="156">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="40" spans="1:4">
-      <c r="A40" s="144"/>
-      <c r="B40" s="130"/>
-      <c r="C40" s="131"/>
-      <c r="D40" s="158" t="str">
+      <c r="A40" s="142"/>
+      <c r="B40" s="128"/>
+      <c r="C40" s="129"/>
+      <c r="D40" s="156" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
     <row r="41" spans="1:4">
-      <c r="A41" s="149"/>
-      <c r="B41" s="133"/>
-      <c r="C41" s="134"/>
-      <c r="D41" s="158" t="str">
+      <c r="A41" s="147"/>
+      <c r="B41" s="131"/>
+      <c r="C41" s="132"/>
+      <c r="D41" s="156" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
@@ -17617,7 +18124,7 @@
       <c r="B7" t="s">
         <v>38</v>
       </c>
-      <c r="C7" s="127">
+      <c r="C7" s="125">
         <v>-10000</v>
       </c>
     </row>
@@ -17625,7 +18132,7 @@
       <c r="B8" t="s">
         <v>39</v>
       </c>
-      <c r="C8" s="127">
+      <c r="C8" s="125">
         <v>-2500</v>
       </c>
     </row>
